--- a/assets/data/anime.xlsx
+++ b/assets/data/anime.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vedan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Anime Archive\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A8352F-7758-473F-B9D9-5666D313899F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560C9B4E-21BB-4DEF-80B9-3AA6DF7506EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Everything I Have Watched So Fa" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="174">
   <si>
     <t>Name</t>
   </si>
@@ -464,6 +464,84 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>N\A</t>
+  </si>
+  <si>
+    <t>A Silent Voice</t>
+  </si>
+  <si>
+    <t>聲の形 (Koe no Katachi)</t>
+  </si>
+  <si>
+    <t>Kyoto Animation</t>
+  </si>
+  <si>
+    <t>Naoko Yamada</t>
+  </si>
+  <si>
+    <t>Drama, Award Winning</t>
+  </si>
+  <si>
+    <t>silent-voice</t>
+  </si>
+  <si>
+    <t>Grave of the Fireflies</t>
+  </si>
+  <si>
+    <t>火垂るの墓 (Hotaru no Haka)</t>
+  </si>
+  <si>
+    <t>Drama</t>
+  </si>
+  <si>
+    <t>graves-of-the-fireflies</t>
+  </si>
+  <si>
+    <t>The Anthem of the Heart</t>
+  </si>
+  <si>
+    <t>心が叫びたがってるんだ。 (Kokoro ga Sakebitagatterunda.)</t>
+  </si>
+  <si>
+    <t>Tatsuyuki Nagai</t>
+  </si>
+  <si>
+    <t>anthem-of-the-heart</t>
+  </si>
+  <si>
+    <t>Attack on Titan</t>
+  </si>
+  <si>
+    <t>進撃の巨人 (Shingeki no Kyojin)</t>
+  </si>
+  <si>
+    <t>Wit Studio / MAPPA</t>
+  </si>
+  <si>
+    <t>Tetsuro Araki / Yuichiro Hayashi</t>
+  </si>
+  <si>
+    <t>Action, Drama, Suspense, Fantasy</t>
+  </si>
+  <si>
+    <t>attack-on-titan</t>
+  </si>
+  <si>
+    <t>A Lull in the Sea</t>
+  </si>
+  <si>
+    <t>凪のあすから (Nagi no Asukara)</t>
+  </si>
+  <si>
+    <t>P.A. Works</t>
+  </si>
+  <si>
+    <t>Toshiya Shinohara</t>
+  </si>
+  <si>
+    <t>lull-in-the-sea</t>
   </si>
 </sst>
 </file>
@@ -751,7 +829,7 @@
     <col min="8" max="8" width="22.85546875" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
     <col min="11" max="11" width="20.85546875" customWidth="1"/>
-    <col min="12" max="12" width="20.28515625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="28.28515625" style="4" customWidth="1"/>
     <col min="13" max="13" width="35.28515625" style="4" customWidth="1"/>
     <col min="14" max="14" width="12.5703125" style="4"/>
     <col min="15" max="15" width="26.140625" style="4" customWidth="1"/>
@@ -1641,7 +1719,7 @@
         <v>7.1</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>101</v>
@@ -1691,7 +1769,7 @@
         <v>7.25</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>107</v>
@@ -1823,59 +1901,244 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
+      <c r="A22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="3">
+        <v>8.94</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2016</v>
+      </c>
+      <c r="J22" s="3">
+        <v>130</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="N22" s="4">
+        <v>21</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
+      <c r="A23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1988</v>
+      </c>
+      <c r="J23" s="3">
+        <v>88</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="N23" s="4">
+        <v>22</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q23" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="A24" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="3">
+        <v>8.02</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <v>2015</v>
+      </c>
+      <c r="J24" s="3">
+        <v>119</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N24" s="4">
+        <v>23</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q24" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="A25" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="3">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
+      <c r="G25" s="3">
+        <v>4</v>
+      </c>
+      <c r="H25" s="3">
+        <v>22</v>
+      </c>
+      <c r="I25" s="3">
+        <v>2013</v>
+      </c>
+      <c r="J25" s="3">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="N25" s="4">
+        <v>24</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="A26" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="3">
+        <v>8.06</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3">
+        <v>26</v>
+      </c>
+      <c r="I26" s="3">
+        <v>2013</v>
+      </c>
+      <c r="J26" s="3">
+        <v>23</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="N26" s="4">
+        <v>25</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C27" s="3"/>

--- a/assets/data/anime.xlsx
+++ b/assets/data/anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Anime Archive\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560C9B4E-21BB-4DEF-80B9-3AA6DF7506EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC4C890-0E2F-405E-B763-6EFBD07759B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="335">
   <si>
     <t>Name</t>
   </si>
@@ -542,6 +542,489 @@
   </si>
   <si>
     <t>lull-in-the-sea</t>
+  </si>
+  <si>
+    <t>Hyouka</t>
+  </si>
+  <si>
+    <t>氷菓 (Hyouka)</t>
+  </si>
+  <si>
+    <t>Yasuhiro Takemoto</t>
+  </si>
+  <si>
+    <t>Mystery, Slice of Life</t>
+  </si>
+  <si>
+    <t>hyouka</t>
+  </si>
+  <si>
+    <t>Darling in the Franxx</t>
+  </si>
+  <si>
+    <t>ダーリン・イン・ザ・フランキス (Dārin In Za Furankisu)</t>
+  </si>
+  <si>
+    <t>A-1 Pictures / Trigger / CloverWorks</t>
+  </si>
+  <si>
+    <t>Atsushi Nishigori</t>
+  </si>
+  <si>
+    <t>Action, Drama, Sci-Fi, Romance</t>
+  </si>
+  <si>
+    <t>darling-in-the-franxx</t>
+  </si>
+  <si>
+    <t>Re:Zero</t>
+  </si>
+  <si>
+    <t>Re:ゼロから始める異世界生活 (Re:Zero kara Hajimeru Isekai Seikatsu)</t>
+  </si>
+  <si>
+    <t>White Fox</t>
+  </si>
+  <si>
+    <t>Masaharu Watanabe</t>
+  </si>
+  <si>
+    <t>Drama, Fantasy, Suspense</t>
+  </si>
+  <si>
+    <t>re-zero</t>
+  </si>
+  <si>
+    <t>Fireworks</t>
+  </si>
+  <si>
+    <t>打ち上げ花火、下から見るか？横から見るか？ (Uchiage Hanabi)</t>
+  </si>
+  <si>
+    <t>Shaft</t>
+  </si>
+  <si>
+    <t>Akiyuki Shinbo / Nobuyuki Takeuchi</t>
+  </si>
+  <si>
+    <t>fireworks</t>
+  </si>
+  <si>
+    <t>Hello World</t>
+  </si>
+  <si>
+    <t>HELLO WORLD</t>
+  </si>
+  <si>
+    <t>Graphinica</t>
+  </si>
+  <si>
+    <t>Tomohiko Itou</t>
+  </si>
+  <si>
+    <t>Sci-Fi, Drama, Romance</t>
+  </si>
+  <si>
+    <t>hello-world</t>
+  </si>
+  <si>
+    <t>Summer Ghost</t>
+  </si>
+  <si>
+    <t>サマーゴースト (Summer Ghost)</t>
+  </si>
+  <si>
+    <t>Flat Studio</t>
+  </si>
+  <si>
+    <t>loundraw</t>
+  </si>
+  <si>
+    <t>Drama, Supernatural</t>
+  </si>
+  <si>
+    <t>Look Back</t>
+  </si>
+  <si>
+    <t>ルックバック (Look Back)</t>
+  </si>
+  <si>
+    <t>Studio Durian</t>
+  </si>
+  <si>
+    <t>Kiyotaka Oshiyama</t>
+  </si>
+  <si>
+    <t>Drama, Avant Garde</t>
+  </si>
+  <si>
+    <t>Vinland Saga</t>
+  </si>
+  <si>
+    <t>ヴィンランド・サガ (Vinland Saga)</t>
+  </si>
+  <si>
+    <t>WIT Studio / MAPPA</t>
+  </si>
+  <si>
+    <t>Shuhei Yabuta</t>
+  </si>
+  <si>
+    <t>Action, Adventure, Drama</t>
+  </si>
+  <si>
+    <t>Death Note</t>
+  </si>
+  <si>
+    <t>デスノート (Death Note)</t>
+  </si>
+  <si>
+    <t>Madhouse</t>
+  </si>
+  <si>
+    <t>Tetsuro Araki</t>
+  </si>
+  <si>
+    <t>Supernatural, Suspense</t>
+  </si>
+  <si>
+    <t>Clannad</t>
+  </si>
+  <si>
+    <t>クラナド (Clannad)</t>
+  </si>
+  <si>
+    <t>Tatsuya Ishihara</t>
+  </si>
+  <si>
+    <t>Insomniacs After School</t>
+  </si>
+  <si>
+    <t>君は放課後インソムニア (Kimi wa Houkago Insomnia)</t>
+  </si>
+  <si>
+    <t>LIDENFILMS</t>
+  </si>
+  <si>
+    <t>Yuki Ikeda</t>
+  </si>
+  <si>
+    <t>Romance, Slice of Life</t>
+  </si>
+  <si>
+    <t>The Apothecary Diaries</t>
+  </si>
+  <si>
+    <t>薬屋のひとりごと (Kusuriya no Hitorigoto)</t>
+  </si>
+  <si>
+    <t>OLM / TOHO animation</t>
+  </si>
+  <si>
+    <t>Norihiro Naganuma</t>
+  </si>
+  <si>
+    <t>Drama, Mystery, Medical</t>
+  </si>
+  <si>
+    <t>Jujutsu Kaisen</t>
+  </si>
+  <si>
+    <t>呪術廻戦 (Jujutsu Kaisen)</t>
+  </si>
+  <si>
+    <t>MAPPA</t>
+  </si>
+  <si>
+    <t>Sunghoo Park / Shota Goshozono</t>
+  </si>
+  <si>
+    <t>Anohana</t>
+  </si>
+  <si>
+    <t>あの日見た花の名前を僕達はまだ知らない。 (Anohana)</t>
+  </si>
+  <si>
+    <t>365 Days to the Wedding</t>
+  </si>
+  <si>
+    <t>Ashi Productions</t>
+  </si>
+  <si>
+    <t>Hiroshi Ikehata</t>
+  </si>
+  <si>
+    <t>Blue Box</t>
+  </si>
+  <si>
+    <t>アオのハコ (Ao no Hako)</t>
+  </si>
+  <si>
+    <t>Telecom Animation Film</t>
+  </si>
+  <si>
+    <t>Yūichirō Yano</t>
+  </si>
+  <si>
+    <t>Romance, Sports</t>
+  </si>
+  <si>
+    <t>The Angel Next Door Spoils Me Rotten</t>
+  </si>
+  <si>
+    <t>お隣の天使様にいつの間にか駄目人間にされていた件 (Otonari no Tenshi-sama)</t>
+  </si>
+  <si>
+    <t>Project No.9</t>
+  </si>
+  <si>
+    <t>Lihua Wang / Chihiro Kumano</t>
+  </si>
+  <si>
+    <t>The Dangers in My Heart</t>
+  </si>
+  <si>
+    <t>僕の心のヤバイやつ (Boku no Kokoro no Yabai Yatsu)</t>
+  </si>
+  <si>
+    <t>Shin-Ei Animation</t>
+  </si>
+  <si>
+    <t>Hiroaki Akagi</t>
+  </si>
+  <si>
+    <t>Comedy, Romance</t>
+  </si>
+  <si>
+    <t>Studio Mother</t>
+  </si>
+  <si>
+    <t>Junichi Yamamoto / Takao Kato</t>
+  </si>
+  <si>
+    <t>Kaguya-sama: Love Is War</t>
+  </si>
+  <si>
+    <t>かぐや様は告らせたい ～天才たちの恋愛頭脳戦～ (Kaguya-sama wa Kokurasetai)</t>
+  </si>
+  <si>
+    <t>Shinichi Omata</t>
+  </si>
+  <si>
+    <t>Toradora!</t>
+  </si>
+  <si>
+    <t>とらドラ！ (Toradora!)</t>
+  </si>
+  <si>
+    <t>J.C.Staff</t>
+  </si>
+  <si>
+    <t>Comedy, Drama, Romance</t>
+  </si>
+  <si>
+    <t>Erased</t>
+  </si>
+  <si>
+    <t>僕だけがいない街 (Boku dake ga Inai Machi)</t>
+  </si>
+  <si>
+    <t>Mystery, Supernatural, Suspense</t>
+  </si>
+  <si>
+    <t>Classroom of the Elite</t>
+  </si>
+  <si>
+    <t>ようこそ実力至上主義の教室へ (Youkoso Jitsuryoku Shijou Shugi no Kyrosshitsu e)</t>
+  </si>
+  <si>
+    <t>Lerche</t>
+  </si>
+  <si>
+    <t>Seiji Kishi / Hiroyuki Hashimoto / Noriyuki Nomata</t>
+  </si>
+  <si>
+    <t>Drama, Suspense</t>
+  </si>
+  <si>
+    <t>Spy × Family</t>
+  </si>
+  <si>
+    <t>SPY×FAMILY (Spy × Family)</t>
+  </si>
+  <si>
+    <t>Wit Studio / CloverWorks</t>
+  </si>
+  <si>
+    <t>Kazuhiro Furuhashi</t>
+  </si>
+  <si>
+    <t>Action, Comedy</t>
+  </si>
+  <si>
+    <t>Alya Sometimes Hides Her Feelings in Russian</t>
+  </si>
+  <si>
+    <t>時々ボソッとロシア語でデレる隣のアーlyaさん (Tokidoki Bosotto Russia-go de Dereru Tonari no Alya-san)</t>
+  </si>
+  <si>
+    <t>Doga Kobo</t>
+  </si>
+  <si>
+    <t>Ryota Itoh</t>
+  </si>
+  <si>
+    <t>The Fragrant Flower Blooms with Dignity</t>
+  </si>
+  <si>
+    <t>薫る花は凛と咲く (Kaoru Hana wa Rin to Saku)</t>
+  </si>
+  <si>
+    <t>Miho Tan Tanaka</t>
+  </si>
+  <si>
+    <t>Howl's Moving Castle</t>
+  </si>
+  <si>
+    <t>ハウルの動く城 (Hauru no Ugoku Shiro)</t>
+  </si>
+  <si>
+    <t>Hayao Miyazaki</t>
+  </si>
+  <si>
+    <t>Adventure, Fantasy, Romance</t>
+  </si>
+  <si>
+    <t>Chainsaw Man</t>
+  </si>
+  <si>
+    <t>チェンソーマン (Chainsaw Man)</t>
+  </si>
+  <si>
+    <t>Ryu Nakayama / Tatsuya Yoshihara</t>
+  </si>
+  <si>
+    <t>Action, Dark Fantasy, Gore</t>
+  </si>
+  <si>
+    <t>Too Many Losing Heroines!</t>
+  </si>
+  <si>
+    <t>負けヒロインが多すぎる！ (Make Heroine ga Oosugiru!)</t>
+  </si>
+  <si>
+    <t>Shotaro Kitamura</t>
+  </si>
+  <si>
+    <t>ジョゼと虎と魚たち (Joze to Tora to Sakana-tachi)</t>
+  </si>
+  <si>
+    <t>Bones</t>
+  </si>
+  <si>
+    <t>Kotaro Tamura</t>
+  </si>
+  <si>
+    <t>More Than a Married Couple,  But Not Lovers</t>
+  </si>
+  <si>
+    <t>夫婦以上、恋人未満。 (Fuufu Ijou Koibito Miman.)</t>
+  </si>
+  <si>
+    <t>結婚するって、本当ですか (Kekkon Surutte,  Honto desu ka?)</t>
+  </si>
+  <si>
+    <t>Josee,  the Tiger and the Fish</t>
+  </si>
+  <si>
+    <t>summer-ghost</t>
+  </si>
+  <si>
+    <t>look-back</t>
+  </si>
+  <si>
+    <t>vinland-saga</t>
+  </si>
+  <si>
+    <t>death-note</t>
+  </si>
+  <si>
+    <t>jujutsu-kaisen</t>
+  </si>
+  <si>
+    <t>blue-box</t>
+  </si>
+  <si>
+    <t>spy-family</t>
+  </si>
+  <si>
+    <t>chainsaw-man</t>
+  </si>
+  <si>
+    <t>clannad</t>
+  </si>
+  <si>
+    <t>insomniacs-after-school</t>
+  </si>
+  <si>
+    <t>classroom-of-the-elite</t>
+  </si>
+  <si>
+    <t>the-fragrant-flower-blooms-with-dignity</t>
+  </si>
+  <si>
+    <t>josee-the-tiger-and-the-fish</t>
+  </si>
+  <si>
+    <t>anohana</t>
+  </si>
+  <si>
+    <t>days-to-the-wedding</t>
+  </si>
+  <si>
+    <t>the-apothecary-diaries</t>
+  </si>
+  <si>
+    <t>the-dangers-in-my-heart</t>
+  </si>
+  <si>
+    <t>more-than-a-married-couple-but-not-lovers</t>
+  </si>
+  <si>
+    <t>erased</t>
+  </si>
+  <si>
+    <t>alya-sometimes-hides-her-feelings-in-russian</t>
+  </si>
+  <si>
+    <t>howl's-moving-castle</t>
+  </si>
+  <si>
+    <t>the-angel-next-door-spoils-me-rotten</t>
+  </si>
+  <si>
+    <t>kaguya-sama-love-is-war</t>
+  </si>
+  <si>
+    <t>toradora</t>
+  </si>
+  <si>
+    <t>too-many-losing-heroines</t>
+  </si>
+  <si>
+    <t>Takopi's Original Sin</t>
+  </si>
+  <si>
+    <t>タコピーの原罪 (Takopi no Genzai)</t>
+  </si>
+  <si>
+    <t>Shinpei Tomooka</t>
+  </si>
+  <si>
+    <t>Drama, Psychological, Sci-Fi</t>
+  </si>
+  <si>
+    <t>takopi's-original-sin</t>
   </si>
 </sst>
 </file>
@@ -589,7 +1072,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -600,6 +1083,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -824,15 +1310,17 @@
   <cols>
     <col min="1" max="1" width="41.28515625" customWidth="1"/>
     <col min="2" max="2" width="95.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="4"/>
     <col min="6" max="6" width="31.42578125" customWidth="1"/>
     <col min="7" max="7" width="18.42578125" customWidth="1"/>
     <col min="8" max="8" width="22.85546875" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
-    <col min="12" max="12" width="28.28515625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="35.28515625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="35.42578125" customWidth="1"/>
+    <col min="12" max="12" width="31.7109375" style="4" customWidth="1"/>
+    <col min="13" max="13" width="36.7109375" style="4" customWidth="1"/>
     <col min="14" max="14" width="12.5703125" style="4"/>
-    <col min="15" max="15" width="26.140625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="40.42578125" style="4" customWidth="1"/>
     <col min="16" max="16" width="15.5703125" customWidth="1"/>
     <col min="17" max="17" width="12.5703125" style="4"/>
   </cols>
@@ -2141,347 +2629,1493 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8.08</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="G27" s="3">
+        <v>1</v>
+      </c>
+      <c r="H27" s="3">
+        <v>22</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2012</v>
+      </c>
+      <c r="J27" s="3">
+        <v>25</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N27" s="4">
+        <v>26</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="A28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3">
+        <v>24</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2018</v>
+      </c>
+      <c r="J28" s="3">
+        <v>24</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="N28" s="4">
+        <v>27</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q28" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="A29" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" t="s">
+        <v>186</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="3">
+        <v>8.24</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
+      <c r="G29" s="3">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3">
+        <v>25</v>
+      </c>
+      <c r="I29" s="3">
+        <v>2016</v>
+      </c>
+      <c r="J29" s="3">
+        <v>25</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="N29" s="4">
+        <v>28</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="A30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="3">
+        <v>6.6</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
+        <v>2017</v>
+      </c>
+      <c r="J30" s="3">
+        <v>90</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="4">
+        <v>29</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="A31" t="s">
+        <v>196</v>
+      </c>
+      <c r="B31" t="s">
+        <v>197</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="3">
+        <v>7.55</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="G31" s="3">
+        <v>1</v>
+      </c>
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
+        <v>2019</v>
+      </c>
+      <c r="J31" s="3">
+        <v>98</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="N31" s="4">
+        <v>30</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B32" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="4">
+        <v>7.42</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="4">
+        <v>1</v>
+      </c>
+      <c r="I32" s="4">
+        <v>2021</v>
+      </c>
+      <c r="J32" s="4">
+        <v>40</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="N32" s="4">
+        <v>31</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
+      <c r="G33" s="3">
+        <v>1</v>
+      </c>
+      <c r="H33" s="3">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2024</v>
+      </c>
+      <c r="J33" s="3">
+        <v>58</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="N33" s="4">
+        <v>32</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q33" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="G34" s="3">
+        <v>2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>24</v>
+      </c>
+      <c r="I34" s="3">
+        <v>2019</v>
+      </c>
+      <c r="J34" s="3">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="N34" s="4">
+        <v>33</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q34" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="3">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="36" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>37</v>
+      </c>
+      <c r="I35" s="3">
+        <v>2006</v>
+      </c>
+      <c r="J35" s="3">
+        <v>23</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="N35" s="4">
+        <v>34</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q35" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D36" s="3">
+        <v>8.01</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-    </row>
-    <row r="37" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
+      <c r="G36" s="3">
+        <v>2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>23</v>
+      </c>
+      <c r="I36" s="3">
+        <v>2007</v>
+      </c>
+      <c r="J36" s="3">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="4">
+        <v>35</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q36" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D37" s="3">
+        <v>8.02</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-    </row>
-    <row r="38" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <v>13</v>
+      </c>
+      <c r="I37" s="3">
+        <v>2023</v>
+      </c>
+      <c r="J37" s="3">
+        <v>24</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="N37" s="4">
+        <v>36</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q37" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" t="s">
+        <v>231</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-    </row>
-    <row r="39" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
+      <c r="G38" s="3">
+        <v>2</v>
+      </c>
+      <c r="H38" s="3">
+        <v>24</v>
+      </c>
+      <c r="I38" s="3">
+        <v>2023</v>
+      </c>
+      <c r="J38" s="3">
+        <v>24</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="N38" s="4">
+        <v>37</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>235</v>
+      </c>
+      <c r="B39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="3">
+        <v>8.65</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
+      <c r="G39" s="3">
+        <v>2</v>
+      </c>
+      <c r="H39" s="3">
+        <v>24</v>
+      </c>
+      <c r="I39" s="3">
+        <v>2020</v>
+      </c>
+      <c r="J39" s="3">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N39" s="4">
+        <v>38</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q39" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="3">
+        <v>8.31</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="G40" s="3">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3">
+        <v>11</v>
+      </c>
+      <c r="I40" s="3">
+        <v>2011</v>
+      </c>
+      <c r="J40" s="3">
+        <v>22</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="N40" s="4">
+        <v>39</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q40" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>241</v>
+      </c>
+      <c r="B41" t="s">
+        <v>303</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="3">
+        <v>7.22</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="G41" s="3">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3">
+        <v>12</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2024</v>
+      </c>
+      <c r="J41" s="3">
+        <v>24</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="N41" s="4">
+        <v>40</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q41" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="3">
+        <v>8.35</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="G42" s="3">
+        <v>2</v>
+      </c>
+      <c r="H42" s="3">
+        <v>25</v>
+      </c>
+      <c r="I42" s="3">
+        <v>2024</v>
+      </c>
+      <c r="J42" s="3">
+        <v>24</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="N42" s="4">
+        <v>41</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q42" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B43" t="s">
+        <v>250</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="3">
+        <v>7.85</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
+      <c r="G43" s="3">
+        <v>2</v>
+      </c>
+      <c r="H43" s="3">
+        <v>12</v>
+      </c>
+      <c r="I43" s="3">
+        <v>2023</v>
+      </c>
+      <c r="J43" s="3">
+        <v>24</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="N43" s="4">
+        <v>42</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q43" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="3">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="G44" s="3">
+        <v>2</v>
+      </c>
+      <c r="H44" s="3">
+        <v>12</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2023</v>
+      </c>
+      <c r="J44" s="3">
+        <v>24</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="N44" s="4">
+        <v>43</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q44" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>301</v>
+      </c>
+      <c r="B45" t="s">
+        <v>302</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" s="3">
+        <v>7.51</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="G45" s="3">
+        <v>1</v>
+      </c>
+      <c r="H45" s="3">
+        <v>12</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2022</v>
+      </c>
+      <c r="J45" s="4">
+        <v>24</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="N45" s="4">
+        <v>44</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q45" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>260</v>
+      </c>
+      <c r="B46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="G46" s="3">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3">
+        <v>12</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2019</v>
+      </c>
+      <c r="J46" s="3">
+        <v>24</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="N46" s="4">
+        <v>45</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q46" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>263</v>
+      </c>
+      <c r="B47" t="s">
+        <v>264</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
+      <c r="G47" s="3">
+        <v>1</v>
+      </c>
+      <c r="H47" s="3">
+        <v>25</v>
+      </c>
+      <c r="I47" s="3">
+        <v>2008</v>
+      </c>
+      <c r="J47" s="3">
+        <v>24</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="N47" s="4">
+        <v>46</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q47" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>267</v>
+      </c>
+      <c r="B48" t="s">
+        <v>268</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="3">
+        <v>8.31</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
+      <c r="G48" s="3">
+        <v>1</v>
+      </c>
+      <c r="H48" s="3">
+        <v>12</v>
+      </c>
+      <c r="I48" s="3">
+        <v>2016</v>
+      </c>
+      <c r="J48" s="3">
+        <v>23</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="N48" s="4">
+        <v>47</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q48" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>270</v>
+      </c>
+      <c r="B49" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" s="3">
+        <v>7.86</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
+      <c r="G49" s="3">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3">
+        <v>13</v>
+      </c>
+      <c r="I49" s="3">
+        <v>2017</v>
+      </c>
+      <c r="J49" s="3">
+        <v>24</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="N49" s="4">
+        <v>48</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q49" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>275</v>
+      </c>
+      <c r="B50" t="s">
+        <v>276</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
+      <c r="G50" s="3">
+        <v>3</v>
+      </c>
+      <c r="H50" s="3">
+        <v>12</v>
+      </c>
+      <c r="I50" s="3">
+        <v>2022</v>
+      </c>
+      <c r="J50" s="3">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="N50" s="4">
+        <v>49</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q50" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>280</v>
+      </c>
+      <c r="B51" t="s">
+        <v>281</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D51" s="3">
+        <v>7.62</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
+      <c r="G51" s="3">
+        <v>2</v>
+      </c>
+      <c r="H51" s="3">
+        <v>12</v>
+      </c>
+      <c r="I51" s="3">
+        <v>2024</v>
+      </c>
+      <c r="J51" s="3">
+        <v>24</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="N51" s="4">
+        <v>50</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q51" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>284</v>
+      </c>
+      <c r="B52" t="s">
+        <v>285</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D52" s="3">
+        <v>8.42</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+      <c r="G52" s="3">
+        <v>1</v>
+      </c>
+      <c r="H52" s="3">
+        <v>12</v>
+      </c>
+      <c r="I52" s="3">
+        <v>2026</v>
+      </c>
+      <c r="J52" s="3">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="N52" s="4">
+        <v>51</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q52" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>287</v>
+      </c>
+      <c r="B53" t="s">
+        <v>288</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="3">
+        <v>8.66</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
+      <c r="G53" s="3">
+        <v>1</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3">
+        <v>2004</v>
+      </c>
+      <c r="J53" s="3">
+        <v>119</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="N53" s="4">
+        <v>52</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q53" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>291</v>
+      </c>
+      <c r="B54" t="s">
+        <v>292</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D54" s="3">
+        <v>8.51</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
+      <c r="G54" s="3">
+        <v>2</v>
+      </c>
+      <c r="H54" s="3">
+        <v>12</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2022</v>
+      </c>
+      <c r="J54" s="3">
+        <v>24</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="N54" s="4">
+        <v>53</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q54" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>295</v>
+      </c>
+      <c r="B55" t="s">
+        <v>296</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" s="3">
+        <v>8.25</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
+      <c r="G55" s="3">
+        <v>1</v>
+      </c>
+      <c r="H55" s="3">
+        <v>12</v>
+      </c>
+      <c r="I55" s="3">
+        <v>2024</v>
+      </c>
+      <c r="J55" s="3">
+        <v>24</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="N55" s="4">
+        <v>54</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q55" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>304</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="3">
+        <v>8.41</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
+      <c r="G56" s="3">
+        <v>1</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3">
+        <v>2020</v>
+      </c>
+      <c r="J56" s="3">
+        <v>98</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N56" s="4">
+        <v>55</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q56" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>330</v>
+      </c>
+      <c r="B57" t="s">
+        <v>331</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" s="3">
+        <v>7.94</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="G57" s="3">
+        <v>1</v>
+      </c>
+      <c r="H57" s="3">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2026</v>
+      </c>
+      <c r="J57" s="3">
+        <v>24</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="N57" s="4">
+        <v>56</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q57" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -2492,7 +4126,7 @@
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -2503,7 +4137,7 @@
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2514,7 +4148,7 @@
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -2525,7 +4159,7 @@
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -2536,7 +4170,7 @@
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -2547,7 +4181,7 @@
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
     </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>

--- a/assets/data/anime.xlsx
+++ b/assets/data/anime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Anime Archive\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68BDE85C-219D-49A6-B2E4-0A8239D1433D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476ECD23-E9CE-4A80-87AD-7A4E6C4E7BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-72" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Everything I Have Watched So Fa" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="364">
   <si>
     <t>Name</t>
   </si>
@@ -1037,6 +1037,81 @@
   </si>
   <si>
     <t>アーケイン (Ākein)</t>
+  </si>
+  <si>
+    <t>Love Unseen Beneath the Clear Night Sky</t>
+  </si>
+  <si>
+    <t>見えない恋は晴れた夜空のもとで (Mietenaishi Koi wa Hareta Yozora no Moto de)</t>
+  </si>
+  <si>
+    <t>Kei Oikawa</t>
+  </si>
+  <si>
+    <t>love-unseen-beneath-the-clear-night-sky</t>
+  </si>
+  <si>
+    <t>僕は彼女を勘違いしてる (Boku wa Kanojo wo Kanchigai Shiteru)</t>
+  </si>
+  <si>
+    <t>Pine Jam</t>
+  </si>
+  <si>
+    <t>Kazuhiro Yoneda</t>
+  </si>
+  <si>
+    <t>Comedy, Romance, Slice of Life</t>
+  </si>
+  <si>
+    <t>oh-boy-was-i-wrong-about-her</t>
+  </si>
+  <si>
+    <t>Oh Boy,  Was I Wrong About Her</t>
+  </si>
+  <si>
+    <t>I Want to Love You Till Your Dying Day</t>
+  </si>
+  <si>
+    <t>きみが死ぬまで恋をしたい (Kimi ga Shinu made Koi wo Shitai)</t>
+  </si>
+  <si>
+    <t>ROLL2</t>
+  </si>
+  <si>
+    <t>Yasushi Tomoda</t>
+  </si>
+  <si>
+    <t>Drama, Dark Fantasy, Yuri</t>
+  </si>
+  <si>
+    <t>i-want-to-love-you-till-your-dying-day</t>
+  </si>
+  <si>
+    <t>I Want to End This Love Game</t>
+  </si>
+  <si>
+    <t>愛してるゲームを終わらせたい (Aishiteiru Game wo Owarasetai)</t>
+  </si>
+  <si>
+    <t>Shota Umehara</t>
+  </si>
+  <si>
+    <t>i-want-to-end-this-love-game</t>
+  </si>
+  <si>
+    <t>Lycoris Recoil</t>
+  </si>
+  <si>
+    <t>リコリス・リコイル (Rikoris Rikoiru)</t>
+  </si>
+  <si>
+    <t>Shingo Adachi</t>
+  </si>
+  <si>
+    <t>Action, Sci-Fi</t>
+  </si>
+  <si>
+    <t>lycoris-recoil</t>
   </si>
 </sst>
 </file>
@@ -4136,59 +4211,245 @@
       </c>
     </row>
     <row r="58" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
+      <c r="A58" t="s">
+        <v>339</v>
+      </c>
+      <c r="B58" t="s">
+        <v>340</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58" s="3">
+        <v>7.68</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
+      <c r="G58" s="3">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3">
+        <v>12</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2026</v>
+      </c>
+      <c r="J58" s="3">
+        <v>24</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N58" s="4">
+        <v>57</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q58" s="4" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="59" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
+      <c r="A59" t="s">
+        <v>348</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D59" s="3">
+        <v>7.42</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
+      <c r="G59" s="3">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3">
+        <v>12</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2026</v>
+      </c>
+      <c r="J59" s="3">
+        <v>24</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="N59" s="4">
+        <v>58</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="60" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
+      <c r="A60" t="s">
+        <v>349</v>
+      </c>
+      <c r="B60" t="s">
+        <v>350</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D60" s="3">
+        <v>7.82</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
+      <c r="G60" s="3">
+        <v>1</v>
+      </c>
+      <c r="H60" s="3">
+        <v>12</v>
+      </c>
+      <c r="I60" s="3">
+        <v>2026</v>
+      </c>
+      <c r="J60" s="3">
+        <v>24</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="N60" s="4">
+        <v>59</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q60" s="4" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="61" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
+      <c r="A61" t="s">
+        <v>355</v>
+      </c>
+      <c r="B61" t="s">
+        <v>356</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D61" s="3">
+        <v>7.95</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
+      <c r="G61" s="3">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3">
+        <v>12</v>
+      </c>
+      <c r="I61" s="3">
+        <v>2026</v>
+      </c>
+      <c r="J61" s="3">
+        <v>24</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="N61" s="4">
+        <v>60</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q61" s="4" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="62" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
+      <c r="A62" t="s">
+        <v>359</v>
+      </c>
+      <c r="B62" t="s">
+        <v>360</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="3">
+        <v>8.23</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
+      <c r="G62" s="3">
+        <v>1</v>
+      </c>
+      <c r="H62" s="3">
+        <v>13</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2022</v>
+      </c>
+      <c r="J62" s="3">
+        <v>24</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="N62" s="4">
+        <v>61</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q62" s="4" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="63" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>

--- a/assets/data/anime.xlsx
+++ b/assets/data/anime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Anime Archive\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476ECD23-E9CE-4A80-87AD-7A4E6C4E7BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A41953-1B30-4BBD-9E9E-56E6F1E2DED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-72" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Everything I Have Watched So Fa" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="365">
   <si>
     <t>Name</t>
   </si>
@@ -1112,6 +1112,9 @@
   </si>
   <si>
     <t>lycoris-recoil</t>
+  </si>
+  <si>
+    <t>If you ever feel like giving up on life, watch this !</t>
   </si>
 </sst>
 </file>
@@ -1396,26 +1399,26 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" customWidth="1"/>
-    <col min="2" max="2" width="95.28515625" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="4"/>
-    <col min="6" max="6" width="31.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="35.42578125" customWidth="1"/>
-    <col min="12" max="12" width="31.7109375" style="4" customWidth="1"/>
-    <col min="13" max="13" width="36.7109375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="4"/>
-    <col min="15" max="15" width="40.42578125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="4"/>
+    <col min="1" max="1" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="95.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="4"/>
+    <col min="6" max="6" width="31.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="35.44140625" customWidth="1"/>
+    <col min="12" max="12" width="31.6640625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="36.6640625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="4"/>
+    <col min="15" max="15" width="40.44140625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="15.5546875" customWidth="1"/>
+    <col min="17" max="17" width="12.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1471,7 +1474,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -1524,7 +1527,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -1574,7 +1577,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -1677,7 +1680,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -1777,7 +1780,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>48</v>
       </c>
@@ -1827,7 +1830,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>54</v>
       </c>
@@ -1880,7 +1883,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -1930,7 +1933,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
@@ -1980,7 +1983,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>71</v>
       </c>
@@ -2030,7 +2033,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>74</v>
       </c>
@@ -2083,7 +2086,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>78</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>334</v>
       </c>
@@ -2183,7 +2186,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>87</v>
       </c>
@@ -2233,7 +2236,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>92</v>
       </c>
@@ -2283,7 +2286,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>96</v>
       </c>
@@ -2333,7 +2336,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>102</v>
       </c>
@@ -2383,7 +2386,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>107</v>
       </c>
@@ -2433,7 +2436,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -2483,7 +2486,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>146</v>
       </c>
@@ -2497,9 +2500,11 @@
         <v>8.94</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F22" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="G22" s="3">
         <v>1</v>
       </c>
@@ -2530,8 +2535,11 @@
       <c r="Q22" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="R22" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>152</v>
       </c>
@@ -2579,7 +2587,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>156</v>
       </c>
@@ -2627,7 +2635,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>160</v>
       </c>
@@ -2675,7 +2683,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>166</v>
       </c>
@@ -2723,7 +2731,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -2771,7 +2779,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>176</v>
       </c>
@@ -2819,7 +2827,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>182</v>
       </c>
@@ -2867,7 +2875,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>188</v>
       </c>
@@ -2915,7 +2923,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>193</v>
       </c>
@@ -2963,7 +2971,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>199</v>
       </c>
@@ -3010,7 +3018,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>204</v>
       </c>
@@ -3058,7 +3066,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>209</v>
       </c>
@@ -3106,7 +3114,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>214</v>
       </c>
@@ -3154,7 +3162,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -3202,7 +3210,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>222</v>
       </c>
@@ -3250,7 +3258,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>227</v>
       </c>
@@ -3298,7 +3306,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>232</v>
       </c>
@@ -3346,7 +3354,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>236</v>
       </c>
@@ -3394,7 +3402,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>238</v>
       </c>
@@ -3442,7 +3450,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>241</v>
       </c>
@@ -3490,7 +3498,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>246</v>
       </c>
@@ -3538,7 +3546,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>250</v>
       </c>
@@ -3586,7 +3594,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>296</v>
       </c>
@@ -3634,7 +3642,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>257</v>
       </c>
@@ -3682,7 +3690,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>260</v>
       </c>
@@ -3730,7 +3738,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>264</v>
       </c>
@@ -3778,7 +3786,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>267</v>
       </c>
@@ -3826,7 +3834,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>271</v>
       </c>
@@ -3874,7 +3882,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>276</v>
       </c>
@@ -3922,7 +3930,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>279</v>
       </c>
@@ -3970,7 +3978,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>282</v>
       </c>
@@ -4018,7 +4026,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>286</v>
       </c>
@@ -4066,7 +4074,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>290</v>
       </c>
@@ -4114,7 +4122,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>299</v>
       </c>
@@ -4162,7 +4170,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>325</v>
       </c>
@@ -4210,7 +4218,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>339</v>
       </c>
@@ -4258,7 +4266,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>348</v>
       </c>
@@ -4307,7 +4315,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>349</v>
       </c>
@@ -4355,7 +4363,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>355</v>
       </c>
@@ -4403,7 +4411,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>359</v>
       </c>
@@ -4451,7 +4459,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -4462,7 +4470,7 @@
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
     </row>
-    <row r="64" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -4473,7 +4481,7 @@
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
     </row>
-    <row r="65" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -4484,7 +4492,7 @@
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
     </row>
-    <row r="66" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -4495,7 +4503,7 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
     </row>
-    <row r="67" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -4506,7 +4514,7 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
     </row>
-    <row r="68" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -4517,7 +4525,7 @@
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
     </row>
-    <row r="69" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -4528,7 +4536,7 @@
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
     </row>
-    <row r="70" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -4539,7 +4547,7 @@
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
     </row>
-    <row r="71" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -4550,7 +4558,7 @@
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
     </row>
-    <row r="72" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -4561,7 +4569,7 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
     </row>
-    <row r="73" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -4572,7 +4580,7 @@
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
     </row>
-    <row r="74" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -4583,7 +4591,7 @@
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
     </row>
-    <row r="75" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -4594,7 +4602,7 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
     </row>
-    <row r="76" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -4605,7 +4613,7 @@
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
     </row>
-    <row r="77" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -4616,7 +4624,7 @@
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
     </row>
-    <row r="78" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -4627,7 +4635,7 @@
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
     </row>
-    <row r="79" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -4638,7 +4646,7 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
     </row>
-    <row r="80" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -4649,7 +4657,7 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
     </row>
-    <row r="81" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -4660,7 +4668,7 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
     </row>
-    <row r="82" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -4671,7 +4679,7 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
     </row>
-    <row r="83" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -4682,7 +4690,7 @@
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
     </row>
-    <row r="84" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -4693,7 +4701,7 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
     </row>
-    <row r="85" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -4704,7 +4712,7 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
     </row>
-    <row r="86" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -4715,7 +4723,7 @@
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
     </row>
-    <row r="87" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -4726,7 +4734,7 @@
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
     </row>
-    <row r="88" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -4737,7 +4745,7 @@
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
     </row>
-    <row r="89" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -4748,7 +4756,7 @@
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
     </row>
-    <row r="90" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -4759,7 +4767,7 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
     </row>
-    <row r="91" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -4770,7 +4778,7 @@
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
     </row>
-    <row r="92" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -4781,7 +4789,7 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
     </row>
-    <row r="93" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -4792,7 +4800,7 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
     </row>
-    <row r="94" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -4803,7 +4811,7 @@
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
     </row>
-    <row r="95" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -4814,7 +4822,7 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
     </row>
-    <row r="96" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -4825,7 +4833,7 @@
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
     </row>
-    <row r="97" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -4836,7 +4844,7 @@
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
     </row>
-    <row r="98" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -4847,7 +4855,7 @@
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
     </row>
-    <row r="99" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -4858,7 +4866,7 @@
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
     </row>
-    <row r="100" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -4869,7 +4877,7 @@
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
     </row>
-    <row r="101" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -4880,7 +4888,7 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
     </row>
-    <row r="102" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -4891,7 +4899,7 @@
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
     </row>
-    <row r="103" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -4902,7 +4910,7 @@
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
     </row>
-    <row r="104" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -4913,7 +4921,7 @@
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
     </row>
-    <row r="105" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -4924,7 +4932,7 @@
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
     </row>
-    <row r="106" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -4935,7 +4943,7 @@
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
     </row>
-    <row r="107" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -4946,7 +4954,7 @@
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
     </row>
-    <row r="108" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -4957,7 +4965,7 @@
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
     </row>
-    <row r="109" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -4968,7 +4976,7 @@
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
     </row>
-    <row r="110" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -4979,7 +4987,7 @@
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
     </row>
-    <row r="111" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -4990,7 +4998,7 @@
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
     </row>
-    <row r="112" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -5001,7 +5009,7 @@
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
     </row>
-    <row r="113" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -5012,7 +5020,7 @@
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
     </row>
-    <row r="114" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -5023,7 +5031,7 @@
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
     </row>
-    <row r="115" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -5034,7 +5042,7 @@
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
     </row>
-    <row r="116" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -5045,7 +5053,7 @@
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
     </row>
-    <row r="117" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -5056,7 +5064,7 @@
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
     </row>
-    <row r="118" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -5067,7 +5075,7 @@
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
     </row>
-    <row r="119" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -5078,7 +5086,7 @@
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
     </row>
-    <row r="120" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -5089,7 +5097,7 @@
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
     </row>
-    <row r="121" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -5100,7 +5108,7 @@
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
     </row>
-    <row r="122" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -5111,7 +5119,7 @@
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
     </row>
-    <row r="123" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -5122,7 +5130,7 @@
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
     </row>
-    <row r="124" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -5133,7 +5141,7 @@
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
     </row>
-    <row r="125" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -5144,7 +5152,7 @@
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
     </row>
-    <row r="126" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -5155,7 +5163,7 @@
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
     </row>
-    <row r="127" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -5166,7 +5174,7 @@
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
     </row>
-    <row r="128" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -5177,7 +5185,7 @@
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
     </row>
-    <row r="129" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -5188,7 +5196,7 @@
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
     </row>
-    <row r="130" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -5199,7 +5207,7 @@
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
     </row>
-    <row r="131" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -5210,7 +5218,7 @@
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
     </row>
-    <row r="132" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -5221,7 +5229,7 @@
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
     </row>
-    <row r="133" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -5232,7 +5240,7 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
     </row>
-    <row r="134" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -5243,7 +5251,7 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
     </row>
-    <row r="135" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -5254,7 +5262,7 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
     </row>
-    <row r="136" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -5265,7 +5273,7 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
     </row>
-    <row r="137" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -5276,7 +5284,7 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
     </row>
-    <row r="138" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -5287,7 +5295,7 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
     </row>
-    <row r="139" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -5298,7 +5306,7 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
     </row>
-    <row r="140" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -5309,7 +5317,7 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
     </row>
-    <row r="141" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -5320,7 +5328,7 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
     </row>
-    <row r="142" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -5331,7 +5339,7 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
     </row>
-    <row r="143" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -5342,7 +5350,7 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
     </row>
-    <row r="144" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -5353,7 +5361,7 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
     </row>
-    <row r="145" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -5364,7 +5372,7 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
     </row>
-    <row r="146" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -5375,7 +5383,7 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
     </row>
-    <row r="147" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -5386,7 +5394,7 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
     </row>
-    <row r="148" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -5397,7 +5405,7 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
     </row>
-    <row r="149" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -5408,7 +5416,7 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
     </row>
-    <row r="150" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -5419,7 +5427,7 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
     </row>
-    <row r="151" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -5430,7 +5438,7 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
     </row>
-    <row r="152" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -5441,7 +5449,7 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
     </row>
-    <row r="153" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -5452,7 +5460,7 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
     </row>
-    <row r="154" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -5463,7 +5471,7 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
     </row>
-    <row r="155" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -5474,7 +5482,7 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
     </row>
-    <row r="156" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -5485,7 +5493,7 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
     </row>
-    <row r="157" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -5496,7 +5504,7 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
     </row>
-    <row r="158" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -5507,7 +5515,7 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
     </row>
-    <row r="159" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -5518,7 +5526,7 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
     </row>
-    <row r="160" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -5529,7 +5537,7 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
     </row>
-    <row r="161" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -5540,7 +5548,7 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
     </row>
-    <row r="162" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -5551,7 +5559,7 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
     </row>
-    <row r="163" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -5562,7 +5570,7 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
     </row>
-    <row r="164" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -5573,7 +5581,7 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
     </row>
-    <row r="165" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -5584,7 +5592,7 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
     </row>
-    <row r="166" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -5595,7 +5603,7 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
     </row>
-    <row r="167" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -5606,7 +5614,7 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
     </row>
-    <row r="168" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -5617,7 +5625,7 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
     </row>
-    <row r="169" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -5628,7 +5636,7 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
     </row>
-    <row r="170" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -5639,7 +5647,7 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
     </row>
-    <row r="171" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -5650,7 +5658,7 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
     </row>
-    <row r="172" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -5661,7 +5669,7 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
     </row>
-    <row r="173" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -5672,7 +5680,7 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
     </row>
-    <row r="174" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -5683,7 +5691,7 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
     </row>
-    <row r="175" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -5694,7 +5702,7 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
     </row>
-    <row r="176" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -5705,7 +5713,7 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
     </row>
-    <row r="177" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -5716,7 +5724,7 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
     </row>
-    <row r="178" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -5727,7 +5735,7 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
     </row>
-    <row r="179" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -5738,7 +5746,7 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
     </row>
-    <row r="180" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -5749,7 +5757,7 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
     </row>
-    <row r="181" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -5760,7 +5768,7 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
     </row>
-    <row r="182" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -5771,7 +5779,7 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
     </row>
-    <row r="183" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -5782,7 +5790,7 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
     </row>
-    <row r="184" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -5793,7 +5801,7 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
     </row>
-    <row r="185" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -5804,7 +5812,7 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
     </row>
-    <row r="186" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -5815,7 +5823,7 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
     </row>
-    <row r="187" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -5826,7 +5834,7 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
     </row>
-    <row r="188" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -5837,7 +5845,7 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
     </row>
-    <row r="189" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -5848,7 +5856,7 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
     </row>
-    <row r="190" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -5859,7 +5867,7 @@
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
     </row>
-    <row r="191" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -5870,7 +5878,7 @@
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
     </row>
-    <row r="192" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -5881,7 +5889,7 @@
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
     </row>
-    <row r="193" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -5892,7 +5900,7 @@
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
     </row>
-    <row r="194" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -5903,7 +5911,7 @@
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
     </row>
-    <row r="195" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -5914,7 +5922,7 @@
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
     </row>
-    <row r="196" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -5925,7 +5933,7 @@
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
     </row>
-    <row r="197" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -5936,7 +5944,7 @@
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
     </row>
-    <row r="198" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -5947,7 +5955,7 @@
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
     </row>
-    <row r="199" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -5958,7 +5966,7 @@
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
     </row>
-    <row r="200" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -5969,7 +5977,7 @@
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
     </row>
-    <row r="201" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -5980,7 +5988,7 @@
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
     </row>
-    <row r="202" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -5991,7 +5999,7 @@
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
     </row>
-    <row r="203" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -6002,7 +6010,7 @@
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
     </row>
-    <row r="204" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -6013,7 +6021,7 @@
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
     </row>
-    <row r="205" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -6024,7 +6032,7 @@
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
     </row>
-    <row r="206" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -6035,7 +6043,7 @@
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
     </row>
-    <row r="207" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -6046,7 +6054,7 @@
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
     </row>
-    <row r="208" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -6057,7 +6065,7 @@
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
     </row>
-    <row r="209" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -6068,7 +6076,7 @@
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
     </row>
-    <row r="210" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -6079,7 +6087,7 @@
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
     </row>
-    <row r="211" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -6090,7 +6098,7 @@
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
     </row>
-    <row r="212" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -6101,7 +6109,7 @@
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
     </row>
-    <row r="213" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -6112,7 +6120,7 @@
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
     </row>
-    <row r="214" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -6123,7 +6131,7 @@
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
     </row>
-    <row r="215" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -6134,7 +6142,7 @@
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
     </row>
-    <row r="216" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -6145,7 +6153,7 @@
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
     </row>
-    <row r="217" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -6156,7 +6164,7 @@
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
     </row>
-    <row r="218" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -6167,7 +6175,7 @@
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
     </row>
-    <row r="219" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -6178,7 +6186,7 @@
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
     </row>
-    <row r="220" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -6189,7 +6197,7 @@
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
     </row>
-    <row r="221" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -6200,7 +6208,7 @@
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
     </row>
-    <row r="222" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -6211,7 +6219,7 @@
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
     </row>
-    <row r="223" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -6222,7 +6230,7 @@
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
     </row>
-    <row r="224" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -6233,7 +6241,7 @@
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
     </row>
-    <row r="225" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -6244,7 +6252,7 @@
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
     </row>
-    <row r="226" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -6255,7 +6263,7 @@
       <c r="J226" s="3"/>
       <c r="K226" s="3"/>
     </row>
-    <row r="227" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -6266,7 +6274,7 @@
       <c r="J227" s="3"/>
       <c r="K227" s="3"/>
     </row>
-    <row r="228" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -6277,7 +6285,7 @@
       <c r="J228" s="3"/>
       <c r="K228" s="3"/>
     </row>
-    <row r="229" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -6288,7 +6296,7 @@
       <c r="J229" s="3"/>
       <c r="K229" s="3"/>
     </row>
-    <row r="230" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -6299,7 +6307,7 @@
       <c r="J230" s="3"/>
       <c r="K230" s="3"/>
     </row>
-    <row r="231" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -6310,7 +6318,7 @@
       <c r="J231" s="3"/>
       <c r="K231" s="3"/>
     </row>
-    <row r="232" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -6321,7 +6329,7 @@
       <c r="J232" s="3"/>
       <c r="K232" s="3"/>
     </row>
-    <row r="233" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -6332,7 +6340,7 @@
       <c r="J233" s="3"/>
       <c r="K233" s="3"/>
     </row>
-    <row r="234" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -6343,7 +6351,7 @@
       <c r="J234" s="3"/>
       <c r="K234" s="3"/>
     </row>
-    <row r="235" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -6354,7 +6362,7 @@
       <c r="J235" s="3"/>
       <c r="K235" s="3"/>
     </row>
-    <row r="236" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -6365,7 +6373,7 @@
       <c r="J236" s="3"/>
       <c r="K236" s="3"/>
     </row>
-    <row r="237" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -6376,7 +6384,7 @@
       <c r="J237" s="3"/>
       <c r="K237" s="3"/>
     </row>
-    <row r="238" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -6387,7 +6395,7 @@
       <c r="J238" s="3"/>
       <c r="K238" s="3"/>
     </row>
-    <row r="239" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -6398,7 +6406,7 @@
       <c r="J239" s="3"/>
       <c r="K239" s="3"/>
     </row>
-    <row r="240" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -6409,7 +6417,7 @@
       <c r="J240" s="3"/>
       <c r="K240" s="3"/>
     </row>
-    <row r="241" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -6420,7 +6428,7 @@
       <c r="J241" s="3"/>
       <c r="K241" s="3"/>
     </row>
-    <row r="242" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -6431,7 +6439,7 @@
       <c r="J242" s="3"/>
       <c r="K242" s="3"/>
     </row>
-    <row r="243" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -6442,7 +6450,7 @@
       <c r="J243" s="3"/>
       <c r="K243" s="3"/>
     </row>
-    <row r="244" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -6453,7 +6461,7 @@
       <c r="J244" s="3"/>
       <c r="K244" s="3"/>
     </row>
-    <row r="245" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -6464,7 +6472,7 @@
       <c r="J245" s="3"/>
       <c r="K245" s="3"/>
     </row>
-    <row r="246" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -6475,7 +6483,7 @@
       <c r="J246" s="3"/>
       <c r="K246" s="3"/>
     </row>
-    <row r="247" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -6486,7 +6494,7 @@
       <c r="J247" s="3"/>
       <c r="K247" s="3"/>
     </row>
-    <row r="248" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -6497,7 +6505,7 @@
       <c r="J248" s="3"/>
       <c r="K248" s="3"/>
     </row>
-    <row r="249" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -6508,7 +6516,7 @@
       <c r="J249" s="3"/>
       <c r="K249" s="3"/>
     </row>
-    <row r="250" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -6519,7 +6527,7 @@
       <c r="J250" s="3"/>
       <c r="K250" s="3"/>
     </row>
-    <row r="251" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -6530,7 +6538,7 @@
       <c r="J251" s="3"/>
       <c r="K251" s="3"/>
     </row>
-    <row r="252" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -6541,7 +6549,7 @@
       <c r="J252" s="3"/>
       <c r="K252" s="3"/>
     </row>
-    <row r="253" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -6552,7 +6560,7 @@
       <c r="J253" s="3"/>
       <c r="K253" s="3"/>
     </row>
-    <row r="254" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -6563,7 +6571,7 @@
       <c r="J254" s="3"/>
       <c r="K254" s="3"/>
     </row>
-    <row r="255" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -6574,7 +6582,7 @@
       <c r="J255" s="3"/>
       <c r="K255" s="3"/>
     </row>
-    <row r="256" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -6585,7 +6593,7 @@
       <c r="J256" s="3"/>
       <c r="K256" s="3"/>
     </row>
-    <row r="257" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -6596,7 +6604,7 @@
       <c r="J257" s="3"/>
       <c r="K257" s="3"/>
     </row>
-    <row r="258" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -6607,7 +6615,7 @@
       <c r="J258" s="3"/>
       <c r="K258" s="3"/>
     </row>
-    <row r="259" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -6618,7 +6626,7 @@
       <c r="J259" s="3"/>
       <c r="K259" s="3"/>
     </row>
-    <row r="260" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -6629,7 +6637,7 @@
       <c r="J260" s="3"/>
       <c r="K260" s="3"/>
     </row>
-    <row r="261" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -6640,7 +6648,7 @@
       <c r="J261" s="3"/>
       <c r="K261" s="3"/>
     </row>
-    <row r="262" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -6651,7 +6659,7 @@
       <c r="J262" s="3"/>
       <c r="K262" s="3"/>
     </row>
-    <row r="263" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -6662,7 +6670,7 @@
       <c r="J263" s="3"/>
       <c r="K263" s="3"/>
     </row>
-    <row r="264" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -6673,7 +6681,7 @@
       <c r="J264" s="3"/>
       <c r="K264" s="3"/>
     </row>
-    <row r="265" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -6684,7 +6692,7 @@
       <c r="J265" s="3"/>
       <c r="K265" s="3"/>
     </row>
-    <row r="266" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -6695,7 +6703,7 @@
       <c r="J266" s="3"/>
       <c r="K266" s="3"/>
     </row>
-    <row r="267" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -6706,7 +6714,7 @@
       <c r="J267" s="3"/>
       <c r="K267" s="3"/>
     </row>
-    <row r="268" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -6717,7 +6725,7 @@
       <c r="J268" s="3"/>
       <c r="K268" s="3"/>
     </row>
-    <row r="269" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -6728,7 +6736,7 @@
       <c r="J269" s="3"/>
       <c r="K269" s="3"/>
     </row>
-    <row r="270" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -6739,7 +6747,7 @@
       <c r="J270" s="3"/>
       <c r="K270" s="3"/>
     </row>
-    <row r="271" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -6750,7 +6758,7 @@
       <c r="J271" s="3"/>
       <c r="K271" s="3"/>
     </row>
-    <row r="272" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -6761,7 +6769,7 @@
       <c r="J272" s="3"/>
       <c r="K272" s="3"/>
     </row>
-    <row r="273" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -6772,7 +6780,7 @@
       <c r="J273" s="3"/>
       <c r="K273" s="3"/>
     </row>
-    <row r="274" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -6783,7 +6791,7 @@
       <c r="J274" s="3"/>
       <c r="K274" s="3"/>
     </row>
-    <row r="275" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -6794,7 +6802,7 @@
       <c r="J275" s="3"/>
       <c r="K275" s="3"/>
     </row>
-    <row r="276" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -6805,7 +6813,7 @@
       <c r="J276" s="3"/>
       <c r="K276" s="3"/>
     </row>
-    <row r="277" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -6816,7 +6824,7 @@
       <c r="J277" s="3"/>
       <c r="K277" s="3"/>
     </row>
-    <row r="278" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -6827,7 +6835,7 @@
       <c r="J278" s="3"/>
       <c r="K278" s="3"/>
     </row>
-    <row r="279" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -6838,7 +6846,7 @@
       <c r="J279" s="3"/>
       <c r="K279" s="3"/>
     </row>
-    <row r="280" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -6849,7 +6857,7 @@
       <c r="J280" s="3"/>
       <c r="K280" s="3"/>
     </row>
-    <row r="281" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -6860,7 +6868,7 @@
       <c r="J281" s="3"/>
       <c r="K281" s="3"/>
     </row>
-    <row r="282" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -6871,7 +6879,7 @@
       <c r="J282" s="3"/>
       <c r="K282" s="3"/>
     </row>
-    <row r="283" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -6882,7 +6890,7 @@
       <c r="J283" s="3"/>
       <c r="K283" s="3"/>
     </row>
-    <row r="284" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -6893,7 +6901,7 @@
       <c r="J284" s="3"/>
       <c r="K284" s="3"/>
     </row>
-    <row r="285" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -6904,7 +6912,7 @@
       <c r="J285" s="3"/>
       <c r="K285" s="3"/>
     </row>
-    <row r="286" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -6915,7 +6923,7 @@
       <c r="J286" s="3"/>
       <c r="K286" s="3"/>
     </row>
-    <row r="287" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -6926,7 +6934,7 @@
       <c r="J287" s="3"/>
       <c r="K287" s="3"/>
     </row>
-    <row r="288" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -6937,7 +6945,7 @@
       <c r="J288" s="3"/>
       <c r="K288" s="3"/>
     </row>
-    <row r="289" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -6948,7 +6956,7 @@
       <c r="J289" s="3"/>
       <c r="K289" s="3"/>
     </row>
-    <row r="290" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -6959,7 +6967,7 @@
       <c r="J290" s="3"/>
       <c r="K290" s="3"/>
     </row>
-    <row r="291" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -6970,7 +6978,7 @@
       <c r="J291" s="3"/>
       <c r="K291" s="3"/>
     </row>
-    <row r="292" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -6981,7 +6989,7 @@
       <c r="J292" s="3"/>
       <c r="K292" s="3"/>
     </row>
-    <row r="293" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -6992,7 +7000,7 @@
       <c r="J293" s="3"/>
       <c r="K293" s="3"/>
     </row>
-    <row r="294" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -7003,7 +7011,7 @@
       <c r="J294" s="3"/>
       <c r="K294" s="3"/>
     </row>
-    <row r="295" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -7014,7 +7022,7 @@
       <c r="J295" s="3"/>
       <c r="K295" s="3"/>
     </row>
-    <row r="296" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -7025,7 +7033,7 @@
       <c r="J296" s="3"/>
       <c r="K296" s="3"/>
     </row>
-    <row r="297" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -7036,7 +7044,7 @@
       <c r="J297" s="3"/>
       <c r="K297" s="3"/>
     </row>
-    <row r="298" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -7047,7 +7055,7 @@
       <c r="J298" s="3"/>
       <c r="K298" s="3"/>
     </row>
-    <row r="299" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -7058,7 +7066,7 @@
       <c r="J299" s="3"/>
       <c r="K299" s="3"/>
     </row>
-    <row r="300" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -7069,7 +7077,7 @@
       <c r="J300" s="3"/>
       <c r="K300" s="3"/>
     </row>
-    <row r="301" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -7080,7 +7088,7 @@
       <c r="J301" s="3"/>
       <c r="K301" s="3"/>
     </row>
-    <row r="302" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -7091,7 +7099,7 @@
       <c r="J302" s="3"/>
       <c r="K302" s="3"/>
     </row>
-    <row r="303" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -7102,7 +7110,7 @@
       <c r="J303" s="3"/>
       <c r="K303" s="3"/>
     </row>
-    <row r="304" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -7113,7 +7121,7 @@
       <c r="J304" s="3"/>
       <c r="K304" s="3"/>
     </row>
-    <row r="305" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -7124,7 +7132,7 @@
       <c r="J305" s="3"/>
       <c r="K305" s="3"/>
     </row>
-    <row r="306" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -7135,7 +7143,7 @@
       <c r="J306" s="3"/>
       <c r="K306" s="3"/>
     </row>
-    <row r="307" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -7146,7 +7154,7 @@
       <c r="J307" s="3"/>
       <c r="K307" s="3"/>
     </row>
-    <row r="308" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -7157,7 +7165,7 @@
       <c r="J308" s="3"/>
       <c r="K308" s="3"/>
     </row>
-    <row r="309" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -7168,7 +7176,7 @@
       <c r="J309" s="3"/>
       <c r="K309" s="3"/>
     </row>
-    <row r="310" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -7179,7 +7187,7 @@
       <c r="J310" s="3"/>
       <c r="K310" s="3"/>
     </row>
-    <row r="311" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -7190,7 +7198,7 @@
       <c r="J311" s="3"/>
       <c r="K311" s="3"/>
     </row>
-    <row r="312" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -7201,7 +7209,7 @@
       <c r="J312" s="3"/>
       <c r="K312" s="3"/>
     </row>
-    <row r="313" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -7212,7 +7220,7 @@
       <c r="J313" s="3"/>
       <c r="K313" s="3"/>
     </row>
-    <row r="314" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -7223,7 +7231,7 @@
       <c r="J314" s="3"/>
       <c r="K314" s="3"/>
     </row>
-    <row r="315" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -7234,7 +7242,7 @@
       <c r="J315" s="3"/>
       <c r="K315" s="3"/>
     </row>
-    <row r="316" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -7245,7 +7253,7 @@
       <c r="J316" s="3"/>
       <c r="K316" s="3"/>
     </row>
-    <row r="317" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -7256,7 +7264,7 @@
       <c r="J317" s="3"/>
       <c r="K317" s="3"/>
     </row>
-    <row r="318" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -7267,7 +7275,7 @@
       <c r="J318" s="3"/>
       <c r="K318" s="3"/>
     </row>
-    <row r="319" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -7278,7 +7286,7 @@
       <c r="J319" s="3"/>
       <c r="K319" s="3"/>
     </row>
-    <row r="320" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -7289,7 +7297,7 @@
       <c r="J320" s="3"/>
       <c r="K320" s="3"/>
     </row>
-    <row r="321" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -7300,7 +7308,7 @@
       <c r="J321" s="3"/>
       <c r="K321" s="3"/>
     </row>
-    <row r="322" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -7311,7 +7319,7 @@
       <c r="J322" s="3"/>
       <c r="K322" s="3"/>
     </row>
-    <row r="323" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -7322,7 +7330,7 @@
       <c r="J323" s="3"/>
       <c r="K323" s="3"/>
     </row>
-    <row r="324" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -7333,7 +7341,7 @@
       <c r="J324" s="3"/>
       <c r="K324" s="3"/>
     </row>
-    <row r="325" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -7344,7 +7352,7 @@
       <c r="J325" s="3"/>
       <c r="K325" s="3"/>
     </row>
-    <row r="326" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -7355,7 +7363,7 @@
       <c r="J326" s="3"/>
       <c r="K326" s="3"/>
     </row>
-    <row r="327" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -7366,7 +7374,7 @@
       <c r="J327" s="3"/>
       <c r="K327" s="3"/>
     </row>
-    <row r="328" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -7377,7 +7385,7 @@
       <c r="J328" s="3"/>
       <c r="K328" s="3"/>
     </row>
-    <row r="329" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -7388,7 +7396,7 @@
       <c r="J329" s="3"/>
       <c r="K329" s="3"/>
     </row>
-    <row r="330" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -7399,7 +7407,7 @@
       <c r="J330" s="3"/>
       <c r="K330" s="3"/>
     </row>
-    <row r="331" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -7410,7 +7418,7 @@
       <c r="J331" s="3"/>
       <c r="K331" s="3"/>
     </row>
-    <row r="332" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -7421,7 +7429,7 @@
       <c r="J332" s="3"/>
       <c r="K332" s="3"/>
     </row>
-    <row r="333" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -7432,7 +7440,7 @@
       <c r="J333" s="3"/>
       <c r="K333" s="3"/>
     </row>
-    <row r="334" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -7443,7 +7451,7 @@
       <c r="J334" s="3"/>
       <c r="K334" s="3"/>
     </row>
-    <row r="335" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -7454,7 +7462,7 @@
       <c r="J335" s="3"/>
       <c r="K335" s="3"/>
     </row>
-    <row r="336" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -7465,7 +7473,7 @@
       <c r="J336" s="3"/>
       <c r="K336" s="3"/>
     </row>
-    <row r="337" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -7476,7 +7484,7 @@
       <c r="J337" s="3"/>
       <c r="K337" s="3"/>
     </row>
-    <row r="338" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -7487,7 +7495,7 @@
       <c r="J338" s="3"/>
       <c r="K338" s="3"/>
     </row>
-    <row r="339" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -7498,7 +7506,7 @@
       <c r="J339" s="3"/>
       <c r="K339" s="3"/>
     </row>
-    <row r="340" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -7509,7 +7517,7 @@
       <c r="J340" s="3"/>
       <c r="K340" s="3"/>
     </row>
-    <row r="341" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -7520,7 +7528,7 @@
       <c r="J341" s="3"/>
       <c r="K341" s="3"/>
     </row>
-    <row r="342" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -7531,7 +7539,7 @@
       <c r="J342" s="3"/>
       <c r="K342" s="3"/>
     </row>
-    <row r="343" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -7542,7 +7550,7 @@
       <c r="J343" s="3"/>
       <c r="K343" s="3"/>
     </row>
-    <row r="344" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -7553,7 +7561,7 @@
       <c r="J344" s="3"/>
       <c r="K344" s="3"/>
     </row>
-    <row r="345" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -7564,7 +7572,7 @@
       <c r="J345" s="3"/>
       <c r="K345" s="3"/>
     </row>
-    <row r="346" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -7575,7 +7583,7 @@
       <c r="J346" s="3"/>
       <c r="K346" s="3"/>
     </row>
-    <row r="347" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
@@ -7586,7 +7594,7 @@
       <c r="J347" s="3"/>
       <c r="K347" s="3"/>
     </row>
-    <row r="348" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
@@ -7597,7 +7605,7 @@
       <c r="J348" s="3"/>
       <c r="K348" s="3"/>
     </row>
-    <row r="349" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="3"/>
@@ -7608,7 +7616,7 @@
       <c r="J349" s="3"/>
       <c r="K349" s="3"/>
     </row>
-    <row r="350" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
       <c r="E350" s="3"/>
@@ -7619,7 +7627,7 @@
       <c r="J350" s="3"/>
       <c r="K350" s="3"/>
     </row>
-    <row r="351" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C351" s="3"/>
       <c r="D351" s="3"/>
       <c r="E351" s="3"/>
@@ -7630,7 +7638,7 @@
       <c r="J351" s="3"/>
       <c r="K351" s="3"/>
     </row>
-    <row r="352" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C352" s="3"/>
       <c r="D352" s="3"/>
       <c r="E352" s="3"/>
@@ -7641,7 +7649,7 @@
       <c r="J352" s="3"/>
       <c r="K352" s="3"/>
     </row>
-    <row r="353" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C353" s="3"/>
       <c r="D353" s="3"/>
       <c r="E353" s="3"/>
@@ -7652,7 +7660,7 @@
       <c r="J353" s="3"/>
       <c r="K353" s="3"/>
     </row>
-    <row r="354" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C354" s="3"/>
       <c r="D354" s="3"/>
       <c r="E354" s="3"/>
@@ -7663,7 +7671,7 @@
       <c r="J354" s="3"/>
       <c r="K354" s="3"/>
     </row>
-    <row r="355" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C355" s="3"/>
       <c r="D355" s="3"/>
       <c r="E355" s="3"/>
@@ -7674,7 +7682,7 @@
       <c r="J355" s="3"/>
       <c r="K355" s="3"/>
     </row>
-    <row r="356" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="3"/>
@@ -7685,7 +7693,7 @@
       <c r="J356" s="3"/>
       <c r="K356" s="3"/>
     </row>
-    <row r="357" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
       <c r="E357" s="3"/>
@@ -7696,7 +7704,7 @@
       <c r="J357" s="3"/>
       <c r="K357" s="3"/>
     </row>
-    <row r="358" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
       <c r="E358" s="3"/>
@@ -7707,7 +7715,7 @@
       <c r="J358" s="3"/>
       <c r="K358" s="3"/>
     </row>
-    <row r="359" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
       <c r="E359" s="3"/>
@@ -7718,7 +7726,7 @@
       <c r="J359" s="3"/>
       <c r="K359" s="3"/>
     </row>
-    <row r="360" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C360" s="3"/>
       <c r="D360" s="3"/>
       <c r="E360" s="3"/>
@@ -7729,7 +7737,7 @@
       <c r="J360" s="3"/>
       <c r="K360" s="3"/>
     </row>
-    <row r="361" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C361" s="3"/>
       <c r="D361" s="3"/>
       <c r="E361" s="3"/>
@@ -7740,7 +7748,7 @@
       <c r="J361" s="3"/>
       <c r="K361" s="3"/>
     </row>
-    <row r="362" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
       <c r="E362" s="3"/>
@@ -7751,7 +7759,7 @@
       <c r="J362" s="3"/>
       <c r="K362" s="3"/>
     </row>
-    <row r="363" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C363" s="3"/>
       <c r="D363" s="3"/>
       <c r="E363" s="3"/>
@@ -7762,7 +7770,7 @@
       <c r="J363" s="3"/>
       <c r="K363" s="3"/>
     </row>
-    <row r="364" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C364" s="3"/>
       <c r="D364" s="3"/>
       <c r="E364" s="3"/>
@@ -7773,7 +7781,7 @@
       <c r="J364" s="3"/>
       <c r="K364" s="3"/>
     </row>
-    <row r="365" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C365" s="3"/>
       <c r="D365" s="3"/>
       <c r="E365" s="3"/>
@@ -7784,7 +7792,7 @@
       <c r="J365" s="3"/>
       <c r="K365" s="3"/>
     </row>
-    <row r="366" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C366" s="3"/>
       <c r="D366" s="3"/>
       <c r="E366" s="3"/>
@@ -7795,7 +7803,7 @@
       <c r="J366" s="3"/>
       <c r="K366" s="3"/>
     </row>
-    <row r="367" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C367" s="3"/>
       <c r="D367" s="3"/>
       <c r="E367" s="3"/>
@@ -7806,7 +7814,7 @@
       <c r="J367" s="3"/>
       <c r="K367" s="3"/>
     </row>
-    <row r="368" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
       <c r="E368" s="3"/>
@@ -7817,7 +7825,7 @@
       <c r="J368" s="3"/>
       <c r="K368" s="3"/>
     </row>
-    <row r="369" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C369" s="3"/>
       <c r="D369" s="3"/>
       <c r="E369" s="3"/>
@@ -7828,7 +7836,7 @@
       <c r="J369" s="3"/>
       <c r="K369" s="3"/>
     </row>
-    <row r="370" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C370" s="3"/>
       <c r="D370" s="3"/>
       <c r="E370" s="3"/>
@@ -7839,7 +7847,7 @@
       <c r="J370" s="3"/>
       <c r="K370" s="3"/>
     </row>
-    <row r="371" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C371" s="3"/>
       <c r="D371" s="3"/>
       <c r="E371" s="3"/>
@@ -7850,7 +7858,7 @@
       <c r="J371" s="3"/>
       <c r="K371" s="3"/>
     </row>
-    <row r="372" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
       <c r="E372" s="3"/>
@@ -7861,7 +7869,7 @@
       <c r="J372" s="3"/>
       <c r="K372" s="3"/>
     </row>
-    <row r="373" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C373" s="3"/>
       <c r="D373" s="3"/>
       <c r="E373" s="3"/>
@@ -7872,7 +7880,7 @@
       <c r="J373" s="3"/>
       <c r="K373" s="3"/>
     </row>
-    <row r="374" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C374" s="3"/>
       <c r="D374" s="3"/>
       <c r="E374" s="3"/>
@@ -7883,7 +7891,7 @@
       <c r="J374" s="3"/>
       <c r="K374" s="3"/>
     </row>
-    <row r="375" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C375" s="3"/>
       <c r="D375" s="3"/>
       <c r="E375" s="3"/>
@@ -7894,7 +7902,7 @@
       <c r="J375" s="3"/>
       <c r="K375" s="3"/>
     </row>
-    <row r="376" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
       <c r="E376" s="3"/>
@@ -7905,7 +7913,7 @@
       <c r="J376" s="3"/>
       <c r="K376" s="3"/>
     </row>
-    <row r="377" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
       <c r="E377" s="3"/>
@@ -7916,7 +7924,7 @@
       <c r="J377" s="3"/>
       <c r="K377" s="3"/>
     </row>
-    <row r="378" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
       <c r="E378" s="3"/>
@@ -7927,7 +7935,7 @@
       <c r="J378" s="3"/>
       <c r="K378" s="3"/>
     </row>
-    <row r="379" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="3"/>
@@ -7938,7 +7946,7 @@
       <c r="J379" s="3"/>
       <c r="K379" s="3"/>
     </row>
-    <row r="380" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="3"/>
@@ -7949,7 +7957,7 @@
       <c r="J380" s="3"/>
       <c r="K380" s="3"/>
     </row>
-    <row r="381" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="3"/>
@@ -7960,7 +7968,7 @@
       <c r="J381" s="3"/>
       <c r="K381" s="3"/>
     </row>
-    <row r="382" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
       <c r="E382" s="3"/>
@@ -7971,7 +7979,7 @@
       <c r="J382" s="3"/>
       <c r="K382" s="3"/>
     </row>
-    <row r="383" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
       <c r="E383" s="3"/>
@@ -7982,7 +7990,7 @@
       <c r="J383" s="3"/>
       <c r="K383" s="3"/>
     </row>
-    <row r="384" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
       <c r="E384" s="3"/>
@@ -7993,7 +8001,7 @@
       <c r="J384" s="3"/>
       <c r="K384" s="3"/>
     </row>
-    <row r="385" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
       <c r="E385" s="3"/>
@@ -8004,7 +8012,7 @@
       <c r="J385" s="3"/>
       <c r="K385" s="3"/>
     </row>
-    <row r="386" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
       <c r="E386" s="3"/>
@@ -8015,7 +8023,7 @@
       <c r="J386" s="3"/>
       <c r="K386" s="3"/>
     </row>
-    <row r="387" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="3"/>
@@ -8026,7 +8034,7 @@
       <c r="J387" s="3"/>
       <c r="K387" s="3"/>
     </row>
-    <row r="388" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="3"/>
@@ -8037,7 +8045,7 @@
       <c r="J388" s="3"/>
       <c r="K388" s="3"/>
     </row>
-    <row r="389" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
       <c r="E389" s="3"/>
@@ -8048,7 +8056,7 @@
       <c r="J389" s="3"/>
       <c r="K389" s="3"/>
     </row>
-    <row r="390" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
       <c r="E390" s="3"/>
@@ -8059,7 +8067,7 @@
       <c r="J390" s="3"/>
       <c r="K390" s="3"/>
     </row>
-    <row r="391" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
       <c r="E391" s="3"/>
@@ -8070,7 +8078,7 @@
       <c r="J391" s="3"/>
       <c r="K391" s="3"/>
     </row>
-    <row r="392" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
       <c r="E392" s="3"/>
@@ -8081,7 +8089,7 @@
       <c r="J392" s="3"/>
       <c r="K392" s="3"/>
     </row>
-    <row r="393" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
       <c r="E393" s="3"/>
@@ -8092,7 +8100,7 @@
       <c r="J393" s="3"/>
       <c r="K393" s="3"/>
     </row>
-    <row r="394" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
       <c r="E394" s="3"/>
@@ -8103,7 +8111,7 @@
       <c r="J394" s="3"/>
       <c r="K394" s="3"/>
     </row>
-    <row r="395" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
       <c r="E395" s="3"/>
@@ -8114,7 +8122,7 @@
       <c r="J395" s="3"/>
       <c r="K395" s="3"/>
     </row>
-    <row r="396" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
       <c r="E396" s="3"/>
@@ -8125,7 +8133,7 @@
       <c r="J396" s="3"/>
       <c r="K396" s="3"/>
     </row>
-    <row r="397" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
       <c r="E397" s="3"/>
@@ -8136,7 +8144,7 @@
       <c r="J397" s="3"/>
       <c r="K397" s="3"/>
     </row>
-    <row r="398" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
       <c r="E398" s="3"/>
@@ -8147,7 +8155,7 @@
       <c r="J398" s="3"/>
       <c r="K398" s="3"/>
     </row>
-    <row r="399" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
       <c r="E399" s="3"/>
@@ -8158,7 +8166,7 @@
       <c r="J399" s="3"/>
       <c r="K399" s="3"/>
     </row>
-    <row r="400" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
       <c r="E400" s="3"/>
@@ -8169,7 +8177,7 @@
       <c r="J400" s="3"/>
       <c r="K400" s="3"/>
     </row>
-    <row r="401" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
       <c r="E401" s="3"/>
@@ -8180,7 +8188,7 @@
       <c r="J401" s="3"/>
       <c r="K401" s="3"/>
     </row>
-    <row r="402" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C402" s="3"/>
       <c r="D402" s="3"/>
       <c r="E402" s="3"/>
@@ -8191,7 +8199,7 @@
       <c r="J402" s="3"/>
       <c r="K402" s="3"/>
     </row>
-    <row r="403" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C403" s="3"/>
       <c r="D403" s="3"/>
       <c r="E403" s="3"/>
@@ -8202,7 +8210,7 @@
       <c r="J403" s="3"/>
       <c r="K403" s="3"/>
     </row>
-    <row r="404" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C404" s="3"/>
       <c r="D404" s="3"/>
       <c r="E404" s="3"/>
@@ -8213,7 +8221,7 @@
       <c r="J404" s="3"/>
       <c r="K404" s="3"/>
     </row>
-    <row r="405" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C405" s="3"/>
       <c r="D405" s="3"/>
       <c r="E405" s="3"/>
@@ -8224,7 +8232,7 @@
       <c r="J405" s="3"/>
       <c r="K405" s="3"/>
     </row>
-    <row r="406" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C406" s="3"/>
       <c r="D406" s="3"/>
       <c r="E406" s="3"/>
@@ -8235,7 +8243,7 @@
       <c r="J406" s="3"/>
       <c r="K406" s="3"/>
     </row>
-    <row r="407" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C407" s="3"/>
       <c r="D407" s="3"/>
       <c r="E407" s="3"/>
@@ -8246,7 +8254,7 @@
       <c r="J407" s="3"/>
       <c r="K407" s="3"/>
     </row>
-    <row r="408" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C408" s="3"/>
       <c r="D408" s="3"/>
       <c r="E408" s="3"/>
@@ -8257,7 +8265,7 @@
       <c r="J408" s="3"/>
       <c r="K408" s="3"/>
     </row>
-    <row r="409" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C409" s="3"/>
       <c r="D409" s="3"/>
       <c r="E409" s="3"/>
@@ -8268,7 +8276,7 @@
       <c r="J409" s="3"/>
       <c r="K409" s="3"/>
     </row>
-    <row r="410" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C410" s="3"/>
       <c r="D410" s="3"/>
       <c r="E410" s="3"/>
@@ -8279,7 +8287,7 @@
       <c r="J410" s="3"/>
       <c r="K410" s="3"/>
     </row>
-    <row r="411" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C411" s="3"/>
       <c r="D411" s="3"/>
       <c r="E411" s="3"/>
@@ -8290,7 +8298,7 @@
       <c r="J411" s="3"/>
       <c r="K411" s="3"/>
     </row>
-    <row r="412" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C412" s="3"/>
       <c r="D412" s="3"/>
       <c r="E412" s="3"/>
@@ -8301,7 +8309,7 @@
       <c r="J412" s="3"/>
       <c r="K412" s="3"/>
     </row>
-    <row r="413" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C413" s="3"/>
       <c r="D413" s="3"/>
       <c r="E413" s="3"/>
@@ -8312,7 +8320,7 @@
       <c r="J413" s="3"/>
       <c r="K413" s="3"/>
     </row>
-    <row r="414" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C414" s="3"/>
       <c r="D414" s="3"/>
       <c r="E414" s="3"/>
@@ -8323,7 +8331,7 @@
       <c r="J414" s="3"/>
       <c r="K414" s="3"/>
     </row>
-    <row r="415" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C415" s="3"/>
       <c r="D415" s="3"/>
       <c r="E415" s="3"/>
@@ -8334,7 +8342,7 @@
       <c r="J415" s="3"/>
       <c r="K415" s="3"/>
     </row>
-    <row r="416" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C416" s="3"/>
       <c r="D416" s="3"/>
       <c r="E416" s="3"/>
@@ -8345,7 +8353,7 @@
       <c r="J416" s="3"/>
       <c r="K416" s="3"/>
     </row>
-    <row r="417" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C417" s="3"/>
       <c r="D417" s="3"/>
       <c r="E417" s="3"/>
@@ -8356,7 +8364,7 @@
       <c r="J417" s="3"/>
       <c r="K417" s="3"/>
     </row>
-    <row r="418" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C418" s="3"/>
       <c r="D418" s="3"/>
       <c r="E418" s="3"/>
@@ -8367,7 +8375,7 @@
       <c r="J418" s="3"/>
       <c r="K418" s="3"/>
     </row>
-    <row r="419" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C419" s="3"/>
       <c r="D419" s="3"/>
       <c r="E419" s="3"/>
@@ -8378,7 +8386,7 @@
       <c r="J419" s="3"/>
       <c r="K419" s="3"/>
     </row>
-    <row r="420" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C420" s="3"/>
       <c r="D420" s="3"/>
       <c r="E420" s="3"/>
@@ -8389,7 +8397,7 @@
       <c r="J420" s="3"/>
       <c r="K420" s="3"/>
     </row>
-    <row r="421" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C421" s="3"/>
       <c r="D421" s="3"/>
       <c r="E421" s="3"/>
@@ -8400,7 +8408,7 @@
       <c r="J421" s="3"/>
       <c r="K421" s="3"/>
     </row>
-    <row r="422" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C422" s="3"/>
       <c r="D422" s="3"/>
       <c r="E422" s="3"/>
@@ -8411,7 +8419,7 @@
       <c r="J422" s="3"/>
       <c r="K422" s="3"/>
     </row>
-    <row r="423" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C423" s="3"/>
       <c r="D423" s="3"/>
       <c r="E423" s="3"/>
@@ -8422,7 +8430,7 @@
       <c r="J423" s="3"/>
       <c r="K423" s="3"/>
     </row>
-    <row r="424" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C424" s="3"/>
       <c r="D424" s="3"/>
       <c r="E424" s="3"/>
@@ -8433,7 +8441,7 @@
       <c r="J424" s="3"/>
       <c r="K424" s="3"/>
     </row>
-    <row r="425" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C425" s="3"/>
       <c r="D425" s="3"/>
       <c r="E425" s="3"/>
@@ -8444,7 +8452,7 @@
       <c r="J425" s="3"/>
       <c r="K425" s="3"/>
     </row>
-    <row r="426" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C426" s="3"/>
       <c r="D426" s="3"/>
       <c r="E426" s="3"/>
@@ -8455,7 +8463,7 @@
       <c r="J426" s="3"/>
       <c r="K426" s="3"/>
     </row>
-    <row r="427" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C427" s="3"/>
       <c r="D427" s="3"/>
       <c r="E427" s="3"/>
@@ -8466,7 +8474,7 @@
       <c r="J427" s="3"/>
       <c r="K427" s="3"/>
     </row>
-    <row r="428" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C428" s="3"/>
       <c r="D428" s="3"/>
       <c r="E428" s="3"/>
@@ -8477,7 +8485,7 @@
       <c r="J428" s="3"/>
       <c r="K428" s="3"/>
     </row>
-    <row r="429" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C429" s="3"/>
       <c r="D429" s="3"/>
       <c r="E429" s="3"/>
@@ -8488,7 +8496,7 @@
       <c r="J429" s="3"/>
       <c r="K429" s="3"/>
     </row>
-    <row r="430" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C430" s="3"/>
       <c r="D430" s="3"/>
       <c r="E430" s="3"/>
@@ -8499,7 +8507,7 @@
       <c r="J430" s="3"/>
       <c r="K430" s="3"/>
     </row>
-    <row r="431" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C431" s="3"/>
       <c r="D431" s="3"/>
       <c r="E431" s="3"/>
@@ -8510,7 +8518,7 @@
       <c r="J431" s="3"/>
       <c r="K431" s="3"/>
     </row>
-    <row r="432" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C432" s="3"/>
       <c r="D432" s="3"/>
       <c r="E432" s="3"/>
@@ -8521,7 +8529,7 @@
       <c r="J432" s="3"/>
       <c r="K432" s="3"/>
     </row>
-    <row r="433" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C433" s="3"/>
       <c r="D433" s="3"/>
       <c r="E433" s="3"/>
@@ -8532,7 +8540,7 @@
       <c r="J433" s="3"/>
       <c r="K433" s="3"/>
     </row>
-    <row r="434" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C434" s="3"/>
       <c r="D434" s="3"/>
       <c r="E434" s="3"/>
@@ -8543,7 +8551,7 @@
       <c r="J434" s="3"/>
       <c r="K434" s="3"/>
     </row>
-    <row r="435" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C435" s="3"/>
       <c r="D435" s="3"/>
       <c r="E435" s="3"/>
@@ -8554,7 +8562,7 @@
       <c r="J435" s="3"/>
       <c r="K435" s="3"/>
     </row>
-    <row r="436" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C436" s="3"/>
       <c r="D436" s="3"/>
       <c r="E436" s="3"/>
@@ -8565,7 +8573,7 @@
       <c r="J436" s="3"/>
       <c r="K436" s="3"/>
     </row>
-    <row r="437" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C437" s="3"/>
       <c r="D437" s="3"/>
       <c r="E437" s="3"/>
@@ -8576,7 +8584,7 @@
       <c r="J437" s="3"/>
       <c r="K437" s="3"/>
     </row>
-    <row r="438" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C438" s="3"/>
       <c r="D438" s="3"/>
       <c r="E438" s="3"/>
@@ -8587,7 +8595,7 @@
       <c r="J438" s="3"/>
       <c r="K438" s="3"/>
     </row>
-    <row r="439" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C439" s="3"/>
       <c r="D439" s="3"/>
       <c r="E439" s="3"/>
@@ -8598,7 +8606,7 @@
       <c r="J439" s="3"/>
       <c r="K439" s="3"/>
     </row>
-    <row r="440" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C440" s="3"/>
       <c r="D440" s="3"/>
       <c r="E440" s="3"/>
@@ -8609,7 +8617,7 @@
       <c r="J440" s="3"/>
       <c r="K440" s="3"/>
     </row>
-    <row r="441" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C441" s="3"/>
       <c r="D441" s="3"/>
       <c r="E441" s="3"/>
@@ -8620,7 +8628,7 @@
       <c r="J441" s="3"/>
       <c r="K441" s="3"/>
     </row>
-    <row r="442" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C442" s="3"/>
       <c r="D442" s="3"/>
       <c r="E442" s="3"/>
@@ -8631,7 +8639,7 @@
       <c r="J442" s="3"/>
       <c r="K442" s="3"/>
     </row>
-    <row r="443" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C443" s="3"/>
       <c r="D443" s="3"/>
       <c r="E443" s="3"/>
@@ -8642,7 +8650,7 @@
       <c r="J443" s="3"/>
       <c r="K443" s="3"/>
     </row>
-    <row r="444" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C444" s="3"/>
       <c r="D444" s="3"/>
       <c r="E444" s="3"/>
@@ -8653,7 +8661,7 @@
       <c r="J444" s="3"/>
       <c r="K444" s="3"/>
     </row>
-    <row r="445" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C445" s="3"/>
       <c r="D445" s="3"/>
       <c r="E445" s="3"/>
@@ -8664,7 +8672,7 @@
       <c r="J445" s="3"/>
       <c r="K445" s="3"/>
     </row>
-    <row r="446" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C446" s="3"/>
       <c r="D446" s="3"/>
       <c r="E446" s="3"/>
@@ -8675,7 +8683,7 @@
       <c r="J446" s="3"/>
       <c r="K446" s="3"/>
     </row>
-    <row r="447" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C447" s="3"/>
       <c r="D447" s="3"/>
       <c r="E447" s="3"/>
@@ -8686,7 +8694,7 @@
       <c r="J447" s="3"/>
       <c r="K447" s="3"/>
     </row>
-    <row r="448" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C448" s="3"/>
       <c r="D448" s="3"/>
       <c r="E448" s="3"/>
@@ -8697,7 +8705,7 @@
       <c r="J448" s="3"/>
       <c r="K448" s="3"/>
     </row>
-    <row r="449" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C449" s="3"/>
       <c r="D449" s="3"/>
       <c r="E449" s="3"/>
@@ -8708,7 +8716,7 @@
       <c r="J449" s="3"/>
       <c r="K449" s="3"/>
     </row>
-    <row r="450" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C450" s="3"/>
       <c r="D450" s="3"/>
       <c r="E450" s="3"/>
@@ -8719,7 +8727,7 @@
       <c r="J450" s="3"/>
       <c r="K450" s="3"/>
     </row>
-    <row r="451" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C451" s="3"/>
       <c r="D451" s="3"/>
       <c r="E451" s="3"/>
@@ -8730,7 +8738,7 @@
       <c r="J451" s="3"/>
       <c r="K451" s="3"/>
     </row>
-    <row r="452" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C452" s="3"/>
       <c r="D452" s="3"/>
       <c r="E452" s="3"/>
@@ -8741,7 +8749,7 @@
       <c r="J452" s="3"/>
       <c r="K452" s="3"/>
     </row>
-    <row r="453" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C453" s="3"/>
       <c r="D453" s="3"/>
       <c r="E453" s="3"/>
@@ -8752,7 +8760,7 @@
       <c r="J453" s="3"/>
       <c r="K453" s="3"/>
     </row>
-    <row r="454" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C454" s="3"/>
       <c r="D454" s="3"/>
       <c r="E454" s="3"/>
@@ -8763,7 +8771,7 @@
       <c r="J454" s="3"/>
       <c r="K454" s="3"/>
     </row>
-    <row r="455" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C455" s="3"/>
       <c r="D455" s="3"/>
       <c r="E455" s="3"/>
@@ -8774,7 +8782,7 @@
       <c r="J455" s="3"/>
       <c r="K455" s="3"/>
     </row>
-    <row r="456" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C456" s="3"/>
       <c r="D456" s="3"/>
       <c r="E456" s="3"/>
@@ -8785,7 +8793,7 @@
       <c r="J456" s="3"/>
       <c r="K456" s="3"/>
     </row>
-    <row r="457" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C457" s="3"/>
       <c r="D457" s="3"/>
       <c r="E457" s="3"/>
@@ -8796,7 +8804,7 @@
       <c r="J457" s="3"/>
       <c r="K457" s="3"/>
     </row>
-    <row r="458" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C458" s="3"/>
       <c r="D458" s="3"/>
       <c r="E458" s="3"/>
@@ -8807,7 +8815,7 @@
       <c r="J458" s="3"/>
       <c r="K458" s="3"/>
     </row>
-    <row r="459" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C459" s="3"/>
       <c r="D459" s="3"/>
       <c r="E459" s="3"/>
@@ -8818,7 +8826,7 @@
       <c r="J459" s="3"/>
       <c r="K459" s="3"/>
     </row>
-    <row r="460" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C460" s="3"/>
       <c r="D460" s="3"/>
       <c r="E460" s="3"/>
@@ -8829,7 +8837,7 @@
       <c r="J460" s="3"/>
       <c r="K460" s="3"/>
     </row>
-    <row r="461" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C461" s="3"/>
       <c r="D461" s="3"/>
       <c r="E461" s="3"/>
@@ -8840,7 +8848,7 @@
       <c r="J461" s="3"/>
       <c r="K461" s="3"/>
     </row>
-    <row r="462" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C462" s="3"/>
       <c r="D462" s="3"/>
       <c r="E462" s="3"/>
@@ -8851,7 +8859,7 @@
       <c r="J462" s="3"/>
       <c r="K462" s="3"/>
     </row>
-    <row r="463" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C463" s="3"/>
       <c r="D463" s="3"/>
       <c r="E463" s="3"/>
@@ -8862,7 +8870,7 @@
       <c r="J463" s="3"/>
       <c r="K463" s="3"/>
     </row>
-    <row r="464" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C464" s="3"/>
       <c r="D464" s="3"/>
       <c r="E464" s="3"/>
@@ -8873,7 +8881,7 @@
       <c r="J464" s="3"/>
       <c r="K464" s="3"/>
     </row>
-    <row r="465" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C465" s="3"/>
       <c r="D465" s="3"/>
       <c r="E465" s="3"/>
@@ -8884,7 +8892,7 @@
       <c r="J465" s="3"/>
       <c r="K465" s="3"/>
     </row>
-    <row r="466" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C466" s="3"/>
       <c r="D466" s="3"/>
       <c r="E466" s="3"/>
@@ -8895,7 +8903,7 @@
       <c r="J466" s="3"/>
       <c r="K466" s="3"/>
     </row>
-    <row r="467" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C467" s="3"/>
       <c r="D467" s="3"/>
       <c r="E467" s="3"/>
@@ -8906,7 +8914,7 @@
       <c r="J467" s="3"/>
       <c r="K467" s="3"/>
     </row>
-    <row r="468" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C468" s="3"/>
       <c r="D468" s="3"/>
       <c r="E468" s="3"/>
@@ -8917,7 +8925,7 @@
       <c r="J468" s="3"/>
       <c r="K468" s="3"/>
     </row>
-    <row r="469" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C469" s="3"/>
       <c r="D469" s="3"/>
       <c r="E469" s="3"/>
@@ -8928,7 +8936,7 @@
       <c r="J469" s="3"/>
       <c r="K469" s="3"/>
     </row>
-    <row r="470" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C470" s="3"/>
       <c r="D470" s="3"/>
       <c r="E470" s="3"/>
@@ -8939,7 +8947,7 @@
       <c r="J470" s="3"/>
       <c r="K470" s="3"/>
     </row>
-    <row r="471" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C471" s="3"/>
       <c r="D471" s="3"/>
       <c r="E471" s="3"/>
@@ -8950,7 +8958,7 @@
       <c r="J471" s="3"/>
       <c r="K471" s="3"/>
     </row>
-    <row r="472" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C472" s="3"/>
       <c r="D472" s="3"/>
       <c r="E472" s="3"/>
@@ -8961,7 +8969,7 @@
       <c r="J472" s="3"/>
       <c r="K472" s="3"/>
     </row>
-    <row r="473" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C473" s="3"/>
       <c r="D473" s="3"/>
       <c r="E473" s="3"/>
@@ -8972,7 +8980,7 @@
       <c r="J473" s="3"/>
       <c r="K473" s="3"/>
     </row>
-    <row r="474" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C474" s="3"/>
       <c r="D474" s="3"/>
       <c r="E474" s="3"/>
@@ -8983,7 +8991,7 @@
       <c r="J474" s="3"/>
       <c r="K474" s="3"/>
     </row>
-    <row r="475" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C475" s="3"/>
       <c r="D475" s="3"/>
       <c r="E475" s="3"/>
@@ -8994,7 +9002,7 @@
       <c r="J475" s="3"/>
       <c r="K475" s="3"/>
     </row>
-    <row r="476" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C476" s="3"/>
       <c r="D476" s="3"/>
       <c r="E476" s="3"/>
@@ -9005,7 +9013,7 @@
       <c r="J476" s="3"/>
       <c r="K476" s="3"/>
     </row>
-    <row r="477" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C477" s="3"/>
       <c r="D477" s="3"/>
       <c r="E477" s="3"/>
@@ -9016,7 +9024,7 @@
       <c r="J477" s="3"/>
       <c r="K477" s="3"/>
     </row>
-    <row r="478" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C478" s="3"/>
       <c r="D478" s="3"/>
       <c r="E478" s="3"/>
@@ -9027,7 +9035,7 @@
       <c r="J478" s="3"/>
       <c r="K478" s="3"/>
     </row>
-    <row r="479" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C479" s="3"/>
       <c r="D479" s="3"/>
       <c r="E479" s="3"/>
@@ -9038,7 +9046,7 @@
       <c r="J479" s="3"/>
       <c r="K479" s="3"/>
     </row>
-    <row r="480" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C480" s="3"/>
       <c r="D480" s="3"/>
       <c r="E480" s="3"/>
@@ -9049,7 +9057,7 @@
       <c r="J480" s="3"/>
       <c r="K480" s="3"/>
     </row>
-    <row r="481" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C481" s="3"/>
       <c r="D481" s="3"/>
       <c r="E481" s="3"/>
@@ -9060,7 +9068,7 @@
       <c r="J481" s="3"/>
       <c r="K481" s="3"/>
     </row>
-    <row r="482" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C482" s="3"/>
       <c r="D482" s="3"/>
       <c r="E482" s="3"/>
@@ -9071,7 +9079,7 @@
       <c r="J482" s="3"/>
       <c r="K482" s="3"/>
     </row>
-    <row r="483" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C483" s="3"/>
       <c r="D483" s="3"/>
       <c r="E483" s="3"/>
@@ -9082,7 +9090,7 @@
       <c r="J483" s="3"/>
       <c r="K483" s="3"/>
     </row>
-    <row r="484" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C484" s="3"/>
       <c r="D484" s="3"/>
       <c r="E484" s="3"/>
@@ -9093,7 +9101,7 @@
       <c r="J484" s="3"/>
       <c r="K484" s="3"/>
     </row>
-    <row r="485" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C485" s="3"/>
       <c r="D485" s="3"/>
       <c r="E485" s="3"/>
@@ -9104,7 +9112,7 @@
       <c r="J485" s="3"/>
       <c r="K485" s="3"/>
     </row>
-    <row r="486" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C486" s="3"/>
       <c r="D486" s="3"/>
       <c r="E486" s="3"/>
@@ -9115,7 +9123,7 @@
       <c r="J486" s="3"/>
       <c r="K486" s="3"/>
     </row>
-    <row r="487" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C487" s="3"/>
       <c r="D487" s="3"/>
       <c r="E487" s="3"/>
@@ -9126,7 +9134,7 @@
       <c r="J487" s="3"/>
       <c r="K487" s="3"/>
     </row>
-    <row r="488" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C488" s="3"/>
       <c r="D488" s="3"/>
       <c r="E488" s="3"/>
@@ -9137,7 +9145,7 @@
       <c r="J488" s="3"/>
       <c r="K488" s="3"/>
     </row>
-    <row r="489" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C489" s="3"/>
       <c r="D489" s="3"/>
       <c r="E489" s="3"/>
@@ -9148,7 +9156,7 @@
       <c r="J489" s="3"/>
       <c r="K489" s="3"/>
     </row>
-    <row r="490" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C490" s="3"/>
       <c r="D490" s="3"/>
       <c r="E490" s="3"/>
@@ -9159,7 +9167,7 @@
       <c r="J490" s="3"/>
       <c r="K490" s="3"/>
     </row>
-    <row r="491" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C491" s="3"/>
       <c r="D491" s="3"/>
       <c r="E491" s="3"/>
@@ -9170,7 +9178,7 @@
       <c r="J491" s="3"/>
       <c r="K491" s="3"/>
     </row>
-    <row r="492" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C492" s="3"/>
       <c r="D492" s="3"/>
       <c r="E492" s="3"/>
@@ -9181,7 +9189,7 @@
       <c r="J492" s="3"/>
       <c r="K492" s="3"/>
     </row>
-    <row r="493" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C493" s="3"/>
       <c r="D493" s="3"/>
       <c r="E493" s="3"/>
@@ -9192,7 +9200,7 @@
       <c r="J493" s="3"/>
       <c r="K493" s="3"/>
     </row>
-    <row r="494" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C494" s="3"/>
       <c r="D494" s="3"/>
       <c r="E494" s="3"/>
@@ -9203,7 +9211,7 @@
       <c r="J494" s="3"/>
       <c r="K494" s="3"/>
     </row>
-    <row r="495" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C495" s="3"/>
       <c r="D495" s="3"/>
       <c r="E495" s="3"/>
@@ -9214,7 +9222,7 @@
       <c r="J495" s="3"/>
       <c r="K495" s="3"/>
     </row>
-    <row r="496" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C496" s="3"/>
       <c r="D496" s="3"/>
       <c r="E496" s="3"/>
@@ -9225,7 +9233,7 @@
       <c r="J496" s="3"/>
       <c r="K496" s="3"/>
     </row>
-    <row r="497" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C497" s="3"/>
       <c r="D497" s="3"/>
       <c r="E497" s="3"/>
@@ -9236,7 +9244,7 @@
       <c r="J497" s="3"/>
       <c r="K497" s="3"/>
     </row>
-    <row r="498" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C498" s="3"/>
       <c r="D498" s="3"/>
       <c r="E498" s="3"/>
@@ -9247,7 +9255,7 @@
       <c r="J498" s="3"/>
       <c r="K498" s="3"/>
     </row>
-    <row r="499" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C499" s="3"/>
       <c r="D499" s="3"/>
       <c r="E499" s="3"/>
@@ -9258,7 +9266,7 @@
       <c r="J499" s="3"/>
       <c r="K499" s="3"/>
     </row>
-    <row r="500" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C500" s="3"/>
       <c r="D500" s="3"/>
       <c r="E500" s="3"/>
@@ -9269,7 +9277,7 @@
       <c r="J500" s="3"/>
       <c r="K500" s="3"/>
     </row>
-    <row r="501" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C501" s="3"/>
       <c r="D501" s="3"/>
       <c r="E501" s="3"/>
@@ -9280,7 +9288,7 @@
       <c r="J501" s="3"/>
       <c r="K501" s="3"/>
     </row>
-    <row r="502" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C502" s="3"/>
       <c r="D502" s="3"/>
       <c r="E502" s="3"/>
@@ -9291,7 +9299,7 @@
       <c r="J502" s="3"/>
       <c r="K502" s="3"/>
     </row>
-    <row r="503" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C503" s="3"/>
       <c r="D503" s="3"/>
       <c r="E503" s="3"/>
@@ -9302,7 +9310,7 @@
       <c r="J503" s="3"/>
       <c r="K503" s="3"/>
     </row>
-    <row r="504" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C504" s="3"/>
       <c r="D504" s="3"/>
       <c r="E504" s="3"/>
@@ -9313,7 +9321,7 @@
       <c r="J504" s="3"/>
       <c r="K504" s="3"/>
     </row>
-    <row r="505" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C505" s="3"/>
       <c r="D505" s="3"/>
       <c r="E505" s="3"/>
@@ -9324,7 +9332,7 @@
       <c r="J505" s="3"/>
       <c r="K505" s="3"/>
     </row>
-    <row r="506" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C506" s="3"/>
       <c r="D506" s="3"/>
       <c r="E506" s="3"/>
@@ -9335,7 +9343,7 @@
       <c r="J506" s="3"/>
       <c r="K506" s="3"/>
     </row>
-    <row r="507" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C507" s="3"/>
       <c r="D507" s="3"/>
       <c r="E507" s="3"/>
@@ -9346,7 +9354,7 @@
       <c r="J507" s="3"/>
       <c r="K507" s="3"/>
     </row>
-    <row r="508" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C508" s="3"/>
       <c r="D508" s="3"/>
       <c r="E508" s="3"/>
@@ -9357,7 +9365,7 @@
       <c r="J508" s="3"/>
       <c r="K508" s="3"/>
     </row>
-    <row r="509" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C509" s="3"/>
       <c r="D509" s="3"/>
       <c r="E509" s="3"/>
@@ -9368,7 +9376,7 @@
       <c r="J509" s="3"/>
       <c r="K509" s="3"/>
     </row>
-    <row r="510" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C510" s="3"/>
       <c r="D510" s="3"/>
       <c r="E510" s="3"/>
@@ -9379,7 +9387,7 @@
       <c r="J510" s="3"/>
       <c r="K510" s="3"/>
     </row>
-    <row r="511" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C511" s="3"/>
       <c r="D511" s="3"/>
       <c r="E511" s="3"/>
@@ -9390,7 +9398,7 @@
       <c r="J511" s="3"/>
       <c r="K511" s="3"/>
     </row>
-    <row r="512" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C512" s="3"/>
       <c r="D512" s="3"/>
       <c r="E512" s="3"/>
@@ -9401,7 +9409,7 @@
       <c r="J512" s="3"/>
       <c r="K512" s="3"/>
     </row>
-    <row r="513" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C513" s="3"/>
       <c r="D513" s="3"/>
       <c r="E513" s="3"/>
@@ -9412,7 +9420,7 @@
       <c r="J513" s="3"/>
       <c r="K513" s="3"/>
     </row>
-    <row r="514" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C514" s="3"/>
       <c r="D514" s="3"/>
       <c r="E514" s="3"/>
@@ -9423,7 +9431,7 @@
       <c r="J514" s="3"/>
       <c r="K514" s="3"/>
     </row>
-    <row r="515" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C515" s="3"/>
       <c r="D515" s="3"/>
       <c r="E515" s="3"/>
@@ -9434,7 +9442,7 @@
       <c r="J515" s="3"/>
       <c r="K515" s="3"/>
     </row>
-    <row r="516" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C516" s="3"/>
       <c r="D516" s="3"/>
       <c r="E516" s="3"/>
@@ -9445,7 +9453,7 @@
       <c r="J516" s="3"/>
       <c r="K516" s="3"/>
     </row>
-    <row r="517" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C517" s="3"/>
       <c r="D517" s="3"/>
       <c r="E517" s="3"/>
@@ -9456,7 +9464,7 @@
       <c r="J517" s="3"/>
       <c r="K517" s="3"/>
     </row>
-    <row r="518" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C518" s="3"/>
       <c r="D518" s="3"/>
       <c r="E518" s="3"/>
@@ -9467,7 +9475,7 @@
       <c r="J518" s="3"/>
       <c r="K518" s="3"/>
     </row>
-    <row r="519" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C519" s="3"/>
       <c r="D519" s="3"/>
       <c r="E519" s="3"/>
@@ -9478,7 +9486,7 @@
       <c r="J519" s="3"/>
       <c r="K519" s="3"/>
     </row>
-    <row r="520" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C520" s="3"/>
       <c r="D520" s="3"/>
       <c r="E520" s="3"/>
@@ -9489,7 +9497,7 @@
       <c r="J520" s="3"/>
       <c r="K520" s="3"/>
     </row>
-    <row r="521" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C521" s="3"/>
       <c r="D521" s="3"/>
       <c r="E521" s="3"/>
@@ -9500,7 +9508,7 @@
       <c r="J521" s="3"/>
       <c r="K521" s="3"/>
     </row>
-    <row r="522" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C522" s="3"/>
       <c r="D522" s="3"/>
       <c r="E522" s="3"/>
@@ -9511,7 +9519,7 @@
       <c r="J522" s="3"/>
       <c r="K522" s="3"/>
     </row>
-    <row r="523" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C523" s="3"/>
       <c r="D523" s="3"/>
       <c r="E523" s="3"/>
@@ -9522,7 +9530,7 @@
       <c r="J523" s="3"/>
       <c r="K523" s="3"/>
     </row>
-    <row r="524" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C524" s="3"/>
       <c r="D524" s="3"/>
       <c r="E524" s="3"/>
@@ -9533,7 +9541,7 @@
       <c r="J524" s="3"/>
       <c r="K524" s="3"/>
     </row>
-    <row r="525" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C525" s="3"/>
       <c r="D525" s="3"/>
       <c r="E525" s="3"/>
@@ -9544,7 +9552,7 @@
       <c r="J525" s="3"/>
       <c r="K525" s="3"/>
     </row>
-    <row r="526" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C526" s="3"/>
       <c r="D526" s="3"/>
       <c r="E526" s="3"/>
@@ -9555,7 +9563,7 @@
       <c r="J526" s="3"/>
       <c r="K526" s="3"/>
     </row>
-    <row r="527" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C527" s="3"/>
       <c r="D527" s="3"/>
       <c r="E527" s="3"/>
@@ -9566,7 +9574,7 @@
       <c r="J527" s="3"/>
       <c r="K527" s="3"/>
     </row>
-    <row r="528" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C528" s="3"/>
       <c r="D528" s="3"/>
       <c r="E528" s="3"/>
@@ -9577,7 +9585,7 @@
       <c r="J528" s="3"/>
       <c r="K528" s="3"/>
     </row>
-    <row r="529" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C529" s="3"/>
       <c r="D529" s="3"/>
       <c r="E529" s="3"/>
@@ -9588,7 +9596,7 @@
       <c r="J529" s="3"/>
       <c r="K529" s="3"/>
     </row>
-    <row r="530" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C530" s="3"/>
       <c r="D530" s="3"/>
       <c r="E530" s="3"/>
@@ -9599,7 +9607,7 @@
       <c r="J530" s="3"/>
       <c r="K530" s="3"/>
     </row>
-    <row r="531" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C531" s="3"/>
       <c r="D531" s="3"/>
       <c r="E531" s="3"/>
@@ -9610,7 +9618,7 @@
       <c r="J531" s="3"/>
       <c r="K531" s="3"/>
     </row>
-    <row r="532" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C532" s="3"/>
       <c r="D532" s="3"/>
       <c r="E532" s="3"/>
@@ -9621,7 +9629,7 @@
       <c r="J532" s="3"/>
       <c r="K532" s="3"/>
     </row>
-    <row r="533" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C533" s="3"/>
       <c r="D533" s="3"/>
       <c r="E533" s="3"/>
@@ -9632,7 +9640,7 @@
       <c r="J533" s="3"/>
       <c r="K533" s="3"/>
     </row>
-    <row r="534" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C534" s="3"/>
       <c r="D534" s="3"/>
       <c r="E534" s="3"/>
@@ -9643,7 +9651,7 @@
       <c r="J534" s="3"/>
       <c r="K534" s="3"/>
     </row>
-    <row r="535" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C535" s="3"/>
       <c r="D535" s="3"/>
       <c r="E535" s="3"/>
@@ -9654,7 +9662,7 @@
       <c r="J535" s="3"/>
       <c r="K535" s="3"/>
     </row>
-    <row r="536" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C536" s="3"/>
       <c r="D536" s="3"/>
       <c r="E536" s="3"/>
@@ -9665,7 +9673,7 @@
       <c r="J536" s="3"/>
       <c r="K536" s="3"/>
     </row>
-    <row r="537" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C537" s="3"/>
       <c r="D537" s="3"/>
       <c r="E537" s="3"/>
@@ -9676,7 +9684,7 @@
       <c r="J537" s="3"/>
       <c r="K537" s="3"/>
     </row>
-    <row r="538" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C538" s="3"/>
       <c r="D538" s="3"/>
       <c r="E538" s="3"/>
@@ -9687,7 +9695,7 @@
       <c r="J538" s="3"/>
       <c r="K538" s="3"/>
     </row>
-    <row r="539" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C539" s="3"/>
       <c r="D539" s="3"/>
       <c r="E539" s="3"/>
@@ -9698,7 +9706,7 @@
       <c r="J539" s="3"/>
       <c r="K539" s="3"/>
     </row>
-    <row r="540" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C540" s="3"/>
       <c r="D540" s="3"/>
       <c r="E540" s="3"/>
@@ -9709,7 +9717,7 @@
       <c r="J540" s="3"/>
       <c r="K540" s="3"/>
     </row>
-    <row r="541" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C541" s="3"/>
       <c r="D541" s="3"/>
       <c r="E541" s="3"/>
@@ -9720,7 +9728,7 @@
       <c r="J541" s="3"/>
       <c r="K541" s="3"/>
     </row>
-    <row r="542" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C542" s="3"/>
       <c r="D542" s="3"/>
       <c r="E542" s="3"/>
@@ -9731,7 +9739,7 @@
       <c r="J542" s="3"/>
       <c r="K542" s="3"/>
     </row>
-    <row r="543" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C543" s="3"/>
       <c r="D543" s="3"/>
       <c r="E543" s="3"/>
@@ -9742,7 +9750,7 @@
       <c r="J543" s="3"/>
       <c r="K543" s="3"/>
     </row>
-    <row r="544" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C544" s="3"/>
       <c r="D544" s="3"/>
       <c r="E544" s="3"/>
@@ -9753,7 +9761,7 @@
       <c r="J544" s="3"/>
       <c r="K544" s="3"/>
     </row>
-    <row r="545" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C545" s="3"/>
       <c r="D545" s="3"/>
       <c r="E545" s="3"/>
@@ -9764,7 +9772,7 @@
       <c r="J545" s="3"/>
       <c r="K545" s="3"/>
     </row>
-    <row r="546" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C546" s="3"/>
       <c r="D546" s="3"/>
       <c r="E546" s="3"/>
@@ -9775,7 +9783,7 @@
       <c r="J546" s="3"/>
       <c r="K546" s="3"/>
     </row>
-    <row r="547" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C547" s="3"/>
       <c r="D547" s="3"/>
       <c r="E547" s="3"/>
@@ -9786,7 +9794,7 @@
       <c r="J547" s="3"/>
       <c r="K547" s="3"/>
     </row>
-    <row r="548" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C548" s="3"/>
       <c r="D548" s="3"/>
       <c r="E548" s="3"/>
@@ -9797,7 +9805,7 @@
       <c r="J548" s="3"/>
       <c r="K548" s="3"/>
     </row>
-    <row r="549" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C549" s="3"/>
       <c r="D549" s="3"/>
       <c r="E549" s="3"/>
@@ -9808,7 +9816,7 @@
       <c r="J549" s="3"/>
       <c r="K549" s="3"/>
     </row>
-    <row r="550" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C550" s="3"/>
       <c r="D550" s="3"/>
       <c r="E550" s="3"/>
@@ -9819,7 +9827,7 @@
       <c r="J550" s="3"/>
       <c r="K550" s="3"/>
     </row>
-    <row r="551" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C551" s="3"/>
       <c r="D551" s="3"/>
       <c r="E551" s="3"/>
@@ -9830,7 +9838,7 @@
       <c r="J551" s="3"/>
       <c r="K551" s="3"/>
     </row>
-    <row r="552" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C552" s="3"/>
       <c r="D552" s="3"/>
       <c r="E552" s="3"/>
@@ -9841,7 +9849,7 @@
       <c r="J552" s="3"/>
       <c r="K552" s="3"/>
     </row>
-    <row r="553" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C553" s="3"/>
       <c r="D553" s="3"/>
       <c r="E553" s="3"/>
@@ -9852,7 +9860,7 @@
       <c r="J553" s="3"/>
       <c r="K553" s="3"/>
     </row>
-    <row r="554" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C554" s="3"/>
       <c r="D554" s="3"/>
       <c r="E554" s="3"/>
@@ -9863,7 +9871,7 @@
       <c r="J554" s="3"/>
       <c r="K554" s="3"/>
     </row>
-    <row r="555" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C555" s="3"/>
       <c r="D555" s="3"/>
       <c r="E555" s="3"/>
@@ -9874,7 +9882,7 @@
       <c r="J555" s="3"/>
       <c r="K555" s="3"/>
     </row>
-    <row r="556" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C556" s="3"/>
       <c r="D556" s="3"/>
       <c r="E556" s="3"/>
@@ -9885,7 +9893,7 @@
       <c r="J556" s="3"/>
       <c r="K556" s="3"/>
     </row>
-    <row r="557" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C557" s="3"/>
       <c r="D557" s="3"/>
       <c r="E557" s="3"/>
@@ -9896,7 +9904,7 @@
       <c r="J557" s="3"/>
       <c r="K557" s="3"/>
     </row>
-    <row r="558" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C558" s="3"/>
       <c r="D558" s="3"/>
       <c r="E558" s="3"/>
@@ -9907,7 +9915,7 @@
       <c r="J558" s="3"/>
       <c r="K558" s="3"/>
     </row>
-    <row r="559" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C559" s="3"/>
       <c r="D559" s="3"/>
       <c r="E559" s="3"/>
@@ -9918,7 +9926,7 @@
       <c r="J559" s="3"/>
       <c r="K559" s="3"/>
     </row>
-    <row r="560" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C560" s="3"/>
       <c r="D560" s="3"/>
       <c r="E560" s="3"/>
@@ -9929,7 +9937,7 @@
       <c r="J560" s="3"/>
       <c r="K560" s="3"/>
     </row>
-    <row r="561" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C561" s="3"/>
       <c r="D561" s="3"/>
       <c r="E561" s="3"/>
@@ -9940,7 +9948,7 @@
       <c r="J561" s="3"/>
       <c r="K561" s="3"/>
     </row>
-    <row r="562" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C562" s="3"/>
       <c r="D562" s="3"/>
       <c r="E562" s="3"/>
@@ -9951,7 +9959,7 @@
       <c r="J562" s="3"/>
       <c r="K562" s="3"/>
     </row>
-    <row r="563" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C563" s="3"/>
       <c r="D563" s="3"/>
       <c r="E563" s="3"/>
@@ -9962,7 +9970,7 @@
       <c r="J563" s="3"/>
       <c r="K563" s="3"/>
     </row>
-    <row r="564" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C564" s="3"/>
       <c r="D564" s="3"/>
       <c r="E564" s="3"/>
@@ -9973,7 +9981,7 @@
       <c r="J564" s="3"/>
       <c r="K564" s="3"/>
     </row>
-    <row r="565" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C565" s="3"/>
       <c r="D565" s="3"/>
       <c r="E565" s="3"/>
@@ -9984,7 +9992,7 @@
       <c r="J565" s="3"/>
       <c r="K565" s="3"/>
     </row>
-    <row r="566" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C566" s="3"/>
       <c r="D566" s="3"/>
       <c r="E566" s="3"/>
@@ -9995,7 +10003,7 @@
       <c r="J566" s="3"/>
       <c r="K566" s="3"/>
     </row>
-    <row r="567" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C567" s="3"/>
       <c r="D567" s="3"/>
       <c r="E567" s="3"/>
@@ -10006,7 +10014,7 @@
       <c r="J567" s="3"/>
       <c r="K567" s="3"/>
     </row>
-    <row r="568" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C568" s="3"/>
       <c r="D568" s="3"/>
       <c r="E568" s="3"/>
@@ -10017,7 +10025,7 @@
       <c r="J568" s="3"/>
       <c r="K568" s="3"/>
     </row>
-    <row r="569" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C569" s="3"/>
       <c r="D569" s="3"/>
       <c r="E569" s="3"/>
@@ -10028,7 +10036,7 @@
       <c r="J569" s="3"/>
       <c r="K569" s="3"/>
     </row>
-    <row r="570" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C570" s="3"/>
       <c r="D570" s="3"/>
       <c r="E570" s="3"/>
@@ -10039,7 +10047,7 @@
       <c r="J570" s="3"/>
       <c r="K570" s="3"/>
     </row>
-    <row r="571" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C571" s="3"/>
       <c r="D571" s="3"/>
       <c r="E571" s="3"/>
@@ -10050,7 +10058,7 @@
       <c r="J571" s="3"/>
       <c r="K571" s="3"/>
     </row>
-    <row r="572" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C572" s="3"/>
       <c r="D572" s="3"/>
       <c r="E572" s="3"/>
@@ -10061,7 +10069,7 @@
       <c r="J572" s="3"/>
       <c r="K572" s="3"/>
     </row>
-    <row r="573" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C573" s="3"/>
       <c r="D573" s="3"/>
       <c r="E573" s="3"/>
@@ -10072,7 +10080,7 @@
       <c r="J573" s="3"/>
       <c r="K573" s="3"/>
     </row>
-    <row r="574" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C574" s="3"/>
       <c r="D574" s="3"/>
       <c r="E574" s="3"/>
@@ -10083,7 +10091,7 @@
       <c r="J574" s="3"/>
       <c r="K574" s="3"/>
     </row>
-    <row r="575" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C575" s="3"/>
       <c r="D575" s="3"/>
       <c r="E575" s="3"/>
@@ -10094,7 +10102,7 @@
       <c r="J575" s="3"/>
       <c r="K575" s="3"/>
     </row>
-    <row r="576" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C576" s="3"/>
       <c r="D576" s="3"/>
       <c r="E576" s="3"/>
@@ -10105,7 +10113,7 @@
       <c r="J576" s="3"/>
       <c r="K576" s="3"/>
     </row>
-    <row r="577" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C577" s="3"/>
       <c r="D577" s="3"/>
       <c r="E577" s="3"/>
@@ -10116,7 +10124,7 @@
       <c r="J577" s="3"/>
       <c r="K577" s="3"/>
     </row>
-    <row r="578" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C578" s="3"/>
       <c r="D578" s="3"/>
       <c r="E578" s="3"/>
@@ -10127,7 +10135,7 @@
       <c r="J578" s="3"/>
       <c r="K578" s="3"/>
     </row>
-    <row r="579" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C579" s="3"/>
       <c r="D579" s="3"/>
       <c r="E579" s="3"/>
@@ -10138,7 +10146,7 @@
       <c r="J579" s="3"/>
       <c r="K579" s="3"/>
     </row>
-    <row r="580" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C580" s="3"/>
       <c r="D580" s="3"/>
       <c r="E580" s="3"/>
@@ -10149,7 +10157,7 @@
       <c r="J580" s="3"/>
       <c r="K580" s="3"/>
     </row>
-    <row r="581" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C581" s="3"/>
       <c r="D581" s="3"/>
       <c r="E581" s="3"/>
@@ -10160,7 +10168,7 @@
       <c r="J581" s="3"/>
       <c r="K581" s="3"/>
     </row>
-    <row r="582" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C582" s="3"/>
       <c r="D582" s="3"/>
       <c r="E582" s="3"/>
@@ -10171,7 +10179,7 @@
       <c r="J582" s="3"/>
       <c r="K582" s="3"/>
     </row>
-    <row r="583" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C583" s="3"/>
       <c r="D583" s="3"/>
       <c r="E583" s="3"/>
@@ -10182,7 +10190,7 @@
       <c r="J583" s="3"/>
       <c r="K583" s="3"/>
     </row>
-    <row r="584" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C584" s="3"/>
       <c r="D584" s="3"/>
       <c r="E584" s="3"/>
@@ -10193,7 +10201,7 @@
       <c r="J584" s="3"/>
       <c r="K584" s="3"/>
     </row>
-    <row r="585" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C585" s="3"/>
       <c r="D585" s="3"/>
       <c r="E585" s="3"/>
@@ -10204,7 +10212,7 @@
       <c r="J585" s="3"/>
       <c r="K585" s="3"/>
     </row>
-    <row r="586" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C586" s="3"/>
       <c r="D586" s="3"/>
       <c r="E586" s="3"/>
@@ -10215,7 +10223,7 @@
       <c r="J586" s="3"/>
       <c r="K586" s="3"/>
     </row>
-    <row r="587" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C587" s="3"/>
       <c r="D587" s="3"/>
       <c r="E587" s="3"/>
@@ -10226,7 +10234,7 @@
       <c r="J587" s="3"/>
       <c r="K587" s="3"/>
     </row>
-    <row r="588" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C588" s="3"/>
       <c r="D588" s="3"/>
       <c r="E588" s="3"/>
@@ -10237,7 +10245,7 @@
       <c r="J588" s="3"/>
       <c r="K588" s="3"/>
     </row>
-    <row r="589" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C589" s="3"/>
       <c r="D589" s="3"/>
       <c r="E589" s="3"/>
@@ -10248,7 +10256,7 @@
       <c r="J589" s="3"/>
       <c r="K589" s="3"/>
     </row>
-    <row r="590" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C590" s="3"/>
       <c r="D590" s="3"/>
       <c r="E590" s="3"/>
@@ -10259,7 +10267,7 @@
       <c r="J590" s="3"/>
       <c r="K590" s="3"/>
     </row>
-    <row r="591" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C591" s="3"/>
       <c r="D591" s="3"/>
       <c r="E591" s="3"/>
@@ -10270,7 +10278,7 @@
       <c r="J591" s="3"/>
       <c r="K591" s="3"/>
     </row>
-    <row r="592" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C592" s="3"/>
       <c r="D592" s="3"/>
       <c r="E592" s="3"/>
@@ -10281,7 +10289,7 @@
       <c r="J592" s="3"/>
       <c r="K592" s="3"/>
     </row>
-    <row r="593" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C593" s="3"/>
       <c r="D593" s="3"/>
       <c r="E593" s="3"/>
@@ -10292,7 +10300,7 @@
       <c r="J593" s="3"/>
       <c r="K593" s="3"/>
     </row>
-    <row r="594" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C594" s="3"/>
       <c r="D594" s="3"/>
       <c r="E594" s="3"/>
@@ -10303,7 +10311,7 @@
       <c r="J594" s="3"/>
       <c r="K594" s="3"/>
     </row>
-    <row r="595" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C595" s="3"/>
       <c r="D595" s="3"/>
       <c r="E595" s="3"/>
@@ -10314,7 +10322,7 @@
       <c r="J595" s="3"/>
       <c r="K595" s="3"/>
     </row>
-    <row r="596" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C596" s="3"/>
       <c r="D596" s="3"/>
       <c r="E596" s="3"/>
@@ -10325,7 +10333,7 @@
       <c r="J596" s="3"/>
       <c r="K596" s="3"/>
     </row>
-    <row r="597" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C597" s="3"/>
       <c r="D597" s="3"/>
       <c r="E597" s="3"/>
@@ -10336,7 +10344,7 @@
       <c r="J597" s="3"/>
       <c r="K597" s="3"/>
     </row>
-    <row r="598" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C598" s="3"/>
       <c r="D598" s="3"/>
       <c r="E598" s="3"/>
@@ -10347,7 +10355,7 @@
       <c r="J598" s="3"/>
       <c r="K598" s="3"/>
     </row>
-    <row r="599" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C599" s="3"/>
       <c r="D599" s="3"/>
       <c r="E599" s="3"/>
@@ -10358,7 +10366,7 @@
       <c r="J599" s="3"/>
       <c r="K599" s="3"/>
     </row>
-    <row r="600" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C600" s="3"/>
       <c r="D600" s="3"/>
       <c r="E600" s="3"/>
@@ -10369,7 +10377,7 @@
       <c r="J600" s="3"/>
       <c r="K600" s="3"/>
     </row>
-    <row r="601" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C601" s="3"/>
       <c r="D601" s="3"/>
       <c r="E601" s="3"/>
@@ -10380,7 +10388,7 @@
       <c r="J601" s="3"/>
       <c r="K601" s="3"/>
     </row>
-    <row r="602" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C602" s="3"/>
       <c r="D602" s="3"/>
       <c r="E602" s="3"/>
@@ -10391,7 +10399,7 @@
       <c r="J602" s="3"/>
       <c r="K602" s="3"/>
     </row>
-    <row r="603" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C603" s="3"/>
       <c r="D603" s="3"/>
       <c r="E603" s="3"/>
@@ -10402,7 +10410,7 @@
       <c r="J603" s="3"/>
       <c r="K603" s="3"/>
     </row>
-    <row r="604" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C604" s="3"/>
       <c r="D604" s="3"/>
       <c r="E604" s="3"/>
@@ -10413,7 +10421,7 @@
       <c r="J604" s="3"/>
       <c r="K604" s="3"/>
     </row>
-    <row r="605" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C605" s="3"/>
       <c r="D605" s="3"/>
       <c r="E605" s="3"/>
@@ -10424,7 +10432,7 @@
       <c r="J605" s="3"/>
       <c r="K605" s="3"/>
     </row>
-    <row r="606" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C606" s="3"/>
       <c r="D606" s="3"/>
       <c r="E606" s="3"/>
@@ -10435,7 +10443,7 @@
       <c r="J606" s="3"/>
       <c r="K606" s="3"/>
     </row>
-    <row r="607" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C607" s="3"/>
       <c r="D607" s="3"/>
       <c r="E607" s="3"/>
@@ -10446,7 +10454,7 @@
       <c r="J607" s="3"/>
       <c r="K607" s="3"/>
     </row>
-    <row r="608" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C608" s="3"/>
       <c r="D608" s="3"/>
       <c r="E608" s="3"/>
@@ -10457,7 +10465,7 @@
       <c r="J608" s="3"/>
       <c r="K608" s="3"/>
     </row>
-    <row r="609" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C609" s="3"/>
       <c r="D609" s="3"/>
       <c r="E609" s="3"/>
@@ -10468,7 +10476,7 @@
       <c r="J609" s="3"/>
       <c r="K609" s="3"/>
     </row>
-    <row r="610" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C610" s="3"/>
       <c r="D610" s="3"/>
       <c r="E610" s="3"/>
@@ -10479,7 +10487,7 @@
       <c r="J610" s="3"/>
       <c r="K610" s="3"/>
     </row>
-    <row r="611" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C611" s="3"/>
       <c r="D611" s="3"/>
       <c r="E611" s="3"/>
@@ -10490,7 +10498,7 @@
       <c r="J611" s="3"/>
       <c r="K611" s="3"/>
     </row>
-    <row r="612" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C612" s="3"/>
       <c r="D612" s="3"/>
       <c r="E612" s="3"/>
@@ -10501,7 +10509,7 @@
       <c r="J612" s="3"/>
       <c r="K612" s="3"/>
     </row>
-    <row r="613" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C613" s="3"/>
       <c r="D613" s="3"/>
       <c r="E613" s="3"/>
@@ -10512,7 +10520,7 @@
       <c r="J613" s="3"/>
       <c r="K613" s="3"/>
     </row>
-    <row r="614" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C614" s="3"/>
       <c r="D614" s="3"/>
       <c r="E614" s="3"/>
@@ -10523,7 +10531,7 @@
       <c r="J614" s="3"/>
       <c r="K614" s="3"/>
     </row>
-    <row r="615" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C615" s="3"/>
       <c r="D615" s="3"/>
       <c r="E615" s="3"/>
@@ -10534,7 +10542,7 @@
       <c r="J615" s="3"/>
       <c r="K615" s="3"/>
     </row>
-    <row r="616" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C616" s="3"/>
       <c r="D616" s="3"/>
       <c r="E616" s="3"/>
@@ -10545,7 +10553,7 @@
       <c r="J616" s="3"/>
       <c r="K616" s="3"/>
     </row>
-    <row r="617" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C617" s="3"/>
       <c r="D617" s="3"/>
       <c r="E617" s="3"/>
@@ -10556,7 +10564,7 @@
       <c r="J617" s="3"/>
       <c r="K617" s="3"/>
     </row>
-    <row r="618" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C618" s="3"/>
       <c r="D618" s="3"/>
       <c r="E618" s="3"/>
@@ -10567,7 +10575,7 @@
       <c r="J618" s="3"/>
       <c r="K618" s="3"/>
     </row>
-    <row r="619" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C619" s="3"/>
       <c r="D619" s="3"/>
       <c r="E619" s="3"/>
@@ -10578,7 +10586,7 @@
       <c r="J619" s="3"/>
       <c r="K619" s="3"/>
     </row>
-    <row r="620" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C620" s="3"/>
       <c r="D620" s="3"/>
       <c r="E620" s="3"/>
@@ -10589,7 +10597,7 @@
       <c r="J620" s="3"/>
       <c r="K620" s="3"/>
     </row>
-    <row r="621" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C621" s="3"/>
       <c r="D621" s="3"/>
       <c r="E621" s="3"/>
@@ -10600,7 +10608,7 @@
       <c r="J621" s="3"/>
       <c r="K621" s="3"/>
     </row>
-    <row r="622" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C622" s="3"/>
       <c r="D622" s="3"/>
       <c r="E622" s="3"/>
@@ -10611,7 +10619,7 @@
       <c r="J622" s="3"/>
       <c r="K622" s="3"/>
     </row>
-    <row r="623" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C623" s="3"/>
       <c r="D623" s="3"/>
       <c r="E623" s="3"/>
@@ -10622,7 +10630,7 @@
       <c r="J623" s="3"/>
       <c r="K623" s="3"/>
     </row>
-    <row r="624" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C624" s="3"/>
       <c r="D624" s="3"/>
       <c r="E624" s="3"/>
@@ -10633,7 +10641,7 @@
       <c r="J624" s="3"/>
       <c r="K624" s="3"/>
     </row>
-    <row r="625" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C625" s="3"/>
       <c r="D625" s="3"/>
       <c r="E625" s="3"/>
@@ -10644,7 +10652,7 @@
       <c r="J625" s="3"/>
       <c r="K625" s="3"/>
     </row>
-    <row r="626" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C626" s="3"/>
       <c r="D626" s="3"/>
       <c r="E626" s="3"/>
@@ -10655,7 +10663,7 @@
       <c r="J626" s="3"/>
       <c r="K626" s="3"/>
     </row>
-    <row r="627" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C627" s="3"/>
       <c r="D627" s="3"/>
       <c r="E627" s="3"/>
@@ -10666,7 +10674,7 @@
       <c r="J627" s="3"/>
       <c r="K627" s="3"/>
     </row>
-    <row r="628" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C628" s="3"/>
       <c r="D628" s="3"/>
       <c r="E628" s="3"/>
@@ -10677,7 +10685,7 @@
       <c r="J628" s="3"/>
       <c r="K628" s="3"/>
     </row>
-    <row r="629" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C629" s="3"/>
       <c r="D629" s="3"/>
       <c r="E629" s="3"/>
@@ -10688,7 +10696,7 @@
       <c r="J629" s="3"/>
       <c r="K629" s="3"/>
     </row>
-    <row r="630" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C630" s="3"/>
       <c r="D630" s="3"/>
       <c r="E630" s="3"/>
@@ -10699,7 +10707,7 @@
       <c r="J630" s="3"/>
       <c r="K630" s="3"/>
     </row>
-    <row r="631" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C631" s="3"/>
       <c r="D631" s="3"/>
       <c r="E631" s="3"/>
@@ -10710,7 +10718,7 @@
       <c r="J631" s="3"/>
       <c r="K631" s="3"/>
     </row>
-    <row r="632" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C632" s="3"/>
       <c r="D632" s="3"/>
       <c r="E632" s="3"/>
@@ -10721,7 +10729,7 @@
       <c r="J632" s="3"/>
       <c r="K632" s="3"/>
     </row>
-    <row r="633" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C633" s="3"/>
       <c r="D633" s="3"/>
       <c r="E633" s="3"/>
@@ -10732,7 +10740,7 @@
       <c r="J633" s="3"/>
       <c r="K633" s="3"/>
     </row>
-    <row r="634" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C634" s="3"/>
       <c r="D634" s="3"/>
       <c r="E634" s="3"/>
@@ -10743,7 +10751,7 @@
       <c r="J634" s="3"/>
       <c r="K634" s="3"/>
     </row>
-    <row r="635" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C635" s="3"/>
       <c r="D635" s="3"/>
       <c r="E635" s="3"/>
@@ -10754,7 +10762,7 @@
       <c r="J635" s="3"/>
       <c r="K635" s="3"/>
     </row>
-    <row r="636" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C636" s="3"/>
       <c r="D636" s="3"/>
       <c r="E636" s="3"/>
@@ -10765,7 +10773,7 @@
       <c r="J636" s="3"/>
       <c r="K636" s="3"/>
     </row>
-    <row r="637" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C637" s="3"/>
       <c r="D637" s="3"/>
       <c r="E637" s="3"/>
@@ -10776,7 +10784,7 @@
       <c r="J637" s="3"/>
       <c r="K637" s="3"/>
     </row>
-    <row r="638" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C638" s="3"/>
       <c r="D638" s="3"/>
       <c r="E638" s="3"/>
@@ -10787,7 +10795,7 @@
       <c r="J638" s="3"/>
       <c r="K638" s="3"/>
     </row>
-    <row r="639" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C639" s="3"/>
       <c r="D639" s="3"/>
       <c r="E639" s="3"/>
@@ -10798,7 +10806,7 @@
       <c r="J639" s="3"/>
       <c r="K639" s="3"/>
     </row>
-    <row r="640" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C640" s="3"/>
       <c r="D640" s="3"/>
       <c r="E640" s="3"/>
@@ -10809,7 +10817,7 @@
       <c r="J640" s="3"/>
       <c r="K640" s="3"/>
     </row>
-    <row r="641" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C641" s="3"/>
       <c r="D641" s="3"/>
       <c r="E641" s="3"/>
@@ -10820,7 +10828,7 @@
       <c r="J641" s="3"/>
       <c r="K641" s="3"/>
     </row>
-    <row r="642" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C642" s="3"/>
       <c r="D642" s="3"/>
       <c r="E642" s="3"/>
@@ -10831,7 +10839,7 @@
       <c r="J642" s="3"/>
       <c r="K642" s="3"/>
     </row>
-    <row r="643" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C643" s="3"/>
       <c r="D643" s="3"/>
       <c r="E643" s="3"/>
@@ -10842,7 +10850,7 @@
       <c r="J643" s="3"/>
       <c r="K643" s="3"/>
     </row>
-    <row r="644" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C644" s="3"/>
       <c r="D644" s="3"/>
       <c r="E644" s="3"/>
@@ -10853,7 +10861,7 @@
       <c r="J644" s="3"/>
       <c r="K644" s="3"/>
     </row>
-    <row r="645" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C645" s="3"/>
       <c r="D645" s="3"/>
       <c r="E645" s="3"/>
@@ -10864,7 +10872,7 @@
       <c r="J645" s="3"/>
       <c r="K645" s="3"/>
     </row>
-    <row r="646" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C646" s="3"/>
       <c r="D646" s="3"/>
       <c r="E646" s="3"/>
@@ -10875,7 +10883,7 @@
       <c r="J646" s="3"/>
       <c r="K646" s="3"/>
     </row>
-    <row r="647" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C647" s="3"/>
       <c r="D647" s="3"/>
       <c r="E647" s="3"/>
@@ -10886,7 +10894,7 @@
       <c r="J647" s="3"/>
       <c r="K647" s="3"/>
     </row>
-    <row r="648" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C648" s="3"/>
       <c r="D648" s="3"/>
       <c r="E648" s="3"/>
@@ -10897,7 +10905,7 @@
       <c r="J648" s="3"/>
       <c r="K648" s="3"/>
     </row>
-    <row r="649" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C649" s="3"/>
       <c r="D649" s="3"/>
       <c r="E649" s="3"/>
@@ -10908,7 +10916,7 @@
       <c r="J649" s="3"/>
       <c r="K649" s="3"/>
     </row>
-    <row r="650" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C650" s="3"/>
       <c r="D650" s="3"/>
       <c r="E650" s="3"/>
@@ -10919,7 +10927,7 @@
       <c r="J650" s="3"/>
       <c r="K650" s="3"/>
     </row>
-    <row r="651" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C651" s="3"/>
       <c r="D651" s="3"/>
       <c r="E651" s="3"/>
@@ -10930,7 +10938,7 @@
       <c r="J651" s="3"/>
       <c r="K651" s="3"/>
     </row>
-    <row r="652" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C652" s="3"/>
       <c r="D652" s="3"/>
       <c r="E652" s="3"/>
@@ -10941,7 +10949,7 @@
       <c r="J652" s="3"/>
       <c r="K652" s="3"/>
     </row>
-    <row r="653" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C653" s="3"/>
       <c r="D653" s="3"/>
       <c r="E653" s="3"/>
@@ -10952,7 +10960,7 @@
       <c r="J653" s="3"/>
       <c r="K653" s="3"/>
     </row>
-    <row r="654" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C654" s="3"/>
       <c r="D654" s="3"/>
       <c r="E654" s="3"/>
@@ -10963,7 +10971,7 @@
       <c r="J654" s="3"/>
       <c r="K654" s="3"/>
     </row>
-    <row r="655" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C655" s="3"/>
       <c r="D655" s="3"/>
       <c r="E655" s="3"/>
@@ -10974,7 +10982,7 @@
       <c r="J655" s="3"/>
       <c r="K655" s="3"/>
     </row>
-    <row r="656" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C656" s="3"/>
       <c r="D656" s="3"/>
       <c r="E656" s="3"/>
@@ -10985,7 +10993,7 @@
       <c r="J656" s="3"/>
       <c r="K656" s="3"/>
     </row>
-    <row r="657" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C657" s="3"/>
       <c r="D657" s="3"/>
       <c r="E657" s="3"/>
@@ -10996,7 +11004,7 @@
       <c r="J657" s="3"/>
       <c r="K657" s="3"/>
     </row>
-    <row r="658" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C658" s="3"/>
       <c r="D658" s="3"/>
       <c r="E658" s="3"/>
@@ -11007,7 +11015,7 @@
       <c r="J658" s="3"/>
       <c r="K658" s="3"/>
     </row>
-    <row r="659" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C659" s="3"/>
       <c r="D659" s="3"/>
       <c r="E659" s="3"/>
@@ -11018,7 +11026,7 @@
       <c r="J659" s="3"/>
       <c r="K659" s="3"/>
     </row>
-    <row r="660" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C660" s="3"/>
       <c r="D660" s="3"/>
       <c r="E660" s="3"/>
@@ -11029,7 +11037,7 @@
       <c r="J660" s="3"/>
       <c r="K660" s="3"/>
     </row>
-    <row r="661" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C661" s="3"/>
       <c r="D661" s="3"/>
       <c r="E661" s="3"/>
@@ -11040,7 +11048,7 @@
       <c r="J661" s="3"/>
       <c r="K661" s="3"/>
     </row>
-    <row r="662" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C662" s="3"/>
       <c r="D662" s="3"/>
       <c r="E662" s="3"/>
@@ -11051,7 +11059,7 @@
       <c r="J662" s="3"/>
       <c r="K662" s="3"/>
     </row>
-    <row r="663" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C663" s="3"/>
       <c r="D663" s="3"/>
       <c r="E663" s="3"/>
@@ -11062,7 +11070,7 @@
       <c r="J663" s="3"/>
       <c r="K663" s="3"/>
     </row>
-    <row r="664" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C664" s="3"/>
       <c r="D664" s="3"/>
       <c r="E664" s="3"/>
@@ -11073,7 +11081,7 @@
       <c r="J664" s="3"/>
       <c r="K664" s="3"/>
     </row>
-    <row r="665" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C665" s="3"/>
       <c r="D665" s="3"/>
       <c r="E665" s="3"/>
@@ -11084,7 +11092,7 @@
       <c r="J665" s="3"/>
       <c r="K665" s="3"/>
     </row>
-    <row r="666" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C666" s="3"/>
       <c r="D666" s="3"/>
       <c r="E666" s="3"/>
@@ -11095,7 +11103,7 @@
       <c r="J666" s="3"/>
       <c r="K666" s="3"/>
     </row>
-    <row r="667" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C667" s="3"/>
       <c r="D667" s="3"/>
       <c r="E667" s="3"/>
@@ -11106,7 +11114,7 @@
       <c r="J667" s="3"/>
       <c r="K667" s="3"/>
     </row>
-    <row r="668" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C668" s="3"/>
       <c r="D668" s="3"/>
       <c r="E668" s="3"/>
@@ -11117,7 +11125,7 @@
       <c r="J668" s="3"/>
       <c r="K668" s="3"/>
     </row>
-    <row r="669" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C669" s="3"/>
       <c r="D669" s="3"/>
       <c r="E669" s="3"/>
@@ -11128,7 +11136,7 @@
       <c r="J669" s="3"/>
       <c r="K669" s="3"/>
     </row>
-    <row r="670" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C670" s="3"/>
       <c r="D670" s="3"/>
       <c r="E670" s="3"/>
@@ -11139,7 +11147,7 @@
       <c r="J670" s="3"/>
       <c r="K670" s="3"/>
     </row>
-    <row r="671" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C671" s="3"/>
       <c r="D671" s="3"/>
       <c r="E671" s="3"/>
@@ -11150,7 +11158,7 @@
       <c r="J671" s="3"/>
       <c r="K671" s="3"/>
     </row>
-    <row r="672" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C672" s="3"/>
       <c r="D672" s="3"/>
       <c r="E672" s="3"/>
@@ -11161,7 +11169,7 @@
       <c r="J672" s="3"/>
       <c r="K672" s="3"/>
     </row>
-    <row r="673" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C673" s="3"/>
       <c r="D673" s="3"/>
       <c r="E673" s="3"/>
@@ -11172,7 +11180,7 @@
       <c r="J673" s="3"/>
       <c r="K673" s="3"/>
     </row>
-    <row r="674" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C674" s="3"/>
       <c r="D674" s="3"/>
       <c r="E674" s="3"/>
@@ -11183,7 +11191,7 @@
       <c r="J674" s="3"/>
       <c r="K674" s="3"/>
     </row>
-    <row r="675" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C675" s="3"/>
       <c r="D675" s="3"/>
       <c r="E675" s="3"/>
@@ -11194,7 +11202,7 @@
       <c r="J675" s="3"/>
       <c r="K675" s="3"/>
     </row>
-    <row r="676" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C676" s="3"/>
       <c r="D676" s="3"/>
       <c r="E676" s="3"/>
@@ -11205,7 +11213,7 @@
       <c r="J676" s="3"/>
       <c r="K676" s="3"/>
     </row>
-    <row r="677" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C677" s="3"/>
       <c r="D677" s="3"/>
       <c r="E677" s="3"/>
@@ -11216,7 +11224,7 @@
       <c r="J677" s="3"/>
       <c r="K677" s="3"/>
     </row>
-    <row r="678" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C678" s="3"/>
       <c r="D678" s="3"/>
       <c r="E678" s="3"/>
@@ -11227,7 +11235,7 @@
       <c r="J678" s="3"/>
       <c r="K678" s="3"/>
     </row>
-    <row r="679" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C679" s="3"/>
       <c r="D679" s="3"/>
       <c r="E679" s="3"/>
@@ -11238,7 +11246,7 @@
       <c r="J679" s="3"/>
       <c r="K679" s="3"/>
     </row>
-    <row r="680" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C680" s="3"/>
       <c r="D680" s="3"/>
       <c r="E680" s="3"/>
@@ -11249,7 +11257,7 @@
       <c r="J680" s="3"/>
       <c r="K680" s="3"/>
     </row>
-    <row r="681" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C681" s="3"/>
       <c r="D681" s="3"/>
       <c r="E681" s="3"/>
@@ -11260,7 +11268,7 @@
       <c r="J681" s="3"/>
       <c r="K681" s="3"/>
     </row>
-    <row r="682" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C682" s="3"/>
       <c r="D682" s="3"/>
       <c r="E682" s="3"/>
@@ -11271,7 +11279,7 @@
       <c r="J682" s="3"/>
       <c r="K682" s="3"/>
     </row>
-    <row r="683" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C683" s="3"/>
       <c r="D683" s="3"/>
       <c r="E683" s="3"/>
@@ -11282,7 +11290,7 @@
       <c r="J683" s="3"/>
       <c r="K683" s="3"/>
     </row>
-    <row r="684" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C684" s="3"/>
       <c r="D684" s="3"/>
       <c r="E684" s="3"/>
@@ -11293,7 +11301,7 @@
       <c r="J684" s="3"/>
       <c r="K684" s="3"/>
     </row>
-    <row r="685" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C685" s="3"/>
       <c r="D685" s="3"/>
       <c r="E685" s="3"/>
@@ -11304,7 +11312,7 @@
       <c r="J685" s="3"/>
       <c r="K685" s="3"/>
     </row>
-    <row r="686" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C686" s="3"/>
       <c r="D686" s="3"/>
       <c r="E686" s="3"/>
@@ -11315,7 +11323,7 @@
       <c r="J686" s="3"/>
       <c r="K686" s="3"/>
     </row>
-    <row r="687" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C687" s="3"/>
       <c r="D687" s="3"/>
       <c r="E687" s="3"/>
@@ -11326,7 +11334,7 @@
       <c r="J687" s="3"/>
       <c r="K687" s="3"/>
     </row>
-    <row r="688" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C688" s="3"/>
       <c r="D688" s="3"/>
       <c r="E688" s="3"/>
@@ -11337,7 +11345,7 @@
       <c r="J688" s="3"/>
       <c r="K688" s="3"/>
     </row>
-    <row r="689" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C689" s="3"/>
       <c r="D689" s="3"/>
       <c r="E689" s="3"/>
@@ -11348,7 +11356,7 @@
       <c r="J689" s="3"/>
       <c r="K689" s="3"/>
     </row>
-    <row r="690" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C690" s="3"/>
       <c r="D690" s="3"/>
       <c r="E690" s="3"/>
@@ -11359,7 +11367,7 @@
       <c r="J690" s="3"/>
       <c r="K690" s="3"/>
     </row>
-    <row r="691" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C691" s="3"/>
       <c r="D691" s="3"/>
       <c r="E691" s="3"/>
@@ -11370,7 +11378,7 @@
       <c r="J691" s="3"/>
       <c r="K691" s="3"/>
     </row>
-    <row r="692" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C692" s="3"/>
       <c r="D692" s="3"/>
       <c r="E692" s="3"/>
@@ -11381,7 +11389,7 @@
       <c r="J692" s="3"/>
       <c r="K692" s="3"/>
     </row>
-    <row r="693" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C693" s="3"/>
       <c r="D693" s="3"/>
       <c r="E693" s="3"/>
@@ -11392,7 +11400,7 @@
       <c r="J693" s="3"/>
       <c r="K693" s="3"/>
     </row>
-    <row r="694" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C694" s="3"/>
       <c r="D694" s="3"/>
       <c r="E694" s="3"/>
@@ -11403,7 +11411,7 @@
       <c r="J694" s="3"/>
       <c r="K694" s="3"/>
     </row>
-    <row r="695" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C695" s="3"/>
       <c r="D695" s="3"/>
       <c r="E695" s="3"/>
@@ -11414,7 +11422,7 @@
       <c r="J695" s="3"/>
       <c r="K695" s="3"/>
     </row>
-    <row r="696" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C696" s="3"/>
       <c r="D696" s="3"/>
       <c r="E696" s="3"/>
@@ -11425,7 +11433,7 @@
       <c r="J696" s="3"/>
       <c r="K696" s="3"/>
     </row>
-    <row r="697" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C697" s="3"/>
       <c r="D697" s="3"/>
       <c r="E697" s="3"/>
@@ -11436,7 +11444,7 @@
       <c r="J697" s="3"/>
       <c r="K697" s="3"/>
     </row>
-    <row r="698" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C698" s="3"/>
       <c r="D698" s="3"/>
       <c r="E698" s="3"/>
@@ -11447,7 +11455,7 @@
       <c r="J698" s="3"/>
       <c r="K698" s="3"/>
     </row>
-    <row r="699" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C699" s="3"/>
       <c r="D699" s="3"/>
       <c r="E699" s="3"/>
@@ -11458,7 +11466,7 @@
       <c r="J699" s="3"/>
       <c r="K699" s="3"/>
     </row>
-    <row r="700" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C700" s="3"/>
       <c r="D700" s="3"/>
       <c r="E700" s="3"/>
@@ -11469,7 +11477,7 @@
       <c r="J700" s="3"/>
       <c r="K700" s="3"/>
     </row>
-    <row r="701" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C701" s="3"/>
       <c r="D701" s="3"/>
       <c r="E701" s="3"/>
@@ -11480,7 +11488,7 @@
       <c r="J701" s="3"/>
       <c r="K701" s="3"/>
     </row>
-    <row r="702" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C702" s="3"/>
       <c r="D702" s="3"/>
       <c r="E702" s="3"/>
@@ -11491,7 +11499,7 @@
       <c r="J702" s="3"/>
       <c r="K702" s="3"/>
     </row>
-    <row r="703" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C703" s="3"/>
       <c r="D703" s="3"/>
       <c r="E703" s="3"/>
@@ -11502,7 +11510,7 @@
       <c r="J703" s="3"/>
       <c r="K703" s="3"/>
     </row>
-    <row r="704" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C704" s="3"/>
       <c r="D704" s="3"/>
       <c r="E704" s="3"/>
@@ -11513,7 +11521,7 @@
       <c r="J704" s="3"/>
       <c r="K704" s="3"/>
     </row>
-    <row r="705" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C705" s="3"/>
       <c r="D705" s="3"/>
       <c r="E705" s="3"/>
@@ -11524,7 +11532,7 @@
       <c r="J705" s="3"/>
       <c r="K705" s="3"/>
     </row>
-    <row r="706" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C706" s="3"/>
       <c r="D706" s="3"/>
       <c r="E706" s="3"/>
@@ -11535,7 +11543,7 @@
       <c r="J706" s="3"/>
       <c r="K706" s="3"/>
     </row>
-    <row r="707" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C707" s="3"/>
       <c r="D707" s="3"/>
       <c r="E707" s="3"/>
@@ -11546,7 +11554,7 @@
       <c r="J707" s="3"/>
       <c r="K707" s="3"/>
     </row>
-    <row r="708" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C708" s="3"/>
       <c r="D708" s="3"/>
       <c r="E708" s="3"/>
@@ -11557,7 +11565,7 @@
       <c r="J708" s="3"/>
       <c r="K708" s="3"/>
     </row>
-    <row r="709" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C709" s="3"/>
       <c r="D709" s="3"/>
       <c r="E709" s="3"/>
@@ -11568,7 +11576,7 @@
       <c r="J709" s="3"/>
       <c r="K709" s="3"/>
     </row>
-    <row r="710" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C710" s="3"/>
       <c r="D710" s="3"/>
       <c r="E710" s="3"/>
@@ -11579,7 +11587,7 @@
       <c r="J710" s="3"/>
       <c r="K710" s="3"/>
     </row>
-    <row r="711" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C711" s="3"/>
       <c r="D711" s="3"/>
       <c r="E711" s="3"/>
@@ -11590,7 +11598,7 @@
       <c r="J711" s="3"/>
       <c r="K711" s="3"/>
     </row>
-    <row r="712" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C712" s="3"/>
       <c r="D712" s="3"/>
       <c r="E712" s="3"/>
@@ -11601,7 +11609,7 @@
       <c r="J712" s="3"/>
       <c r="K712" s="3"/>
     </row>
-    <row r="713" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C713" s="3"/>
       <c r="D713" s="3"/>
       <c r="E713" s="3"/>
@@ -11612,7 +11620,7 @@
       <c r="J713" s="3"/>
       <c r="K713" s="3"/>
     </row>
-    <row r="714" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C714" s="3"/>
       <c r="D714" s="3"/>
       <c r="E714" s="3"/>
@@ -11623,7 +11631,7 @@
       <c r="J714" s="3"/>
       <c r="K714" s="3"/>
     </row>
-    <row r="715" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C715" s="3"/>
       <c r="D715" s="3"/>
       <c r="E715" s="3"/>
@@ -11634,7 +11642,7 @@
       <c r="J715" s="3"/>
       <c r="K715" s="3"/>
     </row>
-    <row r="716" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C716" s="3"/>
       <c r="D716" s="3"/>
       <c r="E716" s="3"/>
@@ -11645,7 +11653,7 @@
       <c r="J716" s="3"/>
       <c r="K716" s="3"/>
     </row>
-    <row r="717" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C717" s="3"/>
       <c r="D717" s="3"/>
       <c r="E717" s="3"/>
@@ -11656,7 +11664,7 @@
       <c r="J717" s="3"/>
       <c r="K717" s="3"/>
     </row>
-    <row r="718" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C718" s="3"/>
       <c r="D718" s="3"/>
       <c r="E718" s="3"/>
@@ -11667,7 +11675,7 @@
       <c r="J718" s="3"/>
       <c r="K718" s="3"/>
     </row>
-    <row r="719" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C719" s="3"/>
       <c r="D719" s="3"/>
       <c r="E719" s="3"/>
@@ -11678,7 +11686,7 @@
       <c r="J719" s="3"/>
       <c r="K719" s="3"/>
     </row>
-    <row r="720" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C720" s="3"/>
       <c r="D720" s="3"/>
       <c r="E720" s="3"/>
@@ -11689,7 +11697,7 @@
       <c r="J720" s="3"/>
       <c r="K720" s="3"/>
     </row>
-    <row r="721" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C721" s="3"/>
       <c r="D721" s="3"/>
       <c r="E721" s="3"/>
@@ -11700,7 +11708,7 @@
       <c r="J721" s="3"/>
       <c r="K721" s="3"/>
     </row>
-    <row r="722" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C722" s="3"/>
       <c r="D722" s="3"/>
       <c r="E722" s="3"/>
@@ -11711,7 +11719,7 @@
       <c r="J722" s="3"/>
       <c r="K722" s="3"/>
     </row>
-    <row r="723" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C723" s="3"/>
       <c r="D723" s="3"/>
       <c r="E723" s="3"/>
@@ -11722,7 +11730,7 @@
       <c r="J723" s="3"/>
       <c r="K723" s="3"/>
     </row>
-    <row r="724" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C724" s="3"/>
       <c r="D724" s="3"/>
       <c r="E724" s="3"/>
@@ -11733,7 +11741,7 @@
       <c r="J724" s="3"/>
       <c r="K724" s="3"/>
     </row>
-    <row r="725" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C725" s="3"/>
       <c r="D725" s="3"/>
       <c r="E725" s="3"/>
@@ -11744,7 +11752,7 @@
       <c r="J725" s="3"/>
       <c r="K725" s="3"/>
     </row>
-    <row r="726" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C726" s="3"/>
       <c r="D726" s="3"/>
       <c r="E726" s="3"/>
@@ -11755,7 +11763,7 @@
       <c r="J726" s="3"/>
       <c r="K726" s="3"/>
     </row>
-    <row r="727" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C727" s="3"/>
       <c r="D727" s="3"/>
       <c r="E727" s="3"/>
@@ -11766,7 +11774,7 @@
       <c r="J727" s="3"/>
       <c r="K727" s="3"/>
     </row>
-    <row r="728" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C728" s="3"/>
       <c r="D728" s="3"/>
       <c r="E728" s="3"/>
@@ -11777,7 +11785,7 @@
       <c r="J728" s="3"/>
       <c r="K728" s="3"/>
     </row>
-    <row r="729" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C729" s="3"/>
       <c r="D729" s="3"/>
       <c r="E729" s="3"/>
@@ -11788,7 +11796,7 @@
       <c r="J729" s="3"/>
       <c r="K729" s="3"/>
     </row>
-    <row r="730" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C730" s="3"/>
       <c r="D730" s="3"/>
       <c r="E730" s="3"/>
@@ -11799,7 +11807,7 @@
       <c r="J730" s="3"/>
       <c r="K730" s="3"/>
     </row>
-    <row r="731" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C731" s="3"/>
       <c r="D731" s="3"/>
       <c r="E731" s="3"/>
@@ -11810,7 +11818,7 @@
       <c r="J731" s="3"/>
       <c r="K731" s="3"/>
     </row>
-    <row r="732" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C732" s="3"/>
       <c r="D732" s="3"/>
       <c r="E732" s="3"/>
@@ -11821,7 +11829,7 @@
       <c r="J732" s="3"/>
       <c r="K732" s="3"/>
     </row>
-    <row r="733" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C733" s="3"/>
       <c r="D733" s="3"/>
       <c r="E733" s="3"/>
@@ -11832,7 +11840,7 @@
       <c r="J733" s="3"/>
       <c r="K733" s="3"/>
     </row>
-    <row r="734" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C734" s="3"/>
       <c r="D734" s="3"/>
       <c r="E734" s="3"/>
@@ -11843,7 +11851,7 @@
       <c r="J734" s="3"/>
       <c r="K734" s="3"/>
     </row>
-    <row r="735" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C735" s="3"/>
       <c r="D735" s="3"/>
       <c r="E735" s="3"/>
@@ -11854,7 +11862,7 @@
       <c r="J735" s="3"/>
       <c r="K735" s="3"/>
     </row>
-    <row r="736" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C736" s="3"/>
       <c r="D736" s="3"/>
       <c r="E736" s="3"/>
@@ -11865,7 +11873,7 @@
       <c r="J736" s="3"/>
       <c r="K736" s="3"/>
     </row>
-    <row r="737" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C737" s="3"/>
       <c r="D737" s="3"/>
       <c r="E737" s="3"/>
@@ -11876,7 +11884,7 @@
       <c r="J737" s="3"/>
       <c r="K737" s="3"/>
     </row>
-    <row r="738" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C738" s="3"/>
       <c r="D738" s="3"/>
       <c r="E738" s="3"/>
@@ -11887,7 +11895,7 @@
       <c r="J738" s="3"/>
       <c r="K738" s="3"/>
     </row>
-    <row r="739" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C739" s="3"/>
       <c r="D739" s="3"/>
       <c r="E739" s="3"/>
@@ -11898,7 +11906,7 @@
       <c r="J739" s="3"/>
       <c r="K739" s="3"/>
     </row>
-    <row r="740" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C740" s="3"/>
       <c r="D740" s="3"/>
       <c r="E740" s="3"/>
@@ -11909,7 +11917,7 @@
       <c r="J740" s="3"/>
       <c r="K740" s="3"/>
     </row>
-    <row r="741" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C741" s="3"/>
       <c r="D741" s="3"/>
       <c r="E741" s="3"/>
@@ -11920,7 +11928,7 @@
       <c r="J741" s="3"/>
       <c r="K741" s="3"/>
     </row>
-    <row r="742" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C742" s="3"/>
       <c r="D742" s="3"/>
       <c r="E742" s="3"/>
@@ -11931,7 +11939,7 @@
       <c r="J742" s="3"/>
       <c r="K742" s="3"/>
     </row>
-    <row r="743" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C743" s="3"/>
       <c r="D743" s="3"/>
       <c r="E743" s="3"/>
@@ -11942,7 +11950,7 @@
       <c r="J743" s="3"/>
       <c r="K743" s="3"/>
     </row>
-    <row r="744" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C744" s="3"/>
       <c r="D744" s="3"/>
       <c r="E744" s="3"/>
@@ -11953,7 +11961,7 @@
       <c r="J744" s="3"/>
       <c r="K744" s="3"/>
     </row>
-    <row r="745" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C745" s="3"/>
       <c r="D745" s="3"/>
       <c r="E745" s="3"/>
@@ -11964,7 +11972,7 @@
       <c r="J745" s="3"/>
       <c r="K745" s="3"/>
     </row>
-    <row r="746" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C746" s="3"/>
       <c r="D746" s="3"/>
       <c r="E746" s="3"/>
@@ -11975,7 +11983,7 @@
       <c r="J746" s="3"/>
       <c r="K746" s="3"/>
     </row>
-    <row r="747" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C747" s="3"/>
       <c r="D747" s="3"/>
       <c r="E747" s="3"/>
@@ -11986,7 +11994,7 @@
       <c r="J747" s="3"/>
       <c r="K747" s="3"/>
     </row>
-    <row r="748" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C748" s="3"/>
       <c r="D748" s="3"/>
       <c r="E748" s="3"/>
@@ -11997,7 +12005,7 @@
       <c r="J748" s="3"/>
       <c r="K748" s="3"/>
     </row>
-    <row r="749" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C749" s="3"/>
       <c r="D749" s="3"/>
       <c r="E749" s="3"/>
@@ -12008,7 +12016,7 @@
       <c r="J749" s="3"/>
       <c r="K749" s="3"/>
     </row>
-    <row r="750" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C750" s="3"/>
       <c r="D750" s="3"/>
       <c r="E750" s="3"/>
@@ -12019,7 +12027,7 @@
       <c r="J750" s="3"/>
       <c r="K750" s="3"/>
     </row>
-    <row r="751" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C751" s="3"/>
       <c r="D751" s="3"/>
       <c r="E751" s="3"/>
@@ -12030,7 +12038,7 @@
       <c r="J751" s="3"/>
       <c r="K751" s="3"/>
     </row>
-    <row r="752" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C752" s="3"/>
       <c r="D752" s="3"/>
       <c r="E752" s="3"/>
@@ -12041,7 +12049,7 @@
       <c r="J752" s="3"/>
       <c r="K752" s="3"/>
     </row>
-    <row r="753" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C753" s="3"/>
       <c r="D753" s="3"/>
       <c r="E753" s="3"/>
@@ -12052,7 +12060,7 @@
       <c r="J753" s="3"/>
       <c r="K753" s="3"/>
     </row>
-    <row r="754" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C754" s="3"/>
       <c r="D754" s="3"/>
       <c r="E754" s="3"/>
@@ -12063,7 +12071,7 @@
       <c r="J754" s="3"/>
       <c r="K754" s="3"/>
     </row>
-    <row r="755" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C755" s="3"/>
       <c r="D755" s="3"/>
       <c r="E755" s="3"/>
@@ -12074,7 +12082,7 @@
       <c r="J755" s="3"/>
       <c r="K755" s="3"/>
     </row>
-    <row r="756" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C756" s="3"/>
       <c r="D756" s="3"/>
       <c r="E756" s="3"/>
@@ -12085,7 +12093,7 @@
       <c r="J756" s="3"/>
       <c r="K756" s="3"/>
     </row>
-    <row r="757" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C757" s="3"/>
       <c r="D757" s="3"/>
       <c r="E757" s="3"/>
@@ -12096,7 +12104,7 @@
       <c r="J757" s="3"/>
       <c r="K757" s="3"/>
     </row>
-    <row r="758" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C758" s="3"/>
       <c r="D758" s="3"/>
       <c r="E758" s="3"/>
@@ -12107,7 +12115,7 @@
       <c r="J758" s="3"/>
       <c r="K758" s="3"/>
     </row>
-    <row r="759" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C759" s="3"/>
       <c r="D759" s="3"/>
       <c r="E759" s="3"/>
@@ -12118,7 +12126,7 @@
       <c r="J759" s="3"/>
       <c r="K759" s="3"/>
     </row>
-    <row r="760" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C760" s="3"/>
       <c r="D760" s="3"/>
       <c r="E760" s="3"/>
@@ -12129,7 +12137,7 @@
       <c r="J760" s="3"/>
       <c r="K760" s="3"/>
     </row>
-    <row r="761" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C761" s="3"/>
       <c r="D761" s="3"/>
       <c r="E761" s="3"/>
@@ -12140,7 +12148,7 @@
       <c r="J761" s="3"/>
       <c r="K761" s="3"/>
     </row>
-    <row r="762" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C762" s="3"/>
       <c r="D762" s="3"/>
       <c r="E762" s="3"/>
@@ -12151,7 +12159,7 @@
       <c r="J762" s="3"/>
       <c r="K762" s="3"/>
     </row>
-    <row r="763" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C763" s="3"/>
       <c r="D763" s="3"/>
       <c r="E763" s="3"/>
@@ -12162,7 +12170,7 @@
       <c r="J763" s="3"/>
       <c r="K763" s="3"/>
     </row>
-    <row r="764" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C764" s="3"/>
       <c r="D764" s="3"/>
       <c r="E764" s="3"/>
@@ -12173,7 +12181,7 @@
       <c r="J764" s="3"/>
       <c r="K764" s="3"/>
     </row>
-    <row r="765" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C765" s="3"/>
       <c r="D765" s="3"/>
       <c r="E765" s="3"/>
@@ -12184,7 +12192,7 @@
       <c r="J765" s="3"/>
       <c r="K765" s="3"/>
     </row>
-    <row r="766" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C766" s="3"/>
       <c r="D766" s="3"/>
       <c r="E766" s="3"/>
@@ -12195,7 +12203,7 @@
       <c r="J766" s="3"/>
       <c r="K766" s="3"/>
     </row>
-    <row r="767" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C767" s="3"/>
       <c r="D767" s="3"/>
       <c r="E767" s="3"/>
@@ -12206,7 +12214,7 @@
       <c r="J767" s="3"/>
       <c r="K767" s="3"/>
     </row>
-    <row r="768" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C768" s="3"/>
       <c r="D768" s="3"/>
       <c r="E768" s="3"/>
@@ -12217,7 +12225,7 @@
       <c r="J768" s="3"/>
       <c r="K768" s="3"/>
     </row>
-    <row r="769" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C769" s="3"/>
       <c r="D769" s="3"/>
       <c r="E769" s="3"/>
@@ -12228,7 +12236,7 @@
       <c r="J769" s="3"/>
       <c r="K769" s="3"/>
     </row>
-    <row r="770" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C770" s="3"/>
       <c r="D770" s="3"/>
       <c r="E770" s="3"/>
@@ -12239,7 +12247,7 @@
       <c r="J770" s="3"/>
       <c r="K770" s="3"/>
     </row>
-    <row r="771" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C771" s="3"/>
       <c r="D771" s="3"/>
       <c r="E771" s="3"/>
@@ -12250,7 +12258,7 @@
       <c r="J771" s="3"/>
       <c r="K771" s="3"/>
     </row>
-    <row r="772" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C772" s="3"/>
       <c r="D772" s="3"/>
       <c r="E772" s="3"/>
@@ -12261,7 +12269,7 @@
       <c r="J772" s="3"/>
       <c r="K772" s="3"/>
     </row>
-    <row r="773" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C773" s="3"/>
       <c r="D773" s="3"/>
       <c r="E773" s="3"/>
@@ -12272,7 +12280,7 @@
       <c r="J773" s="3"/>
       <c r="K773" s="3"/>
     </row>
-    <row r="774" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C774" s="3"/>
       <c r="D774" s="3"/>
       <c r="E774" s="3"/>
@@ -12283,7 +12291,7 @@
       <c r="J774" s="3"/>
       <c r="K774" s="3"/>
     </row>
-    <row r="775" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C775" s="3"/>
       <c r="D775" s="3"/>
       <c r="E775" s="3"/>
@@ -12294,7 +12302,7 @@
       <c r="J775" s="3"/>
       <c r="K775" s="3"/>
     </row>
-    <row r="776" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C776" s="3"/>
       <c r="D776" s="3"/>
       <c r="E776" s="3"/>
@@ -12305,7 +12313,7 @@
       <c r="J776" s="3"/>
       <c r="K776" s="3"/>
     </row>
-    <row r="777" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C777" s="3"/>
       <c r="D777" s="3"/>
       <c r="E777" s="3"/>
@@ -12316,7 +12324,7 @@
       <c r="J777" s="3"/>
       <c r="K777" s="3"/>
     </row>
-    <row r="778" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C778" s="3"/>
       <c r="D778" s="3"/>
       <c r="E778" s="3"/>
@@ -12327,7 +12335,7 @@
       <c r="J778" s="3"/>
       <c r="K778" s="3"/>
     </row>
-    <row r="779" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C779" s="3"/>
       <c r="D779" s="3"/>
       <c r="E779" s="3"/>
@@ -12338,7 +12346,7 @@
       <c r="J779" s="3"/>
       <c r="K779" s="3"/>
     </row>
-    <row r="780" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C780" s="3"/>
       <c r="D780" s="3"/>
       <c r="E780" s="3"/>
@@ -12349,7 +12357,7 @@
       <c r="J780" s="3"/>
       <c r="K780" s="3"/>
     </row>
-    <row r="781" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C781" s="3"/>
       <c r="D781" s="3"/>
       <c r="E781" s="3"/>
@@ -12360,7 +12368,7 @@
       <c r="J781" s="3"/>
       <c r="K781" s="3"/>
     </row>
-    <row r="782" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C782" s="3"/>
       <c r="D782" s="3"/>
       <c r="E782" s="3"/>
@@ -12371,7 +12379,7 @@
       <c r="J782" s="3"/>
       <c r="K782" s="3"/>
     </row>
-    <row r="783" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C783" s="3"/>
       <c r="D783" s="3"/>
       <c r="E783" s="3"/>
@@ -12382,7 +12390,7 @@
       <c r="J783" s="3"/>
       <c r="K783" s="3"/>
     </row>
-    <row r="784" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C784" s="3"/>
       <c r="D784" s="3"/>
       <c r="E784" s="3"/>
@@ -12393,7 +12401,7 @@
       <c r="J784" s="3"/>
       <c r="K784" s="3"/>
     </row>
-    <row r="785" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C785" s="3"/>
       <c r="D785" s="3"/>
       <c r="E785" s="3"/>
@@ -12404,7 +12412,7 @@
       <c r="J785" s="3"/>
       <c r="K785" s="3"/>
     </row>
-    <row r="786" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C786" s="3"/>
       <c r="D786" s="3"/>
       <c r="E786" s="3"/>
@@ -12415,7 +12423,7 @@
       <c r="J786" s="3"/>
       <c r="K786" s="3"/>
     </row>
-    <row r="787" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C787" s="3"/>
       <c r="D787" s="3"/>
       <c r="E787" s="3"/>
@@ -12426,7 +12434,7 @@
       <c r="J787" s="3"/>
       <c r="K787" s="3"/>
     </row>
-    <row r="788" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C788" s="3"/>
       <c r="D788" s="3"/>
       <c r="E788" s="3"/>
@@ -12437,7 +12445,7 @@
       <c r="J788" s="3"/>
       <c r="K788" s="3"/>
     </row>
-    <row r="789" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C789" s="3"/>
       <c r="D789" s="3"/>
       <c r="E789" s="3"/>
@@ -12448,7 +12456,7 @@
       <c r="J789" s="3"/>
       <c r="K789" s="3"/>
     </row>
-    <row r="790" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C790" s="3"/>
       <c r="D790" s="3"/>
       <c r="E790" s="3"/>
@@ -12459,7 +12467,7 @@
       <c r="J790" s="3"/>
       <c r="K790" s="3"/>
     </row>
-    <row r="791" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C791" s="3"/>
       <c r="D791" s="3"/>
       <c r="E791" s="3"/>
@@ -12470,7 +12478,7 @@
       <c r="J791" s="3"/>
       <c r="K791" s="3"/>
     </row>
-    <row r="792" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C792" s="3"/>
       <c r="D792" s="3"/>
       <c r="E792" s="3"/>
@@ -12481,7 +12489,7 @@
       <c r="J792" s="3"/>
       <c r="K792" s="3"/>
     </row>
-    <row r="793" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C793" s="3"/>
       <c r="D793" s="3"/>
       <c r="E793" s="3"/>
@@ -12492,7 +12500,7 @@
       <c r="J793" s="3"/>
       <c r="K793" s="3"/>
     </row>
-    <row r="794" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C794" s="3"/>
       <c r="D794" s="3"/>
       <c r="E794" s="3"/>
@@ -12503,7 +12511,7 @@
       <c r="J794" s="3"/>
       <c r="K794" s="3"/>
     </row>
-    <row r="795" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C795" s="3"/>
       <c r="D795" s="3"/>
       <c r="E795" s="3"/>
@@ -12514,7 +12522,7 @@
       <c r="J795" s="3"/>
       <c r="K795" s="3"/>
     </row>
-    <row r="796" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C796" s="3"/>
       <c r="D796" s="3"/>
       <c r="E796" s="3"/>
@@ -12525,7 +12533,7 @@
       <c r="J796" s="3"/>
       <c r="K796" s="3"/>
     </row>
-    <row r="797" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C797" s="3"/>
       <c r="D797" s="3"/>
       <c r="E797" s="3"/>
@@ -12536,7 +12544,7 @@
       <c r="J797" s="3"/>
       <c r="K797" s="3"/>
     </row>
-    <row r="798" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C798" s="3"/>
       <c r="D798" s="3"/>
       <c r="E798" s="3"/>
@@ -12547,7 +12555,7 @@
       <c r="J798" s="3"/>
       <c r="K798" s="3"/>
     </row>
-    <row r="799" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C799" s="3"/>
       <c r="D799" s="3"/>
       <c r="E799" s="3"/>
@@ -12558,7 +12566,7 @@
       <c r="J799" s="3"/>
       <c r="K799" s="3"/>
     </row>
-    <row r="800" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C800" s="3"/>
       <c r="D800" s="3"/>
       <c r="E800" s="3"/>
@@ -12569,7 +12577,7 @@
       <c r="J800" s="3"/>
       <c r="K800" s="3"/>
     </row>
-    <row r="801" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C801" s="3"/>
       <c r="D801" s="3"/>
       <c r="E801" s="3"/>
@@ -12580,7 +12588,7 @@
       <c r="J801" s="3"/>
       <c r="K801" s="3"/>
     </row>
-    <row r="802" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C802" s="3"/>
       <c r="D802" s="3"/>
       <c r="E802" s="3"/>
@@ -12591,7 +12599,7 @@
       <c r="J802" s="3"/>
       <c r="K802" s="3"/>
     </row>
-    <row r="803" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C803" s="3"/>
       <c r="D803" s="3"/>
       <c r="E803" s="3"/>
@@ -12602,7 +12610,7 @@
       <c r="J803" s="3"/>
       <c r="K803" s="3"/>
     </row>
-    <row r="804" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C804" s="3"/>
       <c r="D804" s="3"/>
       <c r="E804" s="3"/>
@@ -12613,7 +12621,7 @@
       <c r="J804" s="3"/>
       <c r="K804" s="3"/>
     </row>
-    <row r="805" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C805" s="3"/>
       <c r="D805" s="3"/>
       <c r="E805" s="3"/>
@@ -12624,7 +12632,7 @@
       <c r="J805" s="3"/>
       <c r="K805" s="3"/>
     </row>
-    <row r="806" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C806" s="3"/>
       <c r="D806" s="3"/>
       <c r="E806" s="3"/>
@@ -12635,7 +12643,7 @@
       <c r="J806" s="3"/>
       <c r="K806" s="3"/>
     </row>
-    <row r="807" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C807" s="3"/>
       <c r="D807" s="3"/>
       <c r="E807" s="3"/>
@@ -12646,7 +12654,7 @@
       <c r="J807" s="3"/>
       <c r="K807" s="3"/>
     </row>
-    <row r="808" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C808" s="3"/>
       <c r="D808" s="3"/>
       <c r="E808" s="3"/>
@@ -12657,7 +12665,7 @@
       <c r="J808" s="3"/>
       <c r="K808" s="3"/>
     </row>
-    <row r="809" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C809" s="3"/>
       <c r="D809" s="3"/>
       <c r="E809" s="3"/>
@@ -12668,7 +12676,7 @@
       <c r="J809" s="3"/>
       <c r="K809" s="3"/>
     </row>
-    <row r="810" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C810" s="3"/>
       <c r="D810" s="3"/>
       <c r="E810" s="3"/>
@@ -12679,7 +12687,7 @@
       <c r="J810" s="3"/>
       <c r="K810" s="3"/>
     </row>
-    <row r="811" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C811" s="3"/>
       <c r="D811" s="3"/>
       <c r="E811" s="3"/>
@@ -12690,7 +12698,7 @@
       <c r="J811" s="3"/>
       <c r="K811" s="3"/>
     </row>
-    <row r="812" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C812" s="3"/>
       <c r="D812" s="3"/>
       <c r="E812" s="3"/>
@@ -12701,7 +12709,7 @@
       <c r="J812" s="3"/>
       <c r="K812" s="3"/>
     </row>
-    <row r="813" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C813" s="3"/>
       <c r="D813" s="3"/>
       <c r="E813" s="3"/>
@@ -12712,7 +12720,7 @@
       <c r="J813" s="3"/>
       <c r="K813" s="3"/>
     </row>
-    <row r="814" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C814" s="3"/>
       <c r="D814" s="3"/>
       <c r="E814" s="3"/>
@@ -12723,7 +12731,7 @@
       <c r="J814" s="3"/>
       <c r="K814" s="3"/>
     </row>
-    <row r="815" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C815" s="3"/>
       <c r="D815" s="3"/>
       <c r="E815" s="3"/>
@@ -12734,7 +12742,7 @@
       <c r="J815" s="3"/>
       <c r="K815" s="3"/>
     </row>
-    <row r="816" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C816" s="3"/>
       <c r="D816" s="3"/>
       <c r="E816" s="3"/>
@@ -12745,7 +12753,7 @@
       <c r="J816" s="3"/>
       <c r="K816" s="3"/>
     </row>
-    <row r="817" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C817" s="3"/>
       <c r="D817" s="3"/>
       <c r="E817" s="3"/>
@@ -12756,7 +12764,7 @@
       <c r="J817" s="3"/>
       <c r="K817" s="3"/>
     </row>
-    <row r="818" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C818" s="3"/>
       <c r="D818" s="3"/>
       <c r="E818" s="3"/>
@@ -12767,7 +12775,7 @@
       <c r="J818" s="3"/>
       <c r="K818" s="3"/>
     </row>
-    <row r="819" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C819" s="3"/>
       <c r="D819" s="3"/>
       <c r="E819" s="3"/>
@@ -12778,7 +12786,7 @@
       <c r="J819" s="3"/>
       <c r="K819" s="3"/>
     </row>
-    <row r="820" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C820" s="3"/>
       <c r="D820" s="3"/>
       <c r="E820" s="3"/>
@@ -12789,7 +12797,7 @@
       <c r="J820" s="3"/>
       <c r="K820" s="3"/>
     </row>
-    <row r="821" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C821" s="3"/>
       <c r="D821" s="3"/>
       <c r="E821" s="3"/>
@@ -12800,7 +12808,7 @@
       <c r="J821" s="3"/>
       <c r="K821" s="3"/>
     </row>
-    <row r="822" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C822" s="3"/>
       <c r="D822" s="3"/>
       <c r="E822" s="3"/>
@@ -12811,7 +12819,7 @@
       <c r="J822" s="3"/>
       <c r="K822" s="3"/>
     </row>
-    <row r="823" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C823" s="3"/>
       <c r="D823" s="3"/>
       <c r="E823" s="3"/>
@@ -12822,7 +12830,7 @@
       <c r="J823" s="3"/>
       <c r="K823" s="3"/>
     </row>
-    <row r="824" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C824" s="3"/>
       <c r="D824" s="3"/>
       <c r="E824" s="3"/>
@@ -12833,7 +12841,7 @@
       <c r="J824" s="3"/>
       <c r="K824" s="3"/>
     </row>
-    <row r="825" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C825" s="3"/>
       <c r="D825" s="3"/>
       <c r="E825" s="3"/>
@@ -12844,7 +12852,7 @@
       <c r="J825" s="3"/>
       <c r="K825" s="3"/>
     </row>
-    <row r="826" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C826" s="3"/>
       <c r="D826" s="3"/>
       <c r="E826" s="3"/>
@@ -12855,7 +12863,7 @@
       <c r="J826" s="3"/>
       <c r="K826" s="3"/>
     </row>
-    <row r="827" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C827" s="3"/>
       <c r="D827" s="3"/>
       <c r="E827" s="3"/>
@@ -12866,7 +12874,7 @@
       <c r="J827" s="3"/>
       <c r="K827" s="3"/>
     </row>
-    <row r="828" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C828" s="3"/>
       <c r="D828" s="3"/>
       <c r="E828" s="3"/>
@@ -12877,7 +12885,7 @@
       <c r="J828" s="3"/>
       <c r="K828" s="3"/>
     </row>
-    <row r="829" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C829" s="3"/>
       <c r="D829" s="3"/>
       <c r="E829" s="3"/>
@@ -12888,7 +12896,7 @@
       <c r="J829" s="3"/>
       <c r="K829" s="3"/>
     </row>
-    <row r="830" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C830" s="3"/>
       <c r="D830" s="3"/>
       <c r="E830" s="3"/>
@@ -12899,7 +12907,7 @@
       <c r="J830" s="3"/>
       <c r="K830" s="3"/>
     </row>
-    <row r="831" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C831" s="3"/>
       <c r="D831" s="3"/>
       <c r="E831" s="3"/>
@@ -12910,7 +12918,7 @@
       <c r="J831" s="3"/>
       <c r="K831" s="3"/>
     </row>
-    <row r="832" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C832" s="3"/>
       <c r="D832" s="3"/>
       <c r="E832" s="3"/>
@@ -12921,7 +12929,7 @@
       <c r="J832" s="3"/>
       <c r="K832" s="3"/>
     </row>
-    <row r="833" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C833" s="3"/>
       <c r="D833" s="3"/>
       <c r="E833" s="3"/>
@@ -12932,7 +12940,7 @@
       <c r="J833" s="3"/>
       <c r="K833" s="3"/>
     </row>
-    <row r="834" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C834" s="3"/>
       <c r="D834" s="3"/>
       <c r="E834" s="3"/>
@@ -12943,7 +12951,7 @@
       <c r="J834" s="3"/>
       <c r="K834" s="3"/>
     </row>
-    <row r="835" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C835" s="3"/>
       <c r="D835" s="3"/>
       <c r="E835" s="3"/>
@@ -12954,7 +12962,7 @@
       <c r="J835" s="3"/>
       <c r="K835" s="3"/>
     </row>
-    <row r="836" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C836" s="3"/>
       <c r="D836" s="3"/>
       <c r="E836" s="3"/>
@@ -12965,7 +12973,7 @@
       <c r="J836" s="3"/>
       <c r="K836" s="3"/>
     </row>
-    <row r="837" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C837" s="3"/>
       <c r="D837" s="3"/>
       <c r="E837" s="3"/>
@@ -12976,7 +12984,7 @@
       <c r="J837" s="3"/>
       <c r="K837" s="3"/>
     </row>
-    <row r="838" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C838" s="3"/>
       <c r="D838" s="3"/>
       <c r="E838" s="3"/>
@@ -12987,7 +12995,7 @@
       <c r="J838" s="3"/>
       <c r="K838" s="3"/>
     </row>
-    <row r="839" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C839" s="3"/>
       <c r="D839" s="3"/>
       <c r="E839" s="3"/>
@@ -12998,7 +13006,7 @@
       <c r="J839" s="3"/>
       <c r="K839" s="3"/>
     </row>
-    <row r="840" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C840" s="3"/>
       <c r="D840" s="3"/>
       <c r="E840" s="3"/>
@@ -13009,7 +13017,7 @@
       <c r="J840" s="3"/>
       <c r="K840" s="3"/>
     </row>
-    <row r="841" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C841" s="3"/>
       <c r="D841" s="3"/>
       <c r="E841" s="3"/>
@@ -13020,7 +13028,7 @@
       <c r="J841" s="3"/>
       <c r="K841" s="3"/>
     </row>
-    <row r="842" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C842" s="3"/>
       <c r="D842" s="3"/>
       <c r="E842" s="3"/>
@@ -13031,7 +13039,7 @@
       <c r="J842" s="3"/>
       <c r="K842" s="3"/>
     </row>
-    <row r="843" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C843" s="3"/>
       <c r="D843" s="3"/>
       <c r="E843" s="3"/>
@@ -13042,7 +13050,7 @@
       <c r="J843" s="3"/>
       <c r="K843" s="3"/>
     </row>
-    <row r="844" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C844" s="3"/>
       <c r="D844" s="3"/>
       <c r="E844" s="3"/>
@@ -13053,7 +13061,7 @@
       <c r="J844" s="3"/>
       <c r="K844" s="3"/>
     </row>
-    <row r="845" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C845" s="3"/>
       <c r="D845" s="3"/>
       <c r="E845" s="3"/>
@@ -13064,7 +13072,7 @@
       <c r="J845" s="3"/>
       <c r="K845" s="3"/>
     </row>
-    <row r="846" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C846" s="3"/>
       <c r="D846" s="3"/>
       <c r="E846" s="3"/>
@@ -13075,7 +13083,7 @@
       <c r="J846" s="3"/>
       <c r="K846" s="3"/>
     </row>
-    <row r="847" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C847" s="3"/>
       <c r="D847" s="3"/>
       <c r="E847" s="3"/>
@@ -13086,7 +13094,7 @@
       <c r="J847" s="3"/>
       <c r="K847" s="3"/>
     </row>
-    <row r="848" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C848" s="3"/>
       <c r="D848" s="3"/>
       <c r="E848" s="3"/>
@@ -13097,7 +13105,7 @@
       <c r="J848" s="3"/>
       <c r="K848" s="3"/>
     </row>
-    <row r="849" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C849" s="3"/>
       <c r="D849" s="3"/>
       <c r="E849" s="3"/>
@@ -13108,7 +13116,7 @@
       <c r="J849" s="3"/>
       <c r="K849" s="3"/>
     </row>
-    <row r="850" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C850" s="3"/>
       <c r="D850" s="3"/>
       <c r="E850" s="3"/>
@@ -13119,7 +13127,7 @@
       <c r="J850" s="3"/>
       <c r="K850" s="3"/>
     </row>
-    <row r="851" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C851" s="3"/>
       <c r="D851" s="3"/>
       <c r="E851" s="3"/>
@@ -13130,7 +13138,7 @@
       <c r="J851" s="3"/>
       <c r="K851" s="3"/>
     </row>
-    <row r="852" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C852" s="3"/>
       <c r="D852" s="3"/>
       <c r="E852" s="3"/>
@@ -13141,7 +13149,7 @@
       <c r="J852" s="3"/>
       <c r="K852" s="3"/>
     </row>
-    <row r="853" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C853" s="3"/>
       <c r="D853" s="3"/>
       <c r="E853" s="3"/>
@@ -13152,7 +13160,7 @@
       <c r="J853" s="3"/>
       <c r="K853" s="3"/>
     </row>
-    <row r="854" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C854" s="3"/>
       <c r="D854" s="3"/>
       <c r="E854" s="3"/>
@@ -13163,7 +13171,7 @@
       <c r="J854" s="3"/>
       <c r="K854" s="3"/>
     </row>
-    <row r="855" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C855" s="3"/>
       <c r="D855" s="3"/>
       <c r="E855" s="3"/>
@@ -13174,7 +13182,7 @@
       <c r="J855" s="3"/>
       <c r="K855" s="3"/>
     </row>
-    <row r="856" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C856" s="3"/>
       <c r="D856" s="3"/>
       <c r="E856" s="3"/>
@@ -13185,7 +13193,7 @@
       <c r="J856" s="3"/>
       <c r="K856" s="3"/>
     </row>
-    <row r="857" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C857" s="3"/>
       <c r="D857" s="3"/>
       <c r="E857" s="3"/>
@@ -13196,7 +13204,7 @@
       <c r="J857" s="3"/>
       <c r="K857" s="3"/>
     </row>
-    <row r="858" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C858" s="3"/>
       <c r="D858" s="3"/>
       <c r="E858" s="3"/>
@@ -13207,7 +13215,7 @@
       <c r="J858" s="3"/>
       <c r="K858" s="3"/>
     </row>
-    <row r="859" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C859" s="3"/>
       <c r="D859" s="3"/>
       <c r="E859" s="3"/>
@@ -13218,7 +13226,7 @@
       <c r="J859" s="3"/>
       <c r="K859" s="3"/>
     </row>
-    <row r="860" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C860" s="3"/>
       <c r="D860" s="3"/>
       <c r="E860" s="3"/>
@@ -13229,7 +13237,7 @@
       <c r="J860" s="3"/>
       <c r="K860" s="3"/>
     </row>
-    <row r="861" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C861" s="3"/>
       <c r="D861" s="3"/>
       <c r="E861" s="3"/>
@@ -13240,7 +13248,7 @@
       <c r="J861" s="3"/>
       <c r="K861" s="3"/>
     </row>
-    <row r="862" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C862" s="3"/>
       <c r="D862" s="3"/>
       <c r="E862" s="3"/>
@@ -13251,7 +13259,7 @@
       <c r="J862" s="3"/>
       <c r="K862" s="3"/>
     </row>
-    <row r="863" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C863" s="3"/>
       <c r="D863" s="3"/>
       <c r="E863" s="3"/>
@@ -13262,7 +13270,7 @@
       <c r="J863" s="3"/>
       <c r="K863" s="3"/>
     </row>
-    <row r="864" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C864" s="3"/>
       <c r="D864" s="3"/>
       <c r="E864" s="3"/>
@@ -13273,7 +13281,7 @@
       <c r="J864" s="3"/>
       <c r="K864" s="3"/>
     </row>
-    <row r="865" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C865" s="3"/>
       <c r="D865" s="3"/>
       <c r="E865" s="3"/>
@@ -13284,7 +13292,7 @@
       <c r="J865" s="3"/>
       <c r="K865" s="3"/>
     </row>
-    <row r="866" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C866" s="3"/>
       <c r="D866" s="3"/>
       <c r="E866" s="3"/>
@@ -13295,7 +13303,7 @@
       <c r="J866" s="3"/>
       <c r="K866" s="3"/>
     </row>
-    <row r="867" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C867" s="3"/>
       <c r="D867" s="3"/>
       <c r="E867" s="3"/>
@@ -13306,7 +13314,7 @@
       <c r="J867" s="3"/>
       <c r="K867" s="3"/>
     </row>
-    <row r="868" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C868" s="3"/>
       <c r="D868" s="3"/>
       <c r="E868" s="3"/>
@@ -13317,7 +13325,7 @@
       <c r="J868" s="3"/>
       <c r="K868" s="3"/>
     </row>
-    <row r="869" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C869" s="3"/>
       <c r="D869" s="3"/>
       <c r="E869" s="3"/>
@@ -13328,7 +13336,7 @@
       <c r="J869" s="3"/>
       <c r="K869" s="3"/>
     </row>
-    <row r="870" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C870" s="3"/>
       <c r="D870" s="3"/>
       <c r="E870" s="3"/>
@@ -13339,7 +13347,7 @@
       <c r="J870" s="3"/>
       <c r="K870" s="3"/>
     </row>
-    <row r="871" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C871" s="3"/>
       <c r="D871" s="3"/>
       <c r="E871" s="3"/>
@@ -13350,7 +13358,7 @@
       <c r="J871" s="3"/>
       <c r="K871" s="3"/>
     </row>
-    <row r="872" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C872" s="3"/>
       <c r="D872" s="3"/>
       <c r="E872" s="3"/>
@@ -13361,7 +13369,7 @@
       <c r="J872" s="3"/>
       <c r="K872" s="3"/>
     </row>
-    <row r="873" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C873" s="3"/>
       <c r="D873" s="3"/>
       <c r="E873" s="3"/>
@@ -13372,7 +13380,7 @@
       <c r="J873" s="3"/>
       <c r="K873" s="3"/>
     </row>
-    <row r="874" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C874" s="3"/>
       <c r="D874" s="3"/>
       <c r="E874" s="3"/>
@@ -13383,7 +13391,7 @@
       <c r="J874" s="3"/>
       <c r="K874" s="3"/>
     </row>
-    <row r="875" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C875" s="3"/>
       <c r="D875" s="3"/>
       <c r="E875" s="3"/>
@@ -13394,7 +13402,7 @@
       <c r="J875" s="3"/>
       <c r="K875" s="3"/>
     </row>
-    <row r="876" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C876" s="3"/>
       <c r="D876" s="3"/>
       <c r="E876" s="3"/>
@@ -13405,7 +13413,7 @@
       <c r="J876" s="3"/>
       <c r="K876" s="3"/>
     </row>
-    <row r="877" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C877" s="3"/>
       <c r="D877" s="3"/>
       <c r="E877" s="3"/>
@@ -13416,7 +13424,7 @@
       <c r="J877" s="3"/>
       <c r="K877" s="3"/>
     </row>
-    <row r="878" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C878" s="3"/>
       <c r="D878" s="3"/>
       <c r="E878" s="3"/>
@@ -13427,7 +13435,7 @@
       <c r="J878" s="3"/>
       <c r="K878" s="3"/>
     </row>
-    <row r="879" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C879" s="3"/>
       <c r="D879" s="3"/>
       <c r="E879" s="3"/>
@@ -13438,7 +13446,7 @@
       <c r="J879" s="3"/>
       <c r="K879" s="3"/>
     </row>
-    <row r="880" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C880" s="3"/>
       <c r="D880" s="3"/>
       <c r="E880" s="3"/>
@@ -13449,7 +13457,7 @@
       <c r="J880" s="3"/>
       <c r="K880" s="3"/>
     </row>
-    <row r="881" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C881" s="3"/>
       <c r="D881" s="3"/>
       <c r="E881" s="3"/>
@@ -13460,7 +13468,7 @@
       <c r="J881" s="3"/>
       <c r="K881" s="3"/>
     </row>
-    <row r="882" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C882" s="3"/>
       <c r="D882" s="3"/>
       <c r="E882" s="3"/>
@@ -13471,7 +13479,7 @@
       <c r="J882" s="3"/>
       <c r="K882" s="3"/>
     </row>
-    <row r="883" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C883" s="3"/>
       <c r="D883" s="3"/>
       <c r="E883" s="3"/>
@@ -13482,7 +13490,7 @@
       <c r="J883" s="3"/>
       <c r="K883" s="3"/>
     </row>
-    <row r="884" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C884" s="3"/>
       <c r="D884" s="3"/>
       <c r="E884" s="3"/>
@@ -13493,7 +13501,7 @@
       <c r="J884" s="3"/>
       <c r="K884" s="3"/>
     </row>
-    <row r="885" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C885" s="3"/>
       <c r="D885" s="3"/>
       <c r="E885" s="3"/>
@@ -13504,7 +13512,7 @@
       <c r="J885" s="3"/>
       <c r="K885" s="3"/>
     </row>
-    <row r="886" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C886" s="3"/>
       <c r="D886" s="3"/>
       <c r="E886" s="3"/>
@@ -13515,7 +13523,7 @@
       <c r="J886" s="3"/>
       <c r="K886" s="3"/>
     </row>
-    <row r="887" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C887" s="3"/>
       <c r="D887" s="3"/>
       <c r="E887" s="3"/>
@@ -13526,7 +13534,7 @@
       <c r="J887" s="3"/>
       <c r="K887" s="3"/>
     </row>
-    <row r="888" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C888" s="3"/>
       <c r="D888" s="3"/>
       <c r="E888" s="3"/>
@@ -13537,7 +13545,7 @@
       <c r="J888" s="3"/>
       <c r="K888" s="3"/>
     </row>
-    <row r="889" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C889" s="3"/>
       <c r="D889" s="3"/>
       <c r="E889" s="3"/>
@@ -13548,7 +13556,7 @@
       <c r="J889" s="3"/>
       <c r="K889" s="3"/>
     </row>
-    <row r="890" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C890" s="3"/>
       <c r="D890" s="3"/>
       <c r="E890" s="3"/>
@@ -13559,7 +13567,7 @@
       <c r="J890" s="3"/>
       <c r="K890" s="3"/>
     </row>
-    <row r="891" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C891" s="3"/>
       <c r="D891" s="3"/>
       <c r="E891" s="3"/>
@@ -13570,7 +13578,7 @@
       <c r="J891" s="3"/>
       <c r="K891" s="3"/>
     </row>
-    <row r="892" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C892" s="3"/>
       <c r="D892" s="3"/>
       <c r="E892" s="3"/>
@@ -13581,7 +13589,7 @@
       <c r="J892" s="3"/>
       <c r="K892" s="3"/>
     </row>
-    <row r="893" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C893" s="3"/>
       <c r="D893" s="3"/>
       <c r="E893" s="3"/>
@@ -13592,7 +13600,7 @@
       <c r="J893" s="3"/>
       <c r="K893" s="3"/>
     </row>
-    <row r="894" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C894" s="3"/>
       <c r="D894" s="3"/>
       <c r="E894" s="3"/>
@@ -13603,7 +13611,7 @@
       <c r="J894" s="3"/>
       <c r="K894" s="3"/>
     </row>
-    <row r="895" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C895" s="3"/>
       <c r="D895" s="3"/>
       <c r="E895" s="3"/>
@@ -13614,7 +13622,7 @@
       <c r="J895" s="3"/>
       <c r="K895" s="3"/>
     </row>
-    <row r="896" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C896" s="3"/>
       <c r="D896" s="3"/>
       <c r="E896" s="3"/>
@@ -13625,7 +13633,7 @@
       <c r="J896" s="3"/>
       <c r="K896" s="3"/>
     </row>
-    <row r="897" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C897" s="3"/>
       <c r="D897" s="3"/>
       <c r="E897" s="3"/>
@@ -13636,7 +13644,7 @@
       <c r="J897" s="3"/>
       <c r="K897" s="3"/>
     </row>
-    <row r="898" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C898" s="3"/>
       <c r="D898" s="3"/>
       <c r="E898" s="3"/>
@@ -13647,7 +13655,7 @@
       <c r="J898" s="3"/>
       <c r="K898" s="3"/>
     </row>
-    <row r="899" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C899" s="3"/>
       <c r="D899" s="3"/>
       <c r="E899" s="3"/>
@@ -13658,7 +13666,7 @@
       <c r="J899" s="3"/>
       <c r="K899" s="3"/>
     </row>
-    <row r="900" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C900" s="3"/>
       <c r="D900" s="3"/>
       <c r="E900" s="3"/>
@@ -13669,7 +13677,7 @@
       <c r="J900" s="3"/>
       <c r="K900" s="3"/>
     </row>
-    <row r="901" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C901" s="3"/>
       <c r="D901" s="3"/>
       <c r="E901" s="3"/>
@@ -13680,7 +13688,7 @@
       <c r="J901" s="3"/>
       <c r="K901" s="3"/>
     </row>
-    <row r="902" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C902" s="3"/>
       <c r="D902" s="3"/>
       <c r="E902" s="3"/>
@@ -13691,7 +13699,7 @@
       <c r="J902" s="3"/>
       <c r="K902" s="3"/>
     </row>
-    <row r="903" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C903" s="3"/>
       <c r="D903" s="3"/>
       <c r="E903" s="3"/>
@@ -13702,7 +13710,7 @@
       <c r="J903" s="3"/>
       <c r="K903" s="3"/>
     </row>
-    <row r="904" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C904" s="3"/>
       <c r="D904" s="3"/>
       <c r="E904" s="3"/>
@@ -13713,7 +13721,7 @@
       <c r="J904" s="3"/>
       <c r="K904" s="3"/>
     </row>
-    <row r="905" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C905" s="3"/>
       <c r="D905" s="3"/>
       <c r="E905" s="3"/>
@@ -13724,7 +13732,7 @@
       <c r="J905" s="3"/>
       <c r="K905" s="3"/>
     </row>
-    <row r="906" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C906" s="3"/>
       <c r="D906" s="3"/>
       <c r="E906" s="3"/>
@@ -13735,7 +13743,7 @@
       <c r="J906" s="3"/>
       <c r="K906" s="3"/>
     </row>
-    <row r="907" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C907" s="3"/>
       <c r="D907" s="3"/>
       <c r="E907" s="3"/>
@@ -13746,7 +13754,7 @@
       <c r="J907" s="3"/>
       <c r="K907" s="3"/>
     </row>
-    <row r="908" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C908" s="3"/>
       <c r="D908" s="3"/>
       <c r="E908" s="3"/>
@@ -13757,7 +13765,7 @@
       <c r="J908" s="3"/>
       <c r="K908" s="3"/>
     </row>
-    <row r="909" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C909" s="3"/>
       <c r="D909" s="3"/>
       <c r="E909" s="3"/>
@@ -13768,7 +13776,7 @@
       <c r="J909" s="3"/>
       <c r="K909" s="3"/>
     </row>
-    <row r="910" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C910" s="3"/>
       <c r="D910" s="3"/>
       <c r="E910" s="3"/>
@@ -13779,7 +13787,7 @@
       <c r="J910" s="3"/>
       <c r="K910" s="3"/>
     </row>
-    <row r="911" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C911" s="3"/>
       <c r="D911" s="3"/>
       <c r="E911" s="3"/>
@@ -13790,7 +13798,7 @@
       <c r="J911" s="3"/>
       <c r="K911" s="3"/>
     </row>
-    <row r="912" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C912" s="3"/>
       <c r="D912" s="3"/>
       <c r="E912" s="3"/>
@@ -13801,7 +13809,7 @@
       <c r="J912" s="3"/>
       <c r="K912" s="3"/>
     </row>
-    <row r="913" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C913" s="3"/>
       <c r="D913" s="3"/>
       <c r="E913" s="3"/>
@@ -13812,7 +13820,7 @@
       <c r="J913" s="3"/>
       <c r="K913" s="3"/>
     </row>
-    <row r="914" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C914" s="3"/>
       <c r="D914" s="3"/>
       <c r="E914" s="3"/>
@@ -13823,7 +13831,7 @@
       <c r="J914" s="3"/>
       <c r="K914" s="3"/>
     </row>
-    <row r="915" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C915" s="3"/>
       <c r="D915" s="3"/>
       <c r="E915" s="3"/>
@@ -13834,7 +13842,7 @@
       <c r="J915" s="3"/>
       <c r="K915" s="3"/>
     </row>
-    <row r="916" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C916" s="3"/>
       <c r="D916" s="3"/>
       <c r="E916" s="3"/>
@@ -13845,7 +13853,7 @@
       <c r="J916" s="3"/>
       <c r="K916" s="3"/>
     </row>
-    <row r="917" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C917" s="3"/>
       <c r="D917" s="3"/>
       <c r="E917" s="3"/>
@@ -13856,7 +13864,7 @@
       <c r="J917" s="3"/>
       <c r="K917" s="3"/>
     </row>
-    <row r="918" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C918" s="3"/>
       <c r="D918" s="3"/>
       <c r="E918" s="3"/>
@@ -13867,7 +13875,7 @@
       <c r="J918" s="3"/>
       <c r="K918" s="3"/>
     </row>
-    <row r="919" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C919" s="3"/>
       <c r="D919" s="3"/>
       <c r="E919" s="3"/>
@@ -13878,7 +13886,7 @@
       <c r="J919" s="3"/>
       <c r="K919" s="3"/>
     </row>
-    <row r="920" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C920" s="3"/>
       <c r="D920" s="3"/>
       <c r="E920" s="3"/>
@@ -13889,7 +13897,7 @@
       <c r="J920" s="3"/>
       <c r="K920" s="3"/>
     </row>
-    <row r="921" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C921" s="3"/>
       <c r="D921" s="3"/>
       <c r="E921" s="3"/>
@@ -13900,7 +13908,7 @@
       <c r="J921" s="3"/>
       <c r="K921" s="3"/>
     </row>
-    <row r="922" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C922" s="3"/>
       <c r="D922" s="3"/>
       <c r="E922" s="3"/>
@@ -13911,7 +13919,7 @@
       <c r="J922" s="3"/>
       <c r="K922" s="3"/>
     </row>
-    <row r="923" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C923" s="3"/>
       <c r="D923" s="3"/>
       <c r="E923" s="3"/>
@@ -13922,7 +13930,7 @@
       <c r="J923" s="3"/>
       <c r="K923" s="3"/>
     </row>
-    <row r="924" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C924" s="3"/>
       <c r="D924" s="3"/>
       <c r="E924" s="3"/>
@@ -13933,7 +13941,7 @@
       <c r="J924" s="3"/>
       <c r="K924" s="3"/>
     </row>
-    <row r="925" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C925" s="3"/>
       <c r="D925" s="3"/>
       <c r="E925" s="3"/>
@@ -13944,7 +13952,7 @@
       <c r="J925" s="3"/>
       <c r="K925" s="3"/>
     </row>
-    <row r="926" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C926" s="3"/>
       <c r="D926" s="3"/>
       <c r="E926" s="3"/>
@@ -13955,7 +13963,7 @@
       <c r="J926" s="3"/>
       <c r="K926" s="3"/>
     </row>
-    <row r="927" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C927" s="3"/>
       <c r="D927" s="3"/>
       <c r="E927" s="3"/>
@@ -13966,7 +13974,7 @@
       <c r="J927" s="3"/>
       <c r="K927" s="3"/>
     </row>
-    <row r="928" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C928" s="3"/>
       <c r="D928" s="3"/>
       <c r="E928" s="3"/>
@@ -13977,7 +13985,7 @@
       <c r="J928" s="3"/>
       <c r="K928" s="3"/>
     </row>
-    <row r="929" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C929" s="3"/>
       <c r="D929" s="3"/>
       <c r="E929" s="3"/>
@@ -13988,7 +13996,7 @@
       <c r="J929" s="3"/>
       <c r="K929" s="3"/>
     </row>
-    <row r="930" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C930" s="3"/>
       <c r="D930" s="3"/>
       <c r="E930" s="3"/>
@@ -13999,7 +14007,7 @@
       <c r="J930" s="3"/>
       <c r="K930" s="3"/>
     </row>
-    <row r="931" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C931" s="3"/>
       <c r="D931" s="3"/>
       <c r="E931" s="3"/>
@@ -14010,7 +14018,7 @@
       <c r="J931" s="3"/>
       <c r="K931" s="3"/>
     </row>
-    <row r="932" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C932" s="3"/>
       <c r="D932" s="3"/>
       <c r="E932" s="3"/>
@@ -14021,7 +14029,7 @@
       <c r="J932" s="3"/>
       <c r="K932" s="3"/>
     </row>
-    <row r="933" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C933" s="3"/>
       <c r="D933" s="3"/>
       <c r="E933" s="3"/>
@@ -14032,7 +14040,7 @@
       <c r="J933" s="3"/>
       <c r="K933" s="3"/>
     </row>
-    <row r="934" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C934" s="3"/>
       <c r="D934" s="3"/>
       <c r="E934" s="3"/>
@@ -14043,7 +14051,7 @@
       <c r="J934" s="3"/>
       <c r="K934" s="3"/>
     </row>
-    <row r="935" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C935" s="3"/>
       <c r="D935" s="3"/>
       <c r="E935" s="3"/>
@@ -14054,7 +14062,7 @@
       <c r="J935" s="3"/>
       <c r="K935" s="3"/>
     </row>
-    <row r="936" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C936" s="3"/>
       <c r="D936" s="3"/>
       <c r="E936" s="3"/>
@@ -14065,7 +14073,7 @@
       <c r="J936" s="3"/>
       <c r="K936" s="3"/>
     </row>
-    <row r="937" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C937" s="3"/>
       <c r="D937" s="3"/>
       <c r="E937" s="3"/>
@@ -14076,7 +14084,7 @@
       <c r="J937" s="3"/>
       <c r="K937" s="3"/>
     </row>
-    <row r="938" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C938" s="3"/>
       <c r="D938" s="3"/>
       <c r="E938" s="3"/>
@@ -14087,7 +14095,7 @@
       <c r="J938" s="3"/>
       <c r="K938" s="3"/>
     </row>
-    <row r="939" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C939" s="3"/>
       <c r="D939" s="3"/>
       <c r="E939" s="3"/>
@@ -14098,7 +14106,7 @@
       <c r="J939" s="3"/>
       <c r="K939" s="3"/>
     </row>
-    <row r="940" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C940" s="3"/>
       <c r="D940" s="3"/>
       <c r="E940" s="3"/>
@@ -14109,7 +14117,7 @@
       <c r="J940" s="3"/>
       <c r="K940" s="3"/>
     </row>
-    <row r="941" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C941" s="3"/>
       <c r="D941" s="3"/>
       <c r="E941" s="3"/>
@@ -14120,7 +14128,7 @@
       <c r="J941" s="3"/>
       <c r="K941" s="3"/>
     </row>
-    <row r="942" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C942" s="3"/>
       <c r="D942" s="3"/>
       <c r="E942" s="3"/>
@@ -14131,7 +14139,7 @@
       <c r="J942" s="3"/>
       <c r="K942" s="3"/>
     </row>
-    <row r="943" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C943" s="3"/>
       <c r="D943" s="3"/>
       <c r="E943" s="3"/>
@@ -14142,7 +14150,7 @@
       <c r="J943" s="3"/>
       <c r="K943" s="3"/>
     </row>
-    <row r="944" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C944" s="3"/>
       <c r="D944" s="3"/>
       <c r="E944" s="3"/>
@@ -14153,7 +14161,7 @@
       <c r="J944" s="3"/>
       <c r="K944" s="3"/>
     </row>
-    <row r="945" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C945" s="3"/>
       <c r="D945" s="3"/>
       <c r="E945" s="3"/>
@@ -14164,7 +14172,7 @@
       <c r="J945" s="3"/>
       <c r="K945" s="3"/>
     </row>
-    <row r="946" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C946" s="3"/>
       <c r="D946" s="3"/>
       <c r="E946" s="3"/>
@@ -14175,7 +14183,7 @@
       <c r="J946" s="3"/>
       <c r="K946" s="3"/>
     </row>
-    <row r="947" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C947" s="3"/>
       <c r="D947" s="3"/>
       <c r="E947" s="3"/>
@@ -14186,7 +14194,7 @@
       <c r="J947" s="3"/>
       <c r="K947" s="3"/>
     </row>
-    <row r="948" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C948" s="3"/>
       <c r="D948" s="3"/>
       <c r="E948" s="3"/>
@@ -14197,7 +14205,7 @@
       <c r="J948" s="3"/>
       <c r="K948" s="3"/>
     </row>
-    <row r="949" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C949" s="3"/>
       <c r="D949" s="3"/>
       <c r="E949" s="3"/>
@@ -14208,7 +14216,7 @@
       <c r="J949" s="3"/>
       <c r="K949" s="3"/>
     </row>
-    <row r="950" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C950" s="3"/>
       <c r="D950" s="3"/>
       <c r="E950" s="3"/>
@@ -14219,7 +14227,7 @@
       <c r="J950" s="3"/>
       <c r="K950" s="3"/>
     </row>
-    <row r="951" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C951" s="3"/>
       <c r="D951" s="3"/>
       <c r="E951" s="3"/>
@@ -14230,7 +14238,7 @@
       <c r="J951" s="3"/>
       <c r="K951" s="3"/>
     </row>
-    <row r="952" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C952" s="3"/>
       <c r="D952" s="3"/>
       <c r="E952" s="3"/>
@@ -14241,7 +14249,7 @@
       <c r="J952" s="3"/>
       <c r="K952" s="3"/>
     </row>
-    <row r="953" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C953" s="3"/>
       <c r="D953" s="3"/>
       <c r="E953" s="3"/>
@@ -14252,7 +14260,7 @@
       <c r="J953" s="3"/>
       <c r="K953" s="3"/>
     </row>
-    <row r="954" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C954" s="3"/>
       <c r="D954" s="3"/>
       <c r="E954" s="3"/>
@@ -14263,7 +14271,7 @@
       <c r="J954" s="3"/>
       <c r="K954" s="3"/>
     </row>
-    <row r="955" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C955" s="3"/>
       <c r="D955" s="3"/>
       <c r="E955" s="3"/>
@@ -14274,7 +14282,7 @@
       <c r="J955" s="3"/>
       <c r="K955" s="3"/>
     </row>
-    <row r="956" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C956" s="3"/>
       <c r="D956" s="3"/>
       <c r="E956" s="3"/>
@@ -14285,7 +14293,7 @@
       <c r="J956" s="3"/>
       <c r="K956" s="3"/>
     </row>
-    <row r="957" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C957" s="3"/>
       <c r="D957" s="3"/>
       <c r="E957" s="3"/>
@@ -14296,7 +14304,7 @@
       <c r="J957" s="3"/>
       <c r="K957" s="3"/>
     </row>
-    <row r="958" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C958" s="3"/>
       <c r="D958" s="3"/>
       <c r="E958" s="3"/>
@@ -14307,7 +14315,7 @@
       <c r="J958" s="3"/>
       <c r="K958" s="3"/>
     </row>
-    <row r="959" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C959" s="3"/>
       <c r="D959" s="3"/>
       <c r="E959" s="3"/>
@@ -14318,7 +14326,7 @@
       <c r="J959" s="3"/>
       <c r="K959" s="3"/>
     </row>
-    <row r="960" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C960" s="3"/>
       <c r="D960" s="3"/>
       <c r="E960" s="3"/>
@@ -14329,7 +14337,7 @@
       <c r="J960" s="3"/>
       <c r="K960" s="3"/>
     </row>
-    <row r="961" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C961" s="3"/>
       <c r="D961" s="3"/>
       <c r="E961" s="3"/>
@@ -14340,7 +14348,7 @@
       <c r="J961" s="3"/>
       <c r="K961" s="3"/>
     </row>
-    <row r="962" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C962" s="3"/>
       <c r="D962" s="3"/>
       <c r="E962" s="3"/>
@@ -14351,7 +14359,7 @@
       <c r="J962" s="3"/>
       <c r="K962" s="3"/>
     </row>
-    <row r="963" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C963" s="3"/>
       <c r="D963" s="3"/>
       <c r="E963" s="3"/>
@@ -14362,7 +14370,7 @@
       <c r="J963" s="3"/>
       <c r="K963" s="3"/>
     </row>
-    <row r="964" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C964" s="3"/>
       <c r="D964" s="3"/>
       <c r="E964" s="3"/>
@@ -14373,7 +14381,7 @@
       <c r="J964" s="3"/>
       <c r="K964" s="3"/>
     </row>
-    <row r="965" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C965" s="3"/>
       <c r="D965" s="3"/>
       <c r="E965" s="3"/>
@@ -14384,7 +14392,7 @@
       <c r="J965" s="3"/>
       <c r="K965" s="3"/>
     </row>
-    <row r="966" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C966" s="3"/>
       <c r="D966" s="3"/>
       <c r="E966" s="3"/>
@@ -14395,7 +14403,7 @@
       <c r="J966" s="3"/>
       <c r="K966" s="3"/>
     </row>
-    <row r="967" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C967" s="3"/>
       <c r="D967" s="3"/>
       <c r="E967" s="3"/>
@@ -14406,7 +14414,7 @@
       <c r="J967" s="3"/>
       <c r="K967" s="3"/>
     </row>
-    <row r="968" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C968" s="3"/>
       <c r="D968" s="3"/>
       <c r="E968" s="3"/>
@@ -14417,7 +14425,7 @@
       <c r="J968" s="3"/>
       <c r="K968" s="3"/>
     </row>
-    <row r="969" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C969" s="3"/>
       <c r="D969" s="3"/>
       <c r="E969" s="3"/>
@@ -14428,7 +14436,7 @@
       <c r="J969" s="3"/>
       <c r="K969" s="3"/>
     </row>
-    <row r="970" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C970" s="3"/>
       <c r="D970" s="3"/>
       <c r="E970" s="3"/>
@@ -14439,7 +14447,7 @@
       <c r="J970" s="3"/>
       <c r="K970" s="3"/>
     </row>
-    <row r="971" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C971" s="3"/>
       <c r="D971" s="3"/>
       <c r="E971" s="3"/>
@@ -14450,7 +14458,7 @@
       <c r="J971" s="3"/>
       <c r="K971" s="3"/>
     </row>
-    <row r="972" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C972" s="3"/>
       <c r="D972" s="3"/>
       <c r="E972" s="3"/>
@@ -14461,7 +14469,7 @@
       <c r="J972" s="3"/>
       <c r="K972" s="3"/>
     </row>
-    <row r="973" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C973" s="3"/>
       <c r="D973" s="3"/>
       <c r="E973" s="3"/>
@@ -14472,7 +14480,7 @@
       <c r="J973" s="3"/>
       <c r="K973" s="3"/>
     </row>
-    <row r="974" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C974" s="3"/>
       <c r="D974" s="3"/>
       <c r="E974" s="3"/>
@@ -14483,7 +14491,7 @@
       <c r="J974" s="3"/>
       <c r="K974" s="3"/>
     </row>
-    <row r="975" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C975" s="3"/>
       <c r="D975" s="3"/>
       <c r="E975" s="3"/>
@@ -14494,7 +14502,7 @@
       <c r="J975" s="3"/>
       <c r="K975" s="3"/>
     </row>
-    <row r="976" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C976" s="3"/>
       <c r="D976" s="3"/>
       <c r="E976" s="3"/>
@@ -14505,7 +14513,7 @@
       <c r="J976" s="3"/>
       <c r="K976" s="3"/>
     </row>
-    <row r="977" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C977" s="3"/>
       <c r="D977" s="3"/>
       <c r="E977" s="3"/>
@@ -14516,7 +14524,7 @@
       <c r="J977" s="3"/>
       <c r="K977" s="3"/>
     </row>
-    <row r="978" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C978" s="3"/>
       <c r="D978" s="3"/>
       <c r="E978" s="3"/>
@@ -14527,7 +14535,7 @@
       <c r="J978" s="3"/>
       <c r="K978" s="3"/>
     </row>
-    <row r="979" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C979" s="3"/>
       <c r="D979" s="3"/>
       <c r="E979" s="3"/>
@@ -14538,7 +14546,7 @@
       <c r="J979" s="3"/>
       <c r="K979" s="3"/>
     </row>
-    <row r="980" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C980" s="3"/>
       <c r="D980" s="3"/>
       <c r="E980" s="3"/>
@@ -14549,7 +14557,7 @@
       <c r="J980" s="3"/>
       <c r="K980" s="3"/>
     </row>
-    <row r="981" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C981" s="3"/>
       <c r="D981" s="3"/>
       <c r="E981" s="3"/>
@@ -14560,7 +14568,7 @@
       <c r="J981" s="3"/>
       <c r="K981" s="3"/>
     </row>
-    <row r="982" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="982" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C982" s="3"/>
       <c r="D982" s="3"/>
       <c r="E982" s="3"/>
@@ -14571,7 +14579,7 @@
       <c r="J982" s="3"/>
       <c r="K982" s="3"/>
     </row>
-    <row r="983" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="983" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C983" s="3"/>
       <c r="D983" s="3"/>
       <c r="E983" s="3"/>
@@ -14582,7 +14590,7 @@
       <c r="J983" s="3"/>
       <c r="K983" s="3"/>
     </row>
-    <row r="984" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="984" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C984" s="3"/>
       <c r="D984" s="3"/>
       <c r="E984" s="3"/>
@@ -14593,7 +14601,7 @@
       <c r="J984" s="3"/>
       <c r="K984" s="3"/>
     </row>
-    <row r="985" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="985" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C985" s="3"/>
       <c r="D985" s="3"/>
       <c r="E985" s="3"/>
@@ -14604,7 +14612,7 @@
       <c r="J985" s="3"/>
       <c r="K985" s="3"/>
     </row>
-    <row r="986" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="986" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C986" s="3"/>
       <c r="D986" s="3"/>
       <c r="E986" s="3"/>
@@ -14615,7 +14623,7 @@
       <c r="J986" s="3"/>
       <c r="K986" s="3"/>
     </row>
-    <row r="987" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="987" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C987" s="3"/>
       <c r="D987" s="3"/>
       <c r="E987" s="3"/>
@@ -14626,7 +14634,7 @@
       <c r="J987" s="3"/>
       <c r="K987" s="3"/>
     </row>
-    <row r="988" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="988" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C988" s="3"/>
       <c r="D988" s="3"/>
       <c r="E988" s="3"/>
@@ -14637,7 +14645,7 @@
       <c r="J988" s="3"/>
       <c r="K988" s="3"/>
     </row>
-    <row r="989" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="989" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C989" s="3"/>
       <c r="D989" s="3"/>
       <c r="E989" s="3"/>
@@ -14648,7 +14656,7 @@
       <c r="J989" s="3"/>
       <c r="K989" s="3"/>
     </row>
-    <row r="990" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="990" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C990" s="3"/>
       <c r="D990" s="3"/>
       <c r="E990" s="3"/>
@@ -14659,7 +14667,7 @@
       <c r="J990" s="3"/>
       <c r="K990" s="3"/>
     </row>
-    <row r="991" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="991" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C991" s="3"/>
       <c r="D991" s="3"/>
       <c r="E991" s="3"/>
@@ -14670,7 +14678,7 @@
       <c r="J991" s="3"/>
       <c r="K991" s="3"/>
     </row>
-    <row r="992" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="992" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C992" s="3"/>
       <c r="D992" s="3"/>
       <c r="E992" s="3"/>
@@ -14681,7 +14689,7 @@
       <c r="J992" s="3"/>
       <c r="K992" s="3"/>
     </row>
-    <row r="993" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="993" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C993" s="3"/>
       <c r="D993" s="3"/>
       <c r="E993" s="3"/>
@@ -14692,7 +14700,7 @@
       <c r="J993" s="3"/>
       <c r="K993" s="3"/>
     </row>
-    <row r="994" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="994" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C994" s="3"/>
       <c r="D994" s="3"/>
       <c r="E994" s="3"/>
@@ -14703,7 +14711,7 @@
       <c r="J994" s="3"/>
       <c r="K994" s="3"/>
     </row>
-    <row r="995" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="995" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C995" s="3"/>
       <c r="D995" s="3"/>
       <c r="E995" s="3"/>
@@ -14714,7 +14722,7 @@
       <c r="J995" s="3"/>
       <c r="K995" s="3"/>
     </row>
-    <row r="996" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="996" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C996" s="3"/>
       <c r="D996" s="3"/>
       <c r="E996" s="3"/>
@@ -14725,7 +14733,7 @@
       <c r="J996" s="3"/>
       <c r="K996" s="3"/>
     </row>
-    <row r="997" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="997" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C997" s="3"/>
       <c r="D997" s="3"/>
       <c r="E997" s="3"/>
@@ -14736,7 +14744,7 @@
       <c r="J997" s="3"/>
       <c r="K997" s="3"/>
     </row>
-    <row r="998" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="998" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C998" s="3"/>
       <c r="D998" s="3"/>
       <c r="E998" s="3"/>
@@ -14747,7 +14755,7 @@
       <c r="J998" s="3"/>
       <c r="K998" s="3"/>
     </row>
-    <row r="999" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="999" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C999" s="3"/>
       <c r="D999" s="3"/>
       <c r="E999" s="3"/>
@@ -14758,7 +14766,7 @@
       <c r="J999" s="3"/>
       <c r="K999" s="3"/>
     </row>
-    <row r="1000" spans="3:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="1000" spans="3:11" ht="13.2" x14ac:dyDescent="0.25">
       <c r="C1000" s="3"/>
       <c r="D1000" s="3"/>
       <c r="E1000" s="3"/>

--- a/assets/data/anime.xlsx
+++ b/assets/data/anime.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Anime Archive\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A41953-1B30-4BBD-9E9E-56E6F1E2DED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF0E850-F746-4B18-A731-C30503F9DD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2533,7 +2533,7 @@
         <v>151</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R22" s="4" t="s">
         <v>144</v>
